--- a/concursoai_roadmap_v3_FINAL.xlsx
+++ b/concursoai_roadmap_v3_FINAL.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="54">
+  <fonts count="55">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -329,6 +329,11 @@
       <color rgb="00CDD9E5"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00D4A017"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="26">
     <fill>
@@ -528,7 +533,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -761,6 +766,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4091,9 +4099,9 @@
       <c r="Q25" s="40" t="inlineStr"/>
       <c r="R25" s="40" t="inlineStr"/>
       <c r="S25" s="40" t="inlineStr"/>
-      <c r="T25" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T25" s="42" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
         </is>
       </c>
       <c r="U25" s="41" t="inlineStr">
@@ -4143,9 +4151,9 @@
       <c r="Q26" s="40" t="inlineStr"/>
       <c r="R26" s="40" t="inlineStr"/>
       <c r="S26" s="40" t="inlineStr"/>
-      <c r="T26" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T26" s="42" t="inlineStr">
+        <is>
+          <t>✅ Concluido</t>
         </is>
       </c>
       <c r="U26" s="41" t="inlineStr">
@@ -4195,9 +4203,9 @@
       <c r="Q27" s="40" t="inlineStr"/>
       <c r="R27" s="40" t="inlineStr"/>
       <c r="S27" s="40" t="inlineStr"/>
-      <c r="T27" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T27" s="42" t="inlineStr">
+        <is>
+          <t>✅ Concluido</t>
         </is>
       </c>
       <c r="U27" s="41" t="inlineStr">
@@ -4247,9 +4255,9 @@
       <c r="Q28" s="40" t="inlineStr"/>
       <c r="R28" s="40" t="inlineStr"/>
       <c r="S28" s="40" t="inlineStr"/>
-      <c r="T28" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T28" s="42" t="inlineStr">
+        <is>
+          <t>✅ Concluido</t>
         </is>
       </c>
       <c r="U28" s="41" t="inlineStr"/>
@@ -4295,9 +4303,9 @@
       <c r="Q29" s="40" t="inlineStr"/>
       <c r="R29" s="40" t="inlineStr"/>
       <c r="S29" s="40" t="inlineStr"/>
-      <c r="T29" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T29" s="42" t="inlineStr">
+        <is>
+          <t>✅ Concluido</t>
         </is>
       </c>
       <c r="U29" s="41" t="inlineStr">

--- a/concursoai_roadmap_v3_FINAL.xlsx
+++ b/concursoai_roadmap_v3_FINAL.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="55">
+  <fonts count="58">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -334,8 +334,25 @@
       <color rgb="00D4A017"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0000b4a6"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="008ab0c8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="008ab0c8"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="26">
+  <fills count="28">
     <fill>
       <patternFill/>
     </fill>
@@ -462,6 +479,16 @@
         <fgColor rgb="005A3C00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001a3a5c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001a2a1a"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -533,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -769,6 +796,15 @@
     <xf numFmtId="0" fontId="54" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2921,7 +2957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V259"/>
+  <dimension ref="A1:V281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -4355,9 +4391,9 @@
       <c r="Q30" s="40" t="inlineStr"/>
       <c r="R30" s="40" t="inlineStr"/>
       <c r="S30" s="40" t="inlineStr"/>
-      <c r="T30" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T30" s="42" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
         </is>
       </c>
       <c r="U30" s="41" t="inlineStr">
@@ -4407,9 +4443,9 @@
       <c r="Q31" s="40" t="inlineStr"/>
       <c r="R31" s="40" t="inlineStr"/>
       <c r="S31" s="40" t="inlineStr"/>
-      <c r="T31" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T31" s="42" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
         </is>
       </c>
       <c r="U31" s="41" t="inlineStr">
@@ -4483,9 +4519,9 @@
       <c r="Q33" s="40" t="inlineStr"/>
       <c r="R33" s="40" t="inlineStr"/>
       <c r="S33" s="40" t="inlineStr"/>
-      <c r="T33" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T33" s="42" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
         </is>
       </c>
       <c r="U33" s="41" t="inlineStr"/>
@@ -4531,9 +4567,9 @@
       <c r="Q34" s="40" t="inlineStr"/>
       <c r="R34" s="40" t="inlineStr"/>
       <c r="S34" s="40" t="inlineStr"/>
-      <c r="T34" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T34" s="42" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
         </is>
       </c>
       <c r="U34" s="41" t="inlineStr"/>
@@ -4579,9 +4615,9 @@
       <c r="Q35" s="40" t="inlineStr"/>
       <c r="R35" s="40" t="inlineStr"/>
       <c r="S35" s="40" t="inlineStr"/>
-      <c r="T35" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T35" s="42" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
         </is>
       </c>
       <c r="U35" s="41" t="inlineStr">
@@ -4631,9 +4667,9 @@
       <c r="Q36" s="40" t="inlineStr"/>
       <c r="R36" s="40" t="inlineStr"/>
       <c r="S36" s="40" t="inlineStr"/>
-      <c r="T36" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T36" s="42" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
         </is>
       </c>
       <c r="U36" s="41" t="inlineStr"/>
@@ -4683,9 +4719,9 @@
       <c r="Q37" s="40" t="inlineStr"/>
       <c r="R37" s="40" t="inlineStr"/>
       <c r="S37" s="40" t="inlineStr"/>
-      <c r="T37" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T37" s="42" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
         </is>
       </c>
       <c r="U37" s="41" t="inlineStr"/>
@@ -4731,9 +4767,9 @@
       <c r="Q38" s="40" t="inlineStr"/>
       <c r="R38" s="40" t="inlineStr"/>
       <c r="S38" s="40" t="inlineStr"/>
-      <c r="T38" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T38" s="42" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
         </is>
       </c>
       <c r="U38" s="41" t="inlineStr"/>
@@ -4779,9 +4815,9 @@
       <c r="Q39" s="40" t="inlineStr"/>
       <c r="R39" s="40" t="inlineStr"/>
       <c r="S39" s="40" t="inlineStr"/>
-      <c r="T39" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T39" s="42" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
         </is>
       </c>
       <c r="U39" s="41" t="inlineStr">
@@ -4827,1137 +4863,632 @@
       <c r="Q40" s="40" t="inlineStr"/>
       <c r="R40" s="40" t="inlineStr"/>
       <c r="S40" s="40" t="inlineStr"/>
-      <c r="T40" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T40" s="42" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
         </is>
       </c>
       <c r="U40" s="41" t="inlineStr"/>
       <c r="V40" s="1" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ◆  DEPLOY BETA — Railway   ·   Semana 5 (fim)</t>
-        </is>
-      </c>
-      <c r="C41" s="78" t="n"/>
-      <c r="D41" s="78" t="n"/>
-      <c r="E41" s="78" t="n"/>
-      <c r="F41" s="78" t="n"/>
-      <c r="G41" s="78" t="n"/>
-      <c r="H41" s="78" t="n"/>
-      <c r="I41" s="78" t="n"/>
-      <c r="J41" s="78" t="n"/>
-      <c r="K41" s="78" t="n"/>
-      <c r="L41" s="78" t="n"/>
-      <c r="M41" s="78" t="n"/>
-      <c r="N41" s="78" t="n"/>
-      <c r="O41" s="78" t="n"/>
-      <c r="P41" s="78" t="n"/>
-      <c r="Q41" s="78" t="n"/>
-      <c r="R41" s="78" t="n"/>
-      <c r="S41" s="78" t="n"/>
-      <c r="T41" s="78" t="n"/>
-      <c r="U41" s="79" t="n"/>
-      <c r="V41" s="1" t="n"/>
+      <c r="A41" s="81" t="n"/>
+      <c r="B41" s="82" t="inlineStr">
+        <is>
+          <t>INTEGRAÇÃO</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>DEPLOY</t>
-        </is>
-      </c>
-      <c r="C42" s="37" t="inlineStr">
-        <is>
-          <t>Criar Procfile + railway.toml</t>
-        </is>
-      </c>
-      <c r="D42" s="38" t="inlineStr"/>
-      <c r="E42" s="38" t="inlineStr">
-        <is>
-          <t>⚙️ Config</t>
-        </is>
-      </c>
-      <c r="F42" s="40" t="inlineStr"/>
-      <c r="G42" s="40" t="inlineStr"/>
-      <c r="H42" s="40" t="inlineStr"/>
-      <c r="I42" s="40" t="inlineStr"/>
-      <c r="J42" s="57" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="K42" s="40" t="inlineStr"/>
-      <c r="L42" s="40" t="inlineStr"/>
-      <c r="M42" s="40" t="inlineStr"/>
-      <c r="N42" s="40" t="inlineStr"/>
-      <c r="O42" s="40" t="inlineStr"/>
-      <c r="P42" s="40" t="inlineStr"/>
-      <c r="Q42" s="40" t="inlineStr"/>
-      <c r="R42" s="40" t="inlineStr"/>
-      <c r="S42" s="40" t="inlineStr"/>
-      <c r="T42" s="38" t="inlineStr">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>INTEGRAÇÃO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Conectar login/cadastro Streamlit ao POST /auth/register e POST /auth/login</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>JWT salvo em session_state</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>💻 Backend</t>
+        </is>
+      </c>
+      <c r="T42" s="89" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>INTEGRAÇÃO</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Conectar Onboarding Tela 5 ao POST /onboarding (passa perfil A/B/C + tempo_por_materia + dados_csv)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Salva no banco novo</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>💻 Backend</t>
+        </is>
+      </c>
+      <c r="T43" s="89" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>INTEGRAÇÃO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Conectar pg_lancar_bateria ao POST /bateria</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Substitui database.py antigo</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>💻 Backend</t>
+        </is>
+      </c>
+      <c r="T44" s="89" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>INTEGRAÇÃO</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Conectar pg_registrar_erros ao POST /erro-critico</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Substitui database.py antigo</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>💻 Backend</t>
+        </is>
+      </c>
+      <c r="T45" s="89" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>INTEGRAÇÃO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Conectar pg_historico ao GET /baterias</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Paginação real</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>💻 Backend</t>
+        </is>
+      </c>
+      <c r="T46" s="89" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>INTEGRAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>INTEGRAÇÃO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Conectar pg_dashboard ao GET /desempenho (métricas reais)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Dados ao vivo</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>💻 Backend</t>
+        </is>
+      </c>
+      <c r="T48" s="84" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U42" s="41" t="inlineStr">
-        <is>
-          <t>web: uvicorn app.main:app --host 0.0.0.0 --port $PORT</t>
-        </is>
-      </c>
-      <c r="V42" s="1" t="n"/>
-    </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>DEPLOY</t>
-        </is>
-      </c>
-      <c r="C43" s="37" t="inlineStr">
-        <is>
-          <t>Criar conta Railway + conectar GitHub + Plugin PostgreSQL</t>
-        </is>
-      </c>
-      <c r="D43" s="38" t="inlineStr"/>
-      <c r="E43" s="38" t="inlineStr">
-        <is>
-          <t>⚙️ Config</t>
-        </is>
-      </c>
-      <c r="F43" s="40" t="inlineStr"/>
-      <c r="G43" s="40" t="inlineStr"/>
-      <c r="H43" s="40" t="inlineStr"/>
-      <c r="I43" s="40" t="inlineStr"/>
-      <c r="J43" s="57" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="K43" s="40" t="inlineStr"/>
-      <c r="L43" s="40" t="inlineStr"/>
-      <c r="M43" s="40" t="inlineStr"/>
-      <c r="N43" s="40" t="inlineStr"/>
-      <c r="O43" s="40" t="inlineStr"/>
-      <c r="P43" s="40" t="inlineStr"/>
-      <c r="Q43" s="40" t="inlineStr"/>
-      <c r="R43" s="40" t="inlineStr"/>
-      <c r="S43" s="40" t="inlineStr"/>
-      <c r="T43" s="38" t="inlineStr">
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="85" t="n"/>
+      <c r="B49" s="86" t="inlineStr">
+        <is>
+          <t>TESTES</t>
+        </is>
+      </c>
+      <c r="C49" s="87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ◆  TESTES PRÉ-DEPLOY — Validação Visual Completa</t>
+        </is>
+      </c>
+      <c r="D49" s="85" t="n"/>
+      <c r="E49" s="85" t="n"/>
+      <c r="F49" s="85" t="n"/>
+      <c r="G49" s="85" t="n"/>
+      <c r="H49" s="85" t="n"/>
+      <c r="I49" s="85" t="n"/>
+      <c r="J49" s="85" t="n"/>
+      <c r="K49" s="85" t="n"/>
+      <c r="L49" s="85" t="n"/>
+      <c r="M49" s="85" t="n"/>
+      <c r="N49" s="85" t="n"/>
+      <c r="O49" s="85" t="n"/>
+      <c r="P49" s="85" t="n"/>
+      <c r="Q49" s="85" t="n"/>
+      <c r="R49" s="85" t="n"/>
+      <c r="S49" s="85" t="n"/>
+      <c r="T49" s="85" t="n"/>
+      <c r="U49" s="85" t="n"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>TESTES</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TESTE — Login: criar conta nova, login com senha correta, erro com senha errada</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Validar mensagens de erro</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
+        </is>
+      </c>
+      <c r="T50" s="84" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U43" s="41" t="inlineStr"/>
-      <c r="V43" s="1" t="n"/>
-    </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>DEPLOY</t>
-        </is>
-      </c>
-      <c r="C44" s="37" t="inlineStr">
-        <is>
-          <t>railway run alembic upgrade head</t>
-        </is>
-      </c>
-      <c r="D44" s="38" t="inlineStr"/>
-      <c r="E44" s="38" t="inlineStr">
-        <is>
-          <t>💻 Terminal</t>
-        </is>
-      </c>
-      <c r="F44" s="40" t="inlineStr"/>
-      <c r="G44" s="40" t="inlineStr"/>
-      <c r="H44" s="40" t="inlineStr"/>
-      <c r="I44" s="40" t="inlineStr"/>
-      <c r="J44" s="57" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="K44" s="40" t="inlineStr"/>
-      <c r="L44" s="40" t="inlineStr"/>
-      <c r="M44" s="40" t="inlineStr"/>
-      <c r="N44" s="40" t="inlineStr"/>
-      <c r="O44" s="40" t="inlineStr"/>
-      <c r="P44" s="40" t="inlineStr"/>
-      <c r="Q44" s="40" t="inlineStr"/>
-      <c r="R44" s="40" t="inlineStr"/>
-      <c r="S44" s="40" t="inlineStr"/>
-      <c r="T44" s="38" t="inlineStr">
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>TESTES</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TESTE — Onboarding Perfil A: fluxar as 5 telas do zero, verificar cronograma na Tela 5</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Tópicos aparecem?</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
+        </is>
+      </c>
+      <c r="T51" s="84" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U44" s="41" t="inlineStr"/>
-      <c r="V44" s="1" t="n"/>
-    </row>
-    <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>DEPLOY</t>
-        </is>
-      </c>
-      <c r="C45" s="37" t="inlineStr">
-        <is>
-          <t>Criar contas beta testers — script criar_usuario.py</t>
-        </is>
-      </c>
-      <c r="D45" s="38" t="inlineStr"/>
-      <c r="E45" s="38" t="inlineStr">
-        <is>
-          <t>⚙️ Config</t>
-        </is>
-      </c>
-      <c r="F45" s="40" t="inlineStr"/>
-      <c r="G45" s="40" t="inlineStr"/>
-      <c r="H45" s="40" t="inlineStr"/>
-      <c r="I45" s="40" t="inlineStr"/>
-      <c r="J45" s="57" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="K45" s="40" t="inlineStr"/>
-      <c r="L45" s="40" t="inlineStr"/>
-      <c r="M45" s="40" t="inlineStr"/>
-      <c r="N45" s="40" t="inlineStr"/>
-      <c r="O45" s="40" t="inlineStr"/>
-      <c r="P45" s="40" t="inlineStr"/>
-      <c r="Q45" s="40" t="inlineStr"/>
-      <c r="R45" s="40" t="inlineStr"/>
-      <c r="S45" s="40" t="inlineStr"/>
-      <c r="T45" s="38" t="inlineStr">
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>TESTES</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TESTE — Onboarding Perfil B: declarar tempos por matéria, verificar níveis na Tela 5</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>básico/inter/avançado/expert</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
+        </is>
+      </c>
+      <c r="T52" s="84" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U45" s="41" t="inlineStr"/>
-      <c r="V45" s="1" t="n"/>
-    </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="1" t="n"/>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>DEPLOY</t>
-        </is>
-      </c>
-      <c r="C46" s="37" t="inlineStr">
-        <is>
-          <t>Validar fluxo online com dados reais</t>
-        </is>
-      </c>
-      <c r="D46" s="38" t="inlineStr"/>
-      <c r="E46" s="42" t="inlineStr">
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>TESTES</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TESTE — Onboarding Perfil C: importar CSV Qconcursos, verificar dados na Tela 5</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Proficiência populada?</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
         <is>
           <t>✅ Teste</t>
         </is>
       </c>
-      <c r="F46" s="40" t="inlineStr"/>
-      <c r="G46" s="40" t="inlineStr"/>
-      <c r="H46" s="40" t="inlineStr"/>
-      <c r="I46" s="40" t="inlineStr"/>
-      <c r="J46" s="57" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="K46" s="40" t="inlineStr"/>
-      <c r="L46" s="40" t="inlineStr"/>
-      <c r="M46" s="40" t="inlineStr"/>
-      <c r="N46" s="40" t="inlineStr"/>
-      <c r="O46" s="40" t="inlineStr"/>
-      <c r="P46" s="40" t="inlineStr"/>
-      <c r="Q46" s="40" t="inlineStr"/>
-      <c r="R46" s="40" t="inlineStr"/>
-      <c r="S46" s="40" t="inlineStr"/>
-      <c r="T46" s="38" t="inlineStr">
+      <c r="T53" s="89" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>TESTES</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>TESTE — Dashboard: métricas carregam, gráficos aparecem, sem erro de tela vazia</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Dados reais do banco</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
+        </is>
+      </c>
+      <c r="T54" s="84" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U46" s="41" t="inlineStr">
-        <is>
-          <t>Marco: URL pública funcionando</t>
-        </is>
-      </c>
-      <c r="V46" s="1" t="n"/>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="1" t="n"/>
-      <c r="B47" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ◆  FASE 3 — Algoritmo de Priorização + Cronograma Inteligente   ·   Semanas 6–9</t>
-        </is>
-      </c>
-      <c r="C47" s="78" t="n"/>
-      <c r="D47" s="78" t="n"/>
-      <c r="E47" s="78" t="n"/>
-      <c r="F47" s="78" t="n"/>
-      <c r="G47" s="78" t="n"/>
-      <c r="H47" s="78" t="n"/>
-      <c r="I47" s="78" t="n"/>
-      <c r="J47" s="78" t="n"/>
-      <c r="K47" s="78" t="n"/>
-      <c r="L47" s="78" t="n"/>
-      <c r="M47" s="78" t="n"/>
-      <c r="N47" s="78" t="n"/>
-      <c r="O47" s="78" t="n"/>
-      <c r="P47" s="78" t="n"/>
-      <c r="Q47" s="78" t="n"/>
-      <c r="R47" s="78" t="n"/>
-      <c r="S47" s="78" t="n"/>
-      <c r="T47" s="78" t="n"/>
-      <c r="U47" s="79" t="n"/>
-      <c r="V47" s="1" t="n"/>
-    </row>
-    <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="1" t="n"/>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C48" s="37" t="inlineStr">
-        <is>
-          <t>services/priorizacao.py — fórmula: W1×Urgência + W2×Lacuna + W3×Peso + W4×Erros</t>
-        </is>
-      </c>
-      <c r="D48" s="45" t="inlineStr">
-        <is>
-          <t>L-03</t>
-        </is>
-      </c>
-      <c r="E48" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
-        </is>
-      </c>
-      <c r="F48" s="40" t="inlineStr"/>
-      <c r="G48" s="40" t="inlineStr"/>
-      <c r="H48" s="40" t="inlineStr"/>
-      <c r="I48" s="40" t="inlineStr"/>
-      <c r="J48" s="40" t="inlineStr"/>
-      <c r="K48" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="L48" s="40" t="inlineStr"/>
-      <c r="M48" s="40" t="inlineStr"/>
-      <c r="N48" s="40" t="inlineStr"/>
-      <c r="O48" s="40" t="inlineStr"/>
-      <c r="P48" s="40" t="inlineStr"/>
-      <c r="Q48" s="40" t="inlineStr"/>
-      <c r="R48" s="40" t="inlineStr"/>
-      <c r="S48" s="40" t="inlineStr"/>
-      <c r="T48" s="38" t="inlineStr">
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>TESTES</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>TESTE — Lançar Bateria: preencher acertos/erros, selecionar fonte/matéria, salvar e confirmar no histórico</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Peso por fonte correto?</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
+        </is>
+      </c>
+      <c r="T55" s="84" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U48" s="41" t="inlineStr">
-        <is>
-          <t>Pesos lidos do ConfigSistema. Default: W1=0.35 W2=0.30 W3=0.20 W4=0.15</t>
-        </is>
-      </c>
-      <c r="V48" s="1" t="n"/>
-    </row>
-    <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="1" t="n"/>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C49" s="37" t="inlineStr">
-        <is>
-          <t>Decay λ por categoria: Legislação=0.03 / RL=0.08 / outros=0.05</t>
-        </is>
-      </c>
-      <c r="D49" s="45" t="inlineStr">
-        <is>
-          <t>L-03</t>
-        </is>
-      </c>
-      <c r="E49" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
-        </is>
-      </c>
-      <c r="F49" s="40" t="inlineStr"/>
-      <c r="G49" s="40" t="inlineStr"/>
-      <c r="H49" s="40" t="inlineStr"/>
-      <c r="I49" s="40" t="inlineStr"/>
-      <c r="J49" s="40" t="inlineStr"/>
-      <c r="K49" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="L49" s="40" t="inlineStr"/>
-      <c r="M49" s="40" t="inlineStr"/>
-      <c r="N49" s="40" t="inlineStr"/>
-      <c r="O49" s="40" t="inlineStr"/>
-      <c r="P49" s="40" t="inlineStr"/>
-      <c r="Q49" s="40" t="inlineStr"/>
-      <c r="R49" s="40" t="inlineStr"/>
-      <c r="S49" s="40" t="inlineStr"/>
-      <c r="T49" s="38" t="inlineStr">
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>TESTES</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>TESTE — Registrar Erros Críticos: registrar 2 erros, verificar listagem</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>status=pendente por padrão</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
+        </is>
+      </c>
+      <c r="T56" s="84" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U49" s="41" t="inlineStr">
-        <is>
-          <t>λ individual por aluno/tópico virá do FSRS na F-06 usando os campos já no banco</t>
-        </is>
-      </c>
-      <c r="V49" s="1" t="n"/>
-    </row>
-    <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="1" t="n"/>
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C50" s="37" t="inlineStr">
-        <is>
-          <t>Fator de erros críticos no score (W4)</t>
-        </is>
-      </c>
-      <c r="D50" s="45" t="inlineStr">
-        <is>
-          <t>L-08</t>
-        </is>
-      </c>
-      <c r="E50" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
-        </is>
-      </c>
-      <c r="F50" s="40" t="inlineStr"/>
-      <c r="G50" s="40" t="inlineStr"/>
-      <c r="H50" s="40" t="inlineStr"/>
-      <c r="I50" s="40" t="inlineStr"/>
-      <c r="J50" s="40" t="inlineStr"/>
-      <c r="K50" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="L50" s="40" t="inlineStr"/>
-      <c r="M50" s="40" t="inlineStr"/>
-      <c r="N50" s="40" t="inlineStr"/>
-      <c r="O50" s="40" t="inlineStr"/>
-      <c r="P50" s="40" t="inlineStr"/>
-      <c r="Q50" s="40" t="inlineStr"/>
-      <c r="R50" s="40" t="inlineStr"/>
-      <c r="S50" s="40" t="inlineStr"/>
-      <c r="T50" s="38" t="inlineStr">
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>TESTES</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>TESTE — Erros Críticos: filtrar por status, alterar status de pendente → resolvido</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Filtro funciona?</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
+        </is>
+      </c>
+      <c r="T57" s="84" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U50" s="41" t="inlineStr"/>
-      <c r="V50" s="1" t="n"/>
-    </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="1" t="n"/>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C51" s="37" t="inlineStr">
-        <is>
-          <t>GET /agenda — top-5 com breakdown visível do score</t>
-        </is>
-      </c>
-      <c r="D51" s="45" t="inlineStr">
-        <is>
-          <t>L-06</t>
-        </is>
-      </c>
-      <c r="E51" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
-        </is>
-      </c>
-      <c r="F51" s="40" t="inlineStr"/>
-      <c r="G51" s="40" t="inlineStr"/>
-      <c r="H51" s="40" t="inlineStr"/>
-      <c r="I51" s="40" t="inlineStr"/>
-      <c r="J51" s="40" t="inlineStr"/>
-      <c r="K51" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="L51" s="40" t="inlineStr"/>
-      <c r="M51" s="40" t="inlineStr"/>
-      <c r="N51" s="40" t="inlineStr"/>
-      <c r="O51" s="40" t="inlineStr"/>
-      <c r="P51" s="40" t="inlineStr"/>
-      <c r="Q51" s="40" t="inlineStr"/>
-      <c r="R51" s="40" t="inlineStr"/>
-      <c r="S51" s="40" t="inlineStr"/>
-      <c r="T51" s="38" t="inlineStr">
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>TESTES</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>TESTE — Histórico: lista de baterias aparece com paginação, filtro por data/matéria</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Ordenação correta?</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
+        </is>
+      </c>
+      <c r="T58" s="84" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U51" s="41" t="inlineStr">
-        <is>
-          <t>Decompõe: urgência, lacuna, peso, erros — L-06</t>
-        </is>
-      </c>
-      <c r="V51" s="1" t="n"/>
-    </row>
-    <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="1" t="n"/>
-      <c r="B52" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C52" s="37" t="inlineStr">
-        <is>
-          <t>Celery + Redis: recálculo assíncrono após cada input</t>
-        </is>
-      </c>
-      <c r="D52" s="38" t="inlineStr"/>
-      <c r="E52" s="38" t="inlineStr">
-        <is>
-          <t>⚙️ Config</t>
-        </is>
-      </c>
-      <c r="F52" s="40" t="inlineStr"/>
-      <c r="G52" s="40" t="inlineStr"/>
-      <c r="H52" s="40" t="inlineStr"/>
-      <c r="I52" s="40" t="inlineStr"/>
-      <c r="J52" s="40" t="inlineStr"/>
-      <c r="K52" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="L52" s="40" t="inlineStr"/>
-      <c r="M52" s="40" t="inlineStr"/>
-      <c r="N52" s="40" t="inlineStr"/>
-      <c r="O52" s="40" t="inlineStr"/>
-      <c r="P52" s="40" t="inlineStr"/>
-      <c r="Q52" s="40" t="inlineStr"/>
-      <c r="R52" s="40" t="inlineStr"/>
-      <c r="S52" s="40" t="inlineStr"/>
-      <c r="T52" s="38" t="inlineStr">
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>TESTES</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>TESTE — Análise de Erros: gráfico de padrões carrega sem erro</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Dados do banco</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
+        </is>
+      </c>
+      <c r="T59" s="84" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U52" s="41" t="inlineStr"/>
-      <c r="V52" s="1" t="n"/>
-    </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="1" t="n"/>
-      <c r="B53" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C53" s="37" t="inlineStr">
-        <is>
-          <t>services/arvore_generator.py — prompt: caso concreto ANTES do conceito</t>
-        </is>
-      </c>
-      <c r="D53" s="45" t="inlineStr">
-        <is>
-          <t>L-05</t>
-        </is>
-      </c>
-      <c r="E53" s="60" t="inlineStr">
-        <is>
-          <t>🧠 IA</t>
-        </is>
-      </c>
-      <c r="F53" s="40" t="inlineStr"/>
-      <c r="G53" s="40" t="inlineStr"/>
-      <c r="H53" s="40" t="inlineStr"/>
-      <c r="I53" s="40" t="inlineStr"/>
-      <c r="J53" s="40" t="inlineStr"/>
-      <c r="K53" s="40" t="inlineStr"/>
-      <c r="L53" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="M53" s="40" t="inlineStr"/>
-      <c r="N53" s="40" t="inlineStr"/>
-      <c r="O53" s="40" t="inlineStr"/>
-      <c r="P53" s="40" t="inlineStr"/>
-      <c r="Q53" s="40" t="inlineStr"/>
-      <c r="R53" s="40" t="inlineStr"/>
-      <c r="S53" s="40" t="inlineStr"/>
-      <c r="T53" s="38" t="inlineStr">
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>TESTES</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>TESTE — Evolução Mensal: gráfico de curva de mastery aparece</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Escala de tempo correta?</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
+        </is>
+      </c>
+      <c r="T60" s="84" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U53" s="41" t="inlineStr">
-        <is>
-          <t>Estrutura: caso_concreto→conceito→por_quê→quando→distinção. Van Merriënboer 1997.</t>
-        </is>
-      </c>
-      <c r="V53" s="1" t="n"/>
-    </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="1" t="n"/>
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C54" s="37" t="inlineStr">
-        <is>
-          <t>services/edital_parser.py — extrai tópicos/pesos do PDF</t>
-        </is>
-      </c>
-      <c r="D54" s="38" t="inlineStr"/>
-      <c r="E54" s="60" t="inlineStr">
-        <is>
-          <t>🧠 IA</t>
-        </is>
-      </c>
-      <c r="F54" s="40" t="inlineStr"/>
-      <c r="G54" s="40" t="inlineStr"/>
-      <c r="H54" s="40" t="inlineStr"/>
-      <c r="I54" s="40" t="inlineStr"/>
-      <c r="J54" s="40" t="inlineStr"/>
-      <c r="K54" s="40" t="inlineStr"/>
-      <c r="L54" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="M54" s="40" t="inlineStr"/>
-      <c r="N54" s="40" t="inlineStr"/>
-      <c r="O54" s="40" t="inlineStr"/>
-      <c r="P54" s="40" t="inlineStr"/>
-      <c r="Q54" s="40" t="inlineStr"/>
-      <c r="R54" s="40" t="inlineStr"/>
-      <c r="S54" s="40" t="inlineStr"/>
-      <c r="T54" s="38" t="inlineStr">
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>TESTES</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>TESTE — Navegação Sidebar: todos os botões navegam para a tela correta, sem erro de rota</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Nenhuma tela quebrada</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
+        </is>
+      </c>
+      <c r="T61" s="84" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U54" s="41" t="inlineStr">
-        <is>
-          <t>Classifica: explicito/implicito/complementar</t>
-        </is>
-      </c>
-      <c r="V54" s="1" t="n"/>
-    </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="1" t="n"/>
-      <c r="B55" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C55" s="37" t="inlineStr">
-        <is>
-          <t>services/session_generator.py — sessões por tópico com desbloqueio cascata</t>
-        </is>
-      </c>
-      <c r="D55" s="46" t="inlineStr">
-        <is>
-          <t>D-14</t>
-        </is>
-      </c>
-      <c r="E55" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
-        </is>
-      </c>
-      <c r="F55" s="40" t="inlineStr"/>
-      <c r="G55" s="40" t="inlineStr"/>
-      <c r="H55" s="40" t="inlineStr"/>
-      <c r="I55" s="40" t="inlineStr"/>
-      <c r="J55" s="40" t="inlineStr"/>
-      <c r="K55" s="40" t="inlineStr"/>
-      <c r="L55" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="M55" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="N55" s="40" t="inlineStr"/>
-      <c r="O55" s="40" t="inlineStr"/>
-      <c r="P55" s="40" t="inlineStr"/>
-      <c r="Q55" s="40" t="inlineStr"/>
-      <c r="R55" s="40" t="inlineStr"/>
-      <c r="S55" s="40" t="inlineStr"/>
-      <c r="T55" s="38" t="inlineStr">
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>TESTES</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>TESTE — Layout geral: revisar todas as telas em resolução 1366x768 (notebook padrão), ajustar o que estiver cortado ou feio</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Aprovação visual final</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
+        </is>
+      </c>
+      <c r="T62" s="84" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U55" s="41" t="inlineStr">
-        <is>
-          <t>Alto(≥0.7)=4 sessões / Médio(0.3-0.69)=3 / Complementar(&lt;0.3)=2. Tipos: teoria_pdf, exercicios, video, flashcard_texto</t>
-        </is>
-      </c>
-      <c r="V55" s="1" t="n"/>
-    </row>
-    <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="1" t="n"/>
-      <c r="B56" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C56" s="37" t="inlineStr">
-        <is>
-          <t>Tipo de questão por momento: primeiro_contato=70% conceito / revisao=70% elaborativo</t>
-        </is>
-      </c>
-      <c r="D56" s="38" t="inlineStr"/>
-      <c r="E56" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
-        </is>
-      </c>
-      <c r="F56" s="40" t="inlineStr"/>
-      <c r="G56" s="40" t="inlineStr"/>
-      <c r="H56" s="40" t="inlineStr"/>
-      <c r="I56" s="40" t="inlineStr"/>
-      <c r="J56" s="40" t="inlineStr"/>
-      <c r="K56" s="40" t="inlineStr"/>
-      <c r="L56" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="M56" s="40" t="inlineStr"/>
-      <c r="N56" s="40" t="inlineStr"/>
-      <c r="O56" s="40" t="inlineStr"/>
-      <c r="P56" s="40" t="inlineStr"/>
-      <c r="Q56" s="40" t="inlineStr"/>
-      <c r="R56" s="40" t="inlineStr"/>
-      <c r="S56" s="40" t="inlineStr"/>
-      <c r="T56" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
-        </is>
-      </c>
-      <c r="U56" s="41" t="inlineStr">
-        <is>
-          <t>Woloshyn 1992: elaboração funciona melhor com conhecimento prévio</t>
-        </is>
-      </c>
-      <c r="V56" s="1" t="n"/>
-    </row>
-    <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="1" t="n"/>
-      <c r="B57" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C57" s="37" t="inlineStr">
-        <is>
-          <t>Desbloqueio visual de sessões — sessão aparece trancada até pré-req concluído</t>
-        </is>
-      </c>
-      <c r="D57" s="47" t="inlineStr">
-        <is>
-          <t>UX-01</t>
-        </is>
-      </c>
-      <c r="E57" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
-        </is>
-      </c>
-      <c r="F57" s="40" t="inlineStr"/>
-      <c r="G57" s="40" t="inlineStr"/>
-      <c r="H57" s="40" t="inlineStr"/>
-      <c r="I57" s="40" t="inlineStr"/>
-      <c r="J57" s="40" t="inlineStr"/>
-      <c r="K57" s="40" t="inlineStr"/>
-      <c r="L57" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="M57" s="40" t="inlineStr"/>
-      <c r="N57" s="40" t="inlineStr"/>
-      <c r="O57" s="40" t="inlineStr"/>
-      <c r="P57" s="40" t="inlineStr"/>
-      <c r="Q57" s="40" t="inlineStr"/>
-      <c r="R57" s="40" t="inlineStr"/>
-      <c r="S57" s="40" t="inlineStr"/>
-      <c r="T57" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
-        </is>
-      </c>
-      <c r="U57" s="41" t="inlineStr">
-        <is>
-          <t>Zeigarnik effect: tarefas incompletas criam tensão que motiva conclusão</t>
-        </is>
-      </c>
-      <c r="V57" s="1" t="n"/>
-    </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="1" t="n"/>
-      <c r="B58" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C58" s="37" t="inlineStr">
-        <is>
-          <t>Agendamento revisão: ≥80%=15d / 60-79%=7d / 40-59%=3d / &lt;40%=1d</t>
-        </is>
-      </c>
-      <c r="D58" s="45" t="inlineStr">
-        <is>
-          <t>L-03</t>
-        </is>
-      </c>
-      <c r="E58" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
-        </is>
-      </c>
-      <c r="F58" s="40" t="inlineStr"/>
-      <c r="G58" s="40" t="inlineStr"/>
-      <c r="H58" s="40" t="inlineStr"/>
-      <c r="I58" s="40" t="inlineStr"/>
-      <c r="J58" s="40" t="inlineStr"/>
-      <c r="K58" s="40" t="inlineStr"/>
-      <c r="L58" s="40" t="inlineStr"/>
-      <c r="M58" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="N58" s="40" t="inlineStr"/>
-      <c r="O58" s="40" t="inlineStr"/>
-      <c r="P58" s="40" t="inlineStr"/>
-      <c r="Q58" s="40" t="inlineStr"/>
-      <c r="R58" s="40" t="inlineStr"/>
-      <c r="S58" s="40" t="inlineStr"/>
-      <c r="T58" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
-        </is>
-      </c>
-      <c r="U58" s="41" t="inlineStr"/>
-      <c r="V58" s="1" t="n"/>
-    </row>
-    <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="1" t="n"/>
-      <c r="B59" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C59" s="37" t="inlineStr">
-        <is>
-          <t>Feedback de tempo real: duracao_real_min após cada sessão</t>
-        </is>
-      </c>
-      <c r="D59" s="55" t="inlineStr">
-        <is>
-          <t>BETA</t>
-        </is>
-      </c>
-      <c r="E59" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
-        </is>
-      </c>
-      <c r="F59" s="40" t="inlineStr"/>
-      <c r="G59" s="40" t="inlineStr"/>
-      <c r="H59" s="40" t="inlineStr"/>
-      <c r="I59" s="40" t="inlineStr"/>
-      <c r="J59" s="40" t="inlineStr"/>
-      <c r="K59" s="40" t="inlineStr"/>
-      <c r="L59" s="40" t="inlineStr"/>
-      <c r="M59" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="N59" s="40" t="inlineStr"/>
-      <c r="O59" s="40" t="inlineStr"/>
-      <c r="P59" s="40" t="inlineStr"/>
-      <c r="Q59" s="40" t="inlineStr"/>
-      <c r="R59" s="40" t="inlineStr"/>
-      <c r="S59" s="40" t="inlineStr"/>
-      <c r="T59" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
-        </is>
-      </c>
-      <c r="U59" s="41" t="inlineStr">
-        <is>
-          <t>Pergunta única: Muito pouco/Adequado/Precisei de mais. Calibra estimativas individuais.</t>
-        </is>
-      </c>
-      <c r="V59" s="1" t="n"/>
-    </row>
-    <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="1" t="n"/>
-      <c r="B60" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C60" s="37" t="inlineStr">
-        <is>
-          <t>services/viabilidade.py — horas disponíveis vs carga total</t>
-        </is>
-      </c>
-      <c r="D60" s="38" t="inlineStr"/>
-      <c r="E60" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
-        </is>
-      </c>
-      <c r="F60" s="40" t="inlineStr"/>
-      <c r="G60" s="40" t="inlineStr"/>
-      <c r="H60" s="40" t="inlineStr"/>
-      <c r="I60" s="40" t="inlineStr"/>
-      <c r="J60" s="40" t="inlineStr"/>
-      <c r="K60" s="40" t="inlineStr"/>
-      <c r="L60" s="40" t="inlineStr"/>
-      <c r="M60" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="N60" s="40" t="inlineStr"/>
-      <c r="O60" s="40" t="inlineStr"/>
-      <c r="P60" s="40" t="inlineStr"/>
-      <c r="Q60" s="40" t="inlineStr"/>
-      <c r="R60" s="40" t="inlineStr"/>
-      <c r="S60" s="40" t="inlineStr"/>
-      <c r="T60" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
-        </is>
-      </c>
-      <c r="U60" s="41" t="inlineStr">
-        <is>
-          <t>Sugere remover complementares se inviável</t>
-        </is>
-      </c>
-      <c r="V60" s="1" t="n"/>
-    </row>
-    <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="1" t="n"/>
-      <c r="B61" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C61" s="37" t="inlineStr">
-        <is>
-          <t>services/modo_estudo.py — pré/pós edital + sugestão de paralelização</t>
-        </is>
-      </c>
-      <c r="D61" s="38" t="inlineStr"/>
-      <c r="E61" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
-        </is>
-      </c>
-      <c r="F61" s="40" t="inlineStr"/>
-      <c r="G61" s="40" t="inlineStr"/>
-      <c r="H61" s="40" t="inlineStr"/>
-      <c r="I61" s="40" t="inlineStr"/>
-      <c r="J61" s="40" t="inlineStr"/>
-      <c r="K61" s="40" t="inlineStr"/>
-      <c r="L61" s="40" t="inlineStr"/>
-      <c r="M61" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="N61" s="40" t="inlineStr"/>
-      <c r="O61" s="40" t="inlineStr"/>
-      <c r="P61" s="40" t="inlineStr"/>
-      <c r="Q61" s="40" t="inlineStr"/>
-      <c r="R61" s="40" t="inlineStr"/>
-      <c r="S61" s="40" t="inlineStr"/>
-      <c r="T61" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
-        </is>
-      </c>
-      <c r="U61" s="41" t="inlineStr">
-        <is>
-          <t>Semi-automático: sistema sugere, aluno confirma</t>
-        </is>
-      </c>
-      <c r="V61" s="1" t="n"/>
-    </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="1" t="n"/>
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C62" s="37" t="inlineStr">
-        <is>
-          <t>services/diff_edital.py — diff pré vs pós edital</t>
-        </is>
-      </c>
-      <c r="D62" s="38" t="inlineStr"/>
-      <c r="E62" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
-        </is>
-      </c>
-      <c r="F62" s="40" t="inlineStr"/>
-      <c r="G62" s="40" t="inlineStr"/>
-      <c r="H62" s="40" t="inlineStr"/>
-      <c r="I62" s="40" t="inlineStr"/>
-      <c r="J62" s="40" t="inlineStr"/>
-      <c r="K62" s="40" t="inlineStr"/>
-      <c r="L62" s="40" t="inlineStr"/>
-      <c r="M62" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="N62" s="40" t="inlineStr"/>
-      <c r="O62" s="40" t="inlineStr"/>
-      <c r="P62" s="40" t="inlineStr"/>
-      <c r="Q62" s="40" t="inlineStr"/>
-      <c r="R62" s="40" t="inlineStr"/>
-      <c r="S62" s="40" t="inlineStr"/>
-      <c r="T62" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
-        </is>
-      </c>
-      <c r="U62" s="41" t="inlineStr">
-        <is>
-          <t>Gera: novos[], removidos[], peso_alterado[]</t>
-        </is>
-      </c>
-      <c r="V62" s="1" t="n"/>
     </row>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="1" t="n"/>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C63" s="37" t="inlineStr">
-        <is>
-          <t>services/meta_semanal.py — gerar_nova_janela() + fechar_janela()</t>
-        </is>
-      </c>
-      <c r="D63" s="47" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="E63" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
-        </is>
-      </c>
-      <c r="F63" s="40" t="inlineStr"/>
-      <c r="G63" s="40" t="inlineStr"/>
-      <c r="H63" s="40" t="inlineStr"/>
-      <c r="I63" s="40" t="inlineStr"/>
-      <c r="J63" s="40" t="inlineStr"/>
-      <c r="K63" s="40" t="inlineStr"/>
-      <c r="L63" s="40" t="inlineStr"/>
-      <c r="M63" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="N63" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="O63" s="40" t="inlineStr"/>
-      <c r="P63" s="40" t="inlineStr"/>
-      <c r="Q63" s="40" t="inlineStr"/>
-      <c r="R63" s="40" t="inlineStr"/>
-      <c r="S63" s="40" t="inlineStr"/>
-      <c r="T63" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
-        </is>
-      </c>
-      <c r="U63" s="41" t="inlineStr">
-        <is>
-          <t>conservador=85%/moderado=75%/agressivo=65%. Expiração seletiva. Nunca cresce por atraso.</t>
-        </is>
-      </c>
+      <c r="B63" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ◆  DEPLOY BETA — Railway   ·   Semana 5 (fim)</t>
+        </is>
+      </c>
+      <c r="C63" s="78" t="n"/>
+      <c r="D63" s="78" t="n"/>
+      <c r="E63" s="78" t="n"/>
+      <c r="F63" s="78" t="n"/>
+      <c r="G63" s="78" t="n"/>
+      <c r="H63" s="78" t="n"/>
+      <c r="I63" s="78" t="n"/>
+      <c r="J63" s="78" t="n"/>
+      <c r="K63" s="78" t="n"/>
+      <c r="L63" s="78" t="n"/>
+      <c r="M63" s="78" t="n"/>
+      <c r="N63" s="78" t="n"/>
+      <c r="O63" s="78" t="n"/>
+      <c r="P63" s="78" t="n"/>
+      <c r="Q63" s="78" t="n"/>
+      <c r="R63" s="78" t="n"/>
+      <c r="S63" s="78" t="n"/>
+      <c r="T63" s="78" t="n"/>
+      <c r="U63" s="79" t="n"/>
       <c r="V63" s="1" t="n"/>
     </row>
     <row r="64" ht="24" customHeight="1">
       <c r="A64" s="1" t="n"/>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>DEPLOY</t>
         </is>
       </c>
       <c r="C64" s="37" t="inlineStr">
         <is>
-          <t>GET /meta/semana-atual + GET /admin/meta/{id}/historico</t>
-        </is>
-      </c>
-      <c r="D64" s="47" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="E64" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
+          <t>Criar Procfile + railway.toml</t>
+        </is>
+      </c>
+      <c r="D64" s="38" t="inlineStr"/>
+      <c r="E64" s="38" t="inlineStr">
+        <is>
+          <t>⚙️ Config</t>
         </is>
       </c>
       <c r="F64" s="40" t="inlineStr"/>
       <c r="G64" s="40" t="inlineStr"/>
       <c r="H64" s="40" t="inlineStr"/>
       <c r="I64" s="40" t="inlineStr"/>
-      <c r="J64" s="40" t="inlineStr"/>
+      <c r="J64" s="57" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="K64" s="40" t="inlineStr"/>
       <c r="L64" s="40" t="inlineStr"/>
       <c r="M64" s="40" t="inlineStr"/>
-      <c r="N64" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="N64" s="40" t="inlineStr"/>
       <c r="O64" s="40" t="inlineStr"/>
       <c r="P64" s="40" t="inlineStr"/>
       <c r="Q64" s="40" t="inlineStr"/>
@@ -5970,46 +5501,42 @@
       </c>
       <c r="U64" s="41" t="inlineStr">
         <is>
-          <t>Déficit visível só admin/mentor</t>
+          <t>web: uvicorn app.main:app --host 0.0.0.0 --port $PORT</t>
         </is>
       </c>
       <c r="V64" s="1" t="n"/>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="1" t="n"/>
-      <c r="B65" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>DEPLOY</t>
         </is>
       </c>
       <c r="C65" s="37" t="inlineStr">
         <is>
-          <t>Modo Revisão Final (D-13): ativa 14 dias antes, congela novos tópicos</t>
-        </is>
-      </c>
-      <c r="D65" s="61" t="inlineStr">
-        <is>
-          <t>D-13</t>
-        </is>
-      </c>
-      <c r="E65" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
+          <t>Criar conta Railway + conectar GitHub + Plugin PostgreSQL</t>
+        </is>
+      </c>
+      <c r="D65" s="38" t="inlineStr"/>
+      <c r="E65" s="38" t="inlineStr">
+        <is>
+          <t>⚙️ Config</t>
         </is>
       </c>
       <c r="F65" s="40" t="inlineStr"/>
       <c r="G65" s="40" t="inlineStr"/>
       <c r="H65" s="40" t="inlineStr"/>
       <c r="I65" s="40" t="inlineStr"/>
-      <c r="J65" s="40" t="inlineStr"/>
+      <c r="J65" s="57" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="K65" s="40" t="inlineStr"/>
       <c r="L65" s="40" t="inlineStr"/>
       <c r="M65" s="40" t="inlineStr"/>
-      <c r="N65" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="N65" s="40" t="inlineStr"/>
       <c r="O65" s="40" t="inlineStr"/>
       <c r="P65" s="40" t="inlineStr"/>
       <c r="Q65" s="40" t="inlineStr"/>
@@ -6020,42 +5547,38 @@
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U65" s="41" t="inlineStr">
-        <is>
-          <t>Ordena: menor acerto × maior peso × maior decay</t>
-        </is>
-      </c>
+      <c r="U65" s="41" t="inlineStr"/>
       <c r="V65" s="1" t="n"/>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="1" t="n"/>
-      <c r="B66" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>DEPLOY</t>
         </is>
       </c>
       <c r="C66" s="37" t="inlineStr">
         <is>
-          <t>GET /cronograma/gerar + POST /edital/upload + GET /edital/diff</t>
+          <t>railway run alembic upgrade head</t>
         </is>
       </c>
       <c r="D66" s="38" t="inlineStr"/>
-      <c r="E66" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
+      <c r="E66" s="38" t="inlineStr">
+        <is>
+          <t>💻 Terminal</t>
         </is>
       </c>
       <c r="F66" s="40" t="inlineStr"/>
       <c r="G66" s="40" t="inlineStr"/>
       <c r="H66" s="40" t="inlineStr"/>
       <c r="I66" s="40" t="inlineStr"/>
-      <c r="J66" s="40" t="inlineStr"/>
+      <c r="J66" s="57" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="K66" s="40" t="inlineStr"/>
-      <c r="L66" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="L66" s="40" t="inlineStr"/>
       <c r="M66" s="40" t="inlineStr"/>
       <c r="N66" s="40" t="inlineStr"/>
       <c r="O66" s="40" t="inlineStr"/>
@@ -6073,34 +5596,34 @@
     </row>
     <row r="67" ht="24" customHeight="1">
       <c r="A67" s="1" t="n"/>
-      <c r="B67" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>DEPLOY</t>
         </is>
       </c>
       <c r="C67" s="37" t="inlineStr">
         <is>
-          <t>PATCH /cronograma/paralelizar</t>
+          <t>Criar contas beta testers — script criar_usuario.py</t>
         </is>
       </c>
       <c r="D67" s="38" t="inlineStr"/>
-      <c r="E67" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
+      <c r="E67" s="38" t="inlineStr">
+        <is>
+          <t>⚙️ Config</t>
         </is>
       </c>
       <c r="F67" s="40" t="inlineStr"/>
       <c r="G67" s="40" t="inlineStr"/>
       <c r="H67" s="40" t="inlineStr"/>
       <c r="I67" s="40" t="inlineStr"/>
-      <c r="J67" s="40" t="inlineStr"/>
+      <c r="J67" s="57" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="K67" s="40" t="inlineStr"/>
       <c r="L67" s="40" t="inlineStr"/>
-      <c r="M67" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="M67" s="40" t="inlineStr"/>
       <c r="N67" s="40" t="inlineStr"/>
       <c r="O67" s="40" t="inlineStr"/>
       <c r="P67" s="40" t="inlineStr"/>
@@ -6112,48 +5635,40 @@
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U67" s="41" t="inlineStr">
-        <is>
-          <t>Aluno confirma paralelização sugerida</t>
-        </is>
-      </c>
+      <c r="U67" s="41" t="inlineStr"/>
       <c r="V67" s="1" t="n"/>
     </row>
     <row r="68" ht="24" customHeight="1">
       <c r="A68" s="1" t="n"/>
-      <c r="B68" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>DEPLOY</t>
         </is>
       </c>
       <c r="C68" s="37" t="inlineStr">
         <is>
-          <t>Regra interleaving: max 2 sessões da mesma matéria por dia</t>
-        </is>
-      </c>
-      <c r="D68" s="45" t="inlineStr">
-        <is>
-          <t>L-03</t>
-        </is>
-      </c>
-      <c r="E68" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
+          <t>Validar fluxo online com dados reais</t>
+        </is>
+      </c>
+      <c r="D68" s="38" t="inlineStr"/>
+      <c r="E68" s="42" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
         </is>
       </c>
       <c r="F68" s="40" t="inlineStr"/>
       <c r="G68" s="40" t="inlineStr"/>
       <c r="H68" s="40" t="inlineStr"/>
       <c r="I68" s="40" t="inlineStr"/>
-      <c r="J68" s="40" t="inlineStr"/>
+      <c r="J68" s="57" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="K68" s="40" t="inlineStr"/>
       <c r="L68" s="40" t="inlineStr"/>
       <c r="M68" s="40" t="inlineStr"/>
-      <c r="N68" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="N68" s="40" t="inlineStr"/>
       <c r="O68" s="40" t="inlineStr"/>
       <c r="P68" s="40" t="inlineStr"/>
       <c r="Q68" s="40" t="inlineStr"/>
@@ -6166,60 +5681,44 @@
       </c>
       <c r="U68" s="41" t="inlineStr">
         <is>
-          <t>Rohrer &amp; Taylor 2007</t>
+          <t>Marco: URL pública funcionando</t>
         </is>
       </c>
       <c r="V68" s="1" t="n"/>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="1" t="n"/>
-      <c r="B69" s="13" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C69" s="37" t="inlineStr">
-        <is>
-          <t>Testes unitários pytest — algoritmo de priorização</t>
-        </is>
-      </c>
-      <c r="D69" s="38" t="inlineStr"/>
-      <c r="E69" s="42" t="inlineStr">
-        <is>
-          <t>✅ Teste</t>
-        </is>
-      </c>
-      <c r="F69" s="40" t="inlineStr"/>
-      <c r="G69" s="40" t="inlineStr"/>
-      <c r="H69" s="40" t="inlineStr"/>
-      <c r="I69" s="40" t="inlineStr"/>
-      <c r="J69" s="40" t="inlineStr"/>
-      <c r="K69" s="40" t="inlineStr"/>
-      <c r="L69" s="40" t="inlineStr"/>
-      <c r="M69" s="40" t="inlineStr"/>
-      <c r="N69" s="59" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="O69" s="40" t="inlineStr"/>
-      <c r="P69" s="40" t="inlineStr"/>
-      <c r="Q69" s="40" t="inlineStr"/>
-      <c r="R69" s="40" t="inlineStr"/>
-      <c r="S69" s="40" t="inlineStr"/>
-      <c r="T69" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
-        </is>
-      </c>
-      <c r="U69" s="41" t="inlineStr"/>
+      <c r="B69" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ◆  FASE 3 — Algoritmo de Priorização + Cronograma Inteligente   ·   Semanas 6–9</t>
+        </is>
+      </c>
+      <c r="C69" s="78" t="n"/>
+      <c r="D69" s="78" t="n"/>
+      <c r="E69" s="78" t="n"/>
+      <c r="F69" s="78" t="n"/>
+      <c r="G69" s="78" t="n"/>
+      <c r="H69" s="78" t="n"/>
+      <c r="I69" s="78" t="n"/>
+      <c r="J69" s="78" t="n"/>
+      <c r="K69" s="78" t="n"/>
+      <c r="L69" s="78" t="n"/>
+      <c r="M69" s="78" t="n"/>
+      <c r="N69" s="78" t="n"/>
+      <c r="O69" s="78" t="n"/>
+      <c r="P69" s="78" t="n"/>
+      <c r="Q69" s="78" t="n"/>
+      <c r="R69" s="78" t="n"/>
+      <c r="S69" s="78" t="n"/>
+      <c r="T69" s="78" t="n"/>
+      <c r="U69" s="79" t="n"/>
       <c r="V69" s="1" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="1" t="n"/>
-      <c r="B70" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ◆  FASE 4 — Quiz IA + Calibração Adaptativa + Padrão Cognitivo   ·   Semanas 10–12</t>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C70" s="78" t="n"/>
@@ -6245,20 +5744,24 @@
     </row>
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="1" t="n"/>
-      <c r="B71" s="14" t="inlineStr">
-        <is>
-          <t>F-04</t>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C71" s="37" t="inlineStr">
         <is>
-          <t>Camada AIProvider: interface + GeminiProvider + AnthropicProvider</t>
-        </is>
-      </c>
-      <c r="D71" s="38" t="inlineStr"/>
-      <c r="E71" s="60" t="inlineStr">
-        <is>
-          <t>🧠 IA</t>
+          <t>Decay λ por categoria: Legislação=0.03 / RL=0.08 / outros=0.05</t>
+        </is>
+      </c>
+      <c r="D71" s="45" t="inlineStr">
+        <is>
+          <t>L-03</t>
+        </is>
+      </c>
+      <c r="E71" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
         </is>
       </c>
       <c r="F71" s="40" t="inlineStr"/>
@@ -6266,15 +5769,15 @@
       <c r="H71" s="40" t="inlineStr"/>
       <c r="I71" s="40" t="inlineStr"/>
       <c r="J71" s="40" t="inlineStr"/>
-      <c r="K71" s="40" t="inlineStr"/>
+      <c r="K71" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="L71" s="40" t="inlineStr"/>
       <c r="M71" s="40" t="inlineStr"/>
       <c r="N71" s="40" t="inlineStr"/>
-      <c r="O71" s="63" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="O71" s="40" t="inlineStr"/>
       <c r="P71" s="40" t="inlineStr"/>
       <c r="Q71" s="40" t="inlineStr"/>
       <c r="R71" s="40" t="inlineStr"/>
@@ -6286,31 +5789,31 @@
       </c>
       <c r="U71" s="41" t="inlineStr">
         <is>
-          <t>Admin troca via ConfigSistema sem redeploy</t>
+          <t>λ individual por aluno/tópico virá do FSRS na F-06 usando os campos já no banco</t>
         </is>
       </c>
       <c r="V71" s="1" t="n"/>
     </row>
     <row r="72" ht="24" customHeight="1">
       <c r="A72" s="1" t="n"/>
-      <c r="B72" s="14" t="inlineStr">
-        <is>
-          <t>F-04</t>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C72" s="37" t="inlineStr">
         <is>
-          <t>quiz_generator.py — parâmetro momento (primeiro_contato / revisao)</t>
+          <t>Fator de erros críticos no score (W4)</t>
         </is>
       </c>
       <c r="D72" s="45" t="inlineStr">
         <is>
-          <t>L-02</t>
-        </is>
-      </c>
-      <c r="E72" s="60" t="inlineStr">
-        <is>
-          <t>🧠 IA</t>
+          <t>L-08</t>
+        </is>
+      </c>
+      <c r="E72" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
         </is>
       </c>
       <c r="F72" s="40" t="inlineStr"/>
@@ -6318,15 +5821,15 @@
       <c r="H72" s="40" t="inlineStr"/>
       <c r="I72" s="40" t="inlineStr"/>
       <c r="J72" s="40" t="inlineStr"/>
-      <c r="K72" s="40" t="inlineStr"/>
+      <c r="K72" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="L72" s="40" t="inlineStr"/>
       <c r="M72" s="40" t="inlineStr"/>
       <c r="N72" s="40" t="inlineStr"/>
-      <c r="O72" s="63" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="O72" s="40" t="inlineStr"/>
       <c r="P72" s="40" t="inlineStr"/>
       <c r="Q72" s="40" t="inlineStr"/>
       <c r="R72" s="40" t="inlineStr"/>
@@ -6336,29 +5839,29 @@
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U72" s="41" t="inlineStr">
-        <is>
-          <t>primeiro_contato: 70% conceito puro. revisao: 70% contraste+aplicação+exceção.</t>
-        </is>
-      </c>
+      <c r="U72" s="41" t="inlineStr"/>
       <c r="V72" s="1" t="n"/>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="1" t="n"/>
-      <c r="B73" s="14" t="inlineStr">
-        <is>
-          <t>F-04</t>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C73" s="37" t="inlineStr">
         <is>
-          <t>Anti-alucinação: grounding no material real do aluno</t>
-        </is>
-      </c>
-      <c r="D73" s="38" t="inlineStr"/>
-      <c r="E73" s="60" t="inlineStr">
-        <is>
-          <t>🧠 IA</t>
+          <t>GET /agenda — top-5 com breakdown visível do score</t>
+        </is>
+      </c>
+      <c r="D73" s="45" t="inlineStr">
+        <is>
+          <t>L-06</t>
+        </is>
+      </c>
+      <c r="E73" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
         </is>
       </c>
       <c r="F73" s="40" t="inlineStr"/>
@@ -6366,15 +5869,15 @@
       <c r="H73" s="40" t="inlineStr"/>
       <c r="I73" s="40" t="inlineStr"/>
       <c r="J73" s="40" t="inlineStr"/>
-      <c r="K73" s="40" t="inlineStr"/>
+      <c r="K73" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="L73" s="40" t="inlineStr"/>
       <c r="M73" s="40" t="inlineStr"/>
       <c r="N73" s="40" t="inlineStr"/>
-      <c r="O73" s="63" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="O73" s="40" t="inlineStr"/>
       <c r="P73" s="40" t="inlineStr"/>
       <c r="Q73" s="40" t="inlineStr"/>
       <c r="R73" s="40" t="inlineStr"/>
@@ -6384,29 +5887,29 @@
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U73" s="41" t="inlineStr"/>
+      <c r="U73" s="41" t="inlineStr">
+        <is>
+          <t>Decompõe: urgência, lacuna, peso, erros — L-06</t>
+        </is>
+      </c>
       <c r="V73" s="1" t="n"/>
     </row>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="1" t="n"/>
-      <c r="B74" s="14" t="inlineStr">
-        <is>
-          <t>F-04</t>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C74" s="37" t="inlineStr">
         <is>
-          <t>Quiz focado nos erros críticos pendentes do tópico</t>
-        </is>
-      </c>
-      <c r="D74" s="45" t="inlineStr">
-        <is>
-          <t>L-08</t>
-        </is>
-      </c>
-      <c r="E74" s="60" t="inlineStr">
-        <is>
-          <t>🧠 IA</t>
+          <t>Celery + Redis: recálculo assíncrono após cada input</t>
+        </is>
+      </c>
+      <c r="D74" s="38" t="inlineStr"/>
+      <c r="E74" s="38" t="inlineStr">
+        <is>
+          <t>⚙️ Config</t>
         </is>
       </c>
       <c r="F74" s="40" t="inlineStr"/>
@@ -6414,15 +5917,15 @@
       <c r="H74" s="40" t="inlineStr"/>
       <c r="I74" s="40" t="inlineStr"/>
       <c r="J74" s="40" t="inlineStr"/>
-      <c r="K74" s="40" t="inlineStr"/>
+      <c r="K74" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="L74" s="40" t="inlineStr"/>
       <c r="M74" s="40" t="inlineStr"/>
       <c r="N74" s="40" t="inlineStr"/>
-      <c r="O74" s="63" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="O74" s="40" t="inlineStr"/>
       <c r="P74" s="40" t="inlineStr"/>
       <c r="Q74" s="40" t="inlineStr"/>
       <c r="R74" s="40" t="inlineStr"/>
@@ -6437,24 +5940,24 @@
     </row>
     <row r="75" ht="24" customHeight="1">
       <c r="A75" s="1" t="n"/>
-      <c r="B75" s="14" t="inlineStr">
-        <is>
-          <t>F-04</t>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C75" s="37" t="inlineStr">
         <is>
-          <t>Calibração UX-02: sessão tipo=calibracao, 15q em 3 fases adaptativas</t>
-        </is>
-      </c>
-      <c r="D75" s="48" t="inlineStr">
-        <is>
-          <t>UX-02</t>
-        </is>
-      </c>
-      <c r="E75" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
+          <t>services/arvore_generator.py — prompt: caso concreto ANTES do conceito</t>
+        </is>
+      </c>
+      <c r="D75" s="45" t="inlineStr">
+        <is>
+          <t>L-05</t>
+        </is>
+      </c>
+      <c r="E75" s="60" t="inlineStr">
+        <is>
+          <t>🧠 IA</t>
         </is>
       </c>
       <c r="F75" s="40" t="inlineStr"/>
@@ -6463,19 +5966,15 @@
       <c r="I75" s="40" t="inlineStr"/>
       <c r="J75" s="40" t="inlineStr"/>
       <c r="K75" s="40" t="inlineStr"/>
-      <c r="L75" s="40" t="inlineStr"/>
+      <c r="L75" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="M75" s="40" t="inlineStr"/>
       <c r="N75" s="40" t="inlineStr"/>
-      <c r="O75" s="63" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="P75" s="63" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="O75" s="40" t="inlineStr"/>
+      <c r="P75" s="40" t="inlineStr"/>
       <c r="Q75" s="40" t="inlineStr"/>
       <c r="R75" s="40" t="inlineStr"/>
       <c r="S75" s="40" t="inlineStr"/>
@@ -6486,31 +5985,27 @@
       </c>
       <c r="U75" s="41" t="inlineStr">
         <is>
-          <t>Fase1: 5q âncora no nível do tempo declarado / Fase2: 7q refinamento / Fase3: 3q confirmação</t>
+          <t>Estrutura: caso_concreto→conceito→por_quê→quando→distinção. Van Merriënboer 1997.</t>
         </is>
       </c>
       <c r="V75" s="1" t="n"/>
     </row>
     <row r="76" ht="24" customHeight="1">
       <c r="A76" s="1" t="n"/>
-      <c r="B76" s="14" t="inlineStr">
-        <is>
-          <t>F-04</t>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C76" s="37" t="inlineStr">
         <is>
-          <t>Calibração UX-02: lógica adaptativa — ajusta dificuldade pela resposta anterior</t>
-        </is>
-      </c>
-      <c r="D76" s="48" t="inlineStr">
-        <is>
-          <t>UX-02</t>
-        </is>
-      </c>
-      <c r="E76" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
+          <t>services/edital_parser.py — extrai tópicos/pesos do PDF</t>
+        </is>
+      </c>
+      <c r="D76" s="38" t="inlineStr"/>
+      <c r="E76" s="60" t="inlineStr">
+        <is>
+          <t>🧠 IA</t>
         </is>
       </c>
       <c r="F76" s="40" t="inlineStr"/>
@@ -6519,15 +6014,15 @@
       <c r="I76" s="40" t="inlineStr"/>
       <c r="J76" s="40" t="inlineStr"/>
       <c r="K76" s="40" t="inlineStr"/>
-      <c r="L76" s="40" t="inlineStr"/>
+      <c r="L76" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="M76" s="40" t="inlineStr"/>
       <c r="N76" s="40" t="inlineStr"/>
       <c r="O76" s="40" t="inlineStr"/>
-      <c r="P76" s="63" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="P76" s="40" t="inlineStr"/>
       <c r="Q76" s="40" t="inlineStr"/>
       <c r="R76" s="40" t="inlineStr"/>
       <c r="S76" s="40" t="inlineStr"/>
@@ -6538,26 +6033,26 @@
       </c>
       <c r="U76" s="41" t="inlineStr">
         <is>
-          <t>4-5 acertos=sobe / 2-3=mantém / 0-1=desce</t>
+          <t>Classifica: explicito/implicito/complementar</t>
         </is>
       </c>
       <c r="V76" s="1" t="n"/>
     </row>
     <row r="77" ht="24" customHeight="1">
       <c r="A77" s="1" t="n"/>
-      <c r="B77" s="14" t="inlineStr">
-        <is>
-          <t>F-04</t>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C77" s="37" t="inlineStr">
         <is>
-          <t>Calibração UX-02: fonte=calibracao peso 1.2x — diluído após 3 baterias reais</t>
-        </is>
-      </c>
-      <c r="D77" s="48" t="inlineStr">
-        <is>
-          <t>UX-02</t>
+          <t>services/session_generator.py — sessões por tópico com desbloqueio cascata</t>
+        </is>
+      </c>
+      <c r="D77" s="46" t="inlineStr">
+        <is>
+          <t>D-14</t>
         </is>
       </c>
       <c r="E77" s="52" t="inlineStr">
@@ -6571,15 +6066,19 @@
       <c r="I77" s="40" t="inlineStr"/>
       <c r="J77" s="40" t="inlineStr"/>
       <c r="K77" s="40" t="inlineStr"/>
-      <c r="L77" s="40" t="inlineStr"/>
-      <c r="M77" s="40" t="inlineStr"/>
+      <c r="L77" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="M77" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="N77" s="40" t="inlineStr"/>
       <c r="O77" s="40" t="inlineStr"/>
-      <c r="P77" s="63" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="P77" s="40" t="inlineStr"/>
       <c r="Q77" s="40" t="inlineStr"/>
       <c r="R77" s="40" t="inlineStr"/>
       <c r="S77" s="40" t="inlineStr"/>
@@ -6590,31 +6089,27 @@
       </c>
       <c r="U77" s="41" t="inlineStr">
         <is>
-          <t>Dados reais substituem progressivamente. CAT: van der Linden &amp; Hambleton 1997.</t>
+          <t>Alto(≥0.7)=4 sessões / Médio(0.3-0.69)=3 / Complementar(&lt;0.3)=2. Tipos: teoria_pdf, exercicios, video, flashcard_texto</t>
         </is>
       </c>
       <c r="V77" s="1" t="n"/>
     </row>
     <row r="78" ht="24" customHeight="1">
       <c r="A78" s="1" t="n"/>
-      <c r="B78" s="14" t="inlineStr">
-        <is>
-          <t>F-04</t>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C78" s="37" t="inlineStr">
         <is>
-          <t>Calibração UX-02: UI sem timer + framing de diagnóstico + feedback pós-cal</t>
-        </is>
-      </c>
-      <c r="D78" s="48" t="inlineStr">
-        <is>
-          <t>UX-02</t>
-        </is>
-      </c>
-      <c r="E78" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
+          <t>Tipo de questão por momento: primeiro_contato=70% conceito / revisao=70% elaborativo</t>
+        </is>
+      </c>
+      <c r="D78" s="38" t="inlineStr"/>
+      <c r="E78" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
         </is>
       </c>
       <c r="F78" s="40" t="inlineStr"/>
@@ -6623,15 +6118,15 @@
       <c r="I78" s="40" t="inlineStr"/>
       <c r="J78" s="40" t="inlineStr"/>
       <c r="K78" s="40" t="inlineStr"/>
-      <c r="L78" s="40" t="inlineStr"/>
+      <c r="L78" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="M78" s="40" t="inlineStr"/>
       <c r="N78" s="40" t="inlineStr"/>
       <c r="O78" s="40" t="inlineStr"/>
-      <c r="P78" s="63" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="P78" s="40" t="inlineStr"/>
       <c r="Q78" s="40" t="inlineStr"/>
       <c r="R78" s="40" t="inlineStr"/>
       <c r="S78" s="40" t="inlineStr"/>
@@ -6642,31 +6137,31 @@
       </c>
       <c r="U78" s="41" t="inlineStr">
         <is>
-          <t>'Quanto mais honesto, melhor o plano.' Aluno vê nível detectado + pontos fortes + lacunas</t>
+          <t>Woloshyn 1992: elaboração funciona melhor com conhecimento prévio</t>
         </is>
       </c>
       <c r="V78" s="1" t="n"/>
     </row>
     <row r="79" ht="24" customHeight="1">
       <c r="A79" s="1" t="n"/>
-      <c r="B79" s="14" t="inlineStr">
-        <is>
-          <t>F-04</t>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C79" s="37" t="inlineStr">
         <is>
-          <t>flashcard_generator.py — resposta digitada avaliada por IA</t>
-        </is>
-      </c>
-      <c r="D79" s="46" t="inlineStr">
-        <is>
-          <t>D-14</t>
-        </is>
-      </c>
-      <c r="E79" s="60" t="inlineStr">
-        <is>
-          <t>🧠 IA</t>
+          <t>Desbloqueio visual de sessões — sessão aparece trancada até pré-req concluído</t>
+        </is>
+      </c>
+      <c r="D79" s="47" t="inlineStr">
+        <is>
+          <t>UX-01</t>
+        </is>
+      </c>
+      <c r="E79" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
         </is>
       </c>
       <c r="F79" s="40" t="inlineStr"/>
@@ -6675,15 +6170,15 @@
       <c r="I79" s="40" t="inlineStr"/>
       <c r="J79" s="40" t="inlineStr"/>
       <c r="K79" s="40" t="inlineStr"/>
-      <c r="L79" s="40" t="inlineStr"/>
+      <c r="L79" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="M79" s="40" t="inlineStr"/>
       <c r="N79" s="40" t="inlineStr"/>
       <c r="O79" s="40" t="inlineStr"/>
-      <c r="P79" s="63" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="P79" s="40" t="inlineStr"/>
       <c r="Q79" s="40" t="inlineStr"/>
       <c r="R79" s="40" t="inlineStr"/>
       <c r="S79" s="40" t="inlineStr"/>
@@ -6694,31 +6189,31 @@
       </c>
       <c r="U79" s="41" t="inlineStr">
         <is>
-          <t>Sem STT. Chi 1994: self-explanation effect preservado pela geração ativa. IA verifica conceitos cobertos.</t>
+          <t>Zeigarnik effect: tarefas incompletas criam tensão que motiva conclusão</t>
         </is>
       </c>
       <c r="V79" s="1" t="n"/>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="1" t="n"/>
-      <c r="B80" s="14" t="inlineStr">
-        <is>
-          <t>F-04</t>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C80" s="37" t="inlineStr">
         <is>
-          <t>POST /flashcard/avaliar — IA compara resposta com conceitos esperados</t>
-        </is>
-      </c>
-      <c r="D80" s="46" t="inlineStr">
-        <is>
-          <t>D-14</t>
-        </is>
-      </c>
-      <c r="E80" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
+          <t>Agendamento revisão: ≥80%=15d / 60-79%=7d / 40-59%=3d / &lt;40%=1d</t>
+        </is>
+      </c>
+      <c r="D80" s="45" t="inlineStr">
+        <is>
+          <t>L-03</t>
+        </is>
+      </c>
+      <c r="E80" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
         </is>
       </c>
       <c r="F80" s="40" t="inlineStr"/>
@@ -6728,14 +6223,14 @@
       <c r="J80" s="40" t="inlineStr"/>
       <c r="K80" s="40" t="inlineStr"/>
       <c r="L80" s="40" t="inlineStr"/>
-      <c r="M80" s="40" t="inlineStr"/>
+      <c r="M80" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="N80" s="40" t="inlineStr"/>
       <c r="O80" s="40" t="inlineStr"/>
-      <c r="P80" s="63" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="P80" s="40" t="inlineStr"/>
       <c r="Q80" s="40" t="inlineStr"/>
       <c r="R80" s="40" t="inlineStr"/>
       <c r="S80" s="40" t="inlineStr"/>
@@ -6744,33 +6239,29 @@
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U80" s="41" t="inlineStr">
-        <is>
-          <t>Retorna: cobertura, conceitos_ok, conceitos_faltando, feedback</t>
-        </is>
-      </c>
+      <c r="U80" s="41" t="inlineStr"/>
       <c r="V80" s="1" t="n"/>
     </row>
     <row r="81" ht="24" customHeight="1">
       <c r="A81" s="1" t="n"/>
-      <c r="B81" s="14" t="inlineStr">
-        <is>
-          <t>F-04</t>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C81" s="37" t="inlineStr">
         <is>
-          <t>services/nlp_mapper.py — input livre → tópico (Modo Mentor L-01)</t>
-        </is>
-      </c>
-      <c r="D81" s="45" t="inlineStr">
-        <is>
-          <t>L-01</t>
-        </is>
-      </c>
-      <c r="E81" s="60" t="inlineStr">
-        <is>
-          <t>🧠 IA</t>
+          <t>Feedback de tempo real: duracao_real_min após cada sessão</t>
+        </is>
+      </c>
+      <c r="D81" s="55" t="inlineStr">
+        <is>
+          <t>BETA</t>
+        </is>
+      </c>
+      <c r="E81" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
         </is>
       </c>
       <c r="F81" s="40" t="inlineStr"/>
@@ -6780,14 +6271,14 @@
       <c r="J81" s="40" t="inlineStr"/>
       <c r="K81" s="40" t="inlineStr"/>
       <c r="L81" s="40" t="inlineStr"/>
-      <c r="M81" s="40" t="inlineStr"/>
+      <c r="M81" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="N81" s="40" t="inlineStr"/>
       <c r="O81" s="40" t="inlineStr"/>
-      <c r="P81" s="63" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="P81" s="40" t="inlineStr"/>
       <c r="Q81" s="40" t="inlineStr"/>
       <c r="R81" s="40" t="inlineStr"/>
       <c r="S81" s="40" t="inlineStr"/>
@@ -6796,25 +6287,29 @@
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U81" s="41" t="inlineStr"/>
+      <c r="U81" s="41" t="inlineStr">
+        <is>
+          <t>Pergunta única: Muito pouco/Adequado/Precisei de mais. Calibra estimativas individuais.</t>
+        </is>
+      </c>
       <c r="V81" s="1" t="n"/>
     </row>
     <row r="82" ht="24" customHeight="1">
       <c r="A82" s="1" t="n"/>
-      <c r="B82" s="14" t="inlineStr">
-        <is>
-          <t>F-04</t>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C82" s="37" t="inlineStr">
         <is>
-          <t>POST /quiz/gerar + /quiz/responder + POST /sessao/input</t>
+          <t>services/viabilidade.py — horas disponíveis vs carga total</t>
         </is>
       </c>
       <c r="D82" s="38" t="inlineStr"/>
-      <c r="E82" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
+      <c r="E82" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
         </is>
       </c>
       <c r="F82" s="40" t="inlineStr"/>
@@ -6824,14 +6319,14 @@
       <c r="J82" s="40" t="inlineStr"/>
       <c r="K82" s="40" t="inlineStr"/>
       <c r="L82" s="40" t="inlineStr"/>
-      <c r="M82" s="40" t="inlineStr"/>
+      <c r="M82" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="N82" s="40" t="inlineStr"/>
       <c r="O82" s="40" t="inlineStr"/>
-      <c r="P82" s="63" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="P82" s="40" t="inlineStr"/>
       <c r="Q82" s="40" t="inlineStr"/>
       <c r="R82" s="40" t="inlineStr"/>
       <c r="S82" s="40" t="inlineStr"/>
@@ -6840,29 +6335,29 @@
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U82" s="41" t="inlineStr"/>
+      <c r="U82" s="41" t="inlineStr">
+        <is>
+          <t>Sugere remover complementares se inviável</t>
+        </is>
+      </c>
       <c r="V82" s="1" t="n"/>
     </row>
     <row r="83" ht="24" customHeight="1">
       <c r="A83" s="1" t="n"/>
-      <c r="B83" s="14" t="inlineStr">
-        <is>
-          <t>F-04</t>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C83" s="37" t="inlineStr">
         <is>
-          <t>padrao_cognitivo.py — classifica tipo de erro por raciocínio exigido</t>
-        </is>
-      </c>
-      <c r="D83" s="48" t="inlineStr">
-        <is>
-          <t>D-09</t>
-        </is>
-      </c>
-      <c r="E83" s="60" t="inlineStr">
-        <is>
-          <t>🧠 IA</t>
+          <t>services/modo_estudo.py — pré/pós edital + sugestão de paralelização</t>
+        </is>
+      </c>
+      <c r="D83" s="38" t="inlineStr"/>
+      <c r="E83" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
         </is>
       </c>
       <c r="F83" s="40" t="inlineStr"/>
@@ -6872,19 +6367,15 @@
       <c r="J83" s="40" t="inlineStr"/>
       <c r="K83" s="40" t="inlineStr"/>
       <c r="L83" s="40" t="inlineStr"/>
-      <c r="M83" s="40" t="inlineStr"/>
+      <c r="M83" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="N83" s="40" t="inlineStr"/>
       <c r="O83" s="40" t="inlineStr"/>
-      <c r="P83" s="63" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="Q83" s="63" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="P83" s="40" t="inlineStr"/>
+      <c r="Q83" s="40" t="inlineStr"/>
       <c r="R83" s="40" t="inlineStr"/>
       <c r="S83" s="40" t="inlineStr"/>
       <c r="T83" s="38" t="inlineStr">
@@ -6894,31 +6385,27 @@
       </c>
       <c r="U83" s="41" t="inlineStr">
         <is>
-          <t>Ativa com &gt;= 50 questões erradas. Kahneman 2011: System 1 vs System 2.</t>
+          <t>Semi-automático: sistema sugere, aluno confirma</t>
         </is>
       </c>
       <c r="V83" s="1" t="n"/>
     </row>
     <row r="84" ht="24" customHeight="1">
       <c r="A84" s="1" t="n"/>
-      <c r="B84" s="14" t="inlineStr">
-        <is>
-          <t>F-04</t>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C84" s="37" t="inlineStr">
         <is>
-          <t>Quiz prioriza tipo problemático detectado para o aluno</t>
-        </is>
-      </c>
-      <c r="D84" s="48" t="inlineStr">
-        <is>
-          <t>D-09</t>
-        </is>
-      </c>
-      <c r="E84" s="60" t="inlineStr">
-        <is>
-          <t>🧠 IA</t>
+          <t>services/diff_edital.py — diff pré vs pós edital</t>
+        </is>
+      </c>
+      <c r="D84" s="38" t="inlineStr"/>
+      <c r="E84" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
         </is>
       </c>
       <c r="F84" s="40" t="inlineStr"/>
@@ -6928,15 +6415,15 @@
       <c r="J84" s="40" t="inlineStr"/>
       <c r="K84" s="40" t="inlineStr"/>
       <c r="L84" s="40" t="inlineStr"/>
-      <c r="M84" s="40" t="inlineStr"/>
+      <c r="M84" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="N84" s="40" t="inlineStr"/>
       <c r="O84" s="40" t="inlineStr"/>
       <c r="P84" s="40" t="inlineStr"/>
-      <c r="Q84" s="63" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="Q84" s="40" t="inlineStr"/>
       <c r="R84" s="40" t="inlineStr"/>
       <c r="S84" s="40" t="inlineStr"/>
       <c r="T84" s="38" t="inlineStr">
@@ -6944,25 +6431,33 @@
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U84" s="41" t="inlineStr"/>
+      <c r="U84" s="41" t="inlineStr">
+        <is>
+          <t>Gera: novos[], removidos[], peso_alterado[]</t>
+        </is>
+      </c>
       <c r="V84" s="1" t="n"/>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="1" t="n"/>
-      <c r="B85" s="14" t="inlineStr">
-        <is>
-          <t>F-04</t>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C85" s="37" t="inlineStr">
         <is>
-          <t>Testar fluxo completo: calibração → quiz elaborativo → flashcard</t>
-        </is>
-      </c>
-      <c r="D85" s="38" t="inlineStr"/>
-      <c r="E85" s="42" t="inlineStr">
-        <is>
-          <t>✅ Teste</t>
+          <t>services/meta_semanal.py — gerar_nova_janela() + fechar_janela()</t>
+        </is>
+      </c>
+      <c r="D85" s="47" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="E85" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
         </is>
       </c>
       <c r="F85" s="40" t="inlineStr"/>
@@ -6972,15 +6467,19 @@
       <c r="J85" s="40" t="inlineStr"/>
       <c r="K85" s="40" t="inlineStr"/>
       <c r="L85" s="40" t="inlineStr"/>
-      <c r="M85" s="40" t="inlineStr"/>
-      <c r="N85" s="40" t="inlineStr"/>
+      <c r="M85" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="N85" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="O85" s="40" t="inlineStr"/>
       <c r="P85" s="40" t="inlineStr"/>
-      <c r="Q85" s="63" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="Q85" s="40" t="inlineStr"/>
       <c r="R85" s="40" t="inlineStr"/>
       <c r="S85" s="40" t="inlineStr"/>
       <c r="T85" s="38" t="inlineStr">
@@ -6990,16 +6489,16 @@
       </c>
       <c r="U85" s="41" t="inlineStr">
         <is>
-          <t>Marco: quiz IA funcionando</t>
+          <t>conservador=85%/moderado=75%/agressivo=65%. Expiração seletiva. Nunca cresce por atraso.</t>
         </is>
       </c>
       <c r="V85" s="1" t="n"/>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="1" t="n"/>
-      <c r="B86" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ◆  PAINEL ADMIN   ·   Semanas 12–14</t>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C86" s="78" t="n"/>
@@ -7025,24 +6524,24 @@
     </row>
     <row r="87" ht="24" customHeight="1">
       <c r="A87" s="1" t="n"/>
-      <c r="B87" s="15" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C87" s="37" t="inlineStr">
         <is>
-          <t>Middleware: bloquear /admin para role != admin</t>
-        </is>
-      </c>
-      <c r="D87" s="43" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
-      <c r="E87" s="50" t="inlineStr">
-        <is>
-          <t>🔒 Auth</t>
+          <t>Modo Revisão Final (D-13): ativa 14 dias antes, congela novos tópicos</t>
+        </is>
+      </c>
+      <c r="D87" s="61" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="E87" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
         </is>
       </c>
       <c r="F87" s="40" t="inlineStr"/>
@@ -7053,14 +6552,14 @@
       <c r="K87" s="40" t="inlineStr"/>
       <c r="L87" s="40" t="inlineStr"/>
       <c r="M87" s="40" t="inlineStr"/>
-      <c r="N87" s="40" t="inlineStr"/>
+      <c r="N87" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="O87" s="40" t="inlineStr"/>
       <c r="P87" s="40" t="inlineStr"/>
-      <c r="Q87" s="65" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="Q87" s="40" t="inlineStr"/>
       <c r="R87" s="40" t="inlineStr"/>
       <c r="S87" s="40" t="inlineStr"/>
       <c r="T87" s="38" t="inlineStr">
@@ -7068,26 +6567,26 @@
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U87" s="41" t="inlineStr"/>
+      <c r="U87" s="41" t="inlineStr">
+        <is>
+          <t>Ordena: menor acerto × maior peso × maior decay</t>
+        </is>
+      </c>
       <c r="V87" s="1" t="n"/>
     </row>
     <row r="88" ht="24" customHeight="1">
       <c r="A88" s="1" t="n"/>
-      <c r="B88" s="15" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C88" s="37" t="inlineStr">
         <is>
-          <t>GET/POST/PATCH /admin/usuarios — criar, bloquear, resetar senha</t>
-        </is>
-      </c>
-      <c r="D88" s="43" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
+          <t>GET /cronograma/gerar + POST /edital/upload + GET /edital/diff</t>
+        </is>
+      </c>
+      <c r="D88" s="38" t="inlineStr"/>
       <c r="E88" s="51" t="inlineStr">
         <is>
           <t>🔌 API</t>
@@ -7099,16 +6598,16 @@
       <c r="I88" s="40" t="inlineStr"/>
       <c r="J88" s="40" t="inlineStr"/>
       <c r="K88" s="40" t="inlineStr"/>
-      <c r="L88" s="40" t="inlineStr"/>
+      <c r="L88" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="M88" s="40" t="inlineStr"/>
       <c r="N88" s="40" t="inlineStr"/>
       <c r="O88" s="40" t="inlineStr"/>
       <c r="P88" s="40" t="inlineStr"/>
-      <c r="Q88" s="65" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="Q88" s="40" t="inlineStr"/>
       <c r="R88" s="40" t="inlineStr"/>
       <c r="S88" s="40" t="inlineStr"/>
       <c r="T88" s="38" t="inlineStr">
@@ -7121,21 +6620,17 @@
     </row>
     <row r="89" ht="24" customHeight="1">
       <c r="A89" s="1" t="n"/>
-      <c r="B89" s="15" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C89" s="37" t="inlineStr">
         <is>
-          <t>GET /admin/dashboard-geral — IP, % conclusão, situacao tópicos</t>
-        </is>
-      </c>
-      <c r="D89" s="43" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
+          <t>PATCH /cronograma/paralelizar</t>
+        </is>
+      </c>
+      <c r="D89" s="38" t="inlineStr"/>
       <c r="E89" s="51" t="inlineStr">
         <is>
           <t>🔌 API</t>
@@ -7148,45 +6643,49 @@
       <c r="J89" s="40" t="inlineStr"/>
       <c r="K89" s="40" t="inlineStr"/>
       <c r="L89" s="40" t="inlineStr"/>
-      <c r="M89" s="40" t="inlineStr"/>
+      <c r="M89" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="N89" s="40" t="inlineStr"/>
       <c r="O89" s="40" t="inlineStr"/>
       <c r="P89" s="40" t="inlineStr"/>
       <c r="Q89" s="40" t="inlineStr"/>
-      <c r="R89" s="65" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="R89" s="40" t="inlineStr"/>
       <c r="S89" s="40" t="inlineStr"/>
       <c r="T89" s="38" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U89" s="41" t="inlineStr"/>
+      <c r="U89" s="41" t="inlineStr">
+        <is>
+          <t>Aluno confirma paralelização sugerida</t>
+        </is>
+      </c>
       <c r="V89" s="1" t="n"/>
     </row>
     <row r="90" ht="24" customHeight="1">
       <c r="A90" s="1" t="n"/>
-      <c r="B90" s="15" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C90" s="37" t="inlineStr">
         <is>
-          <t>POST /admin/editais + PUT /admin/topicos</t>
-        </is>
-      </c>
-      <c r="D90" s="43" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
-      <c r="E90" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
+          <t>Regra interleaving: max 2 sessões da mesma matéria por dia</t>
+        </is>
+      </c>
+      <c r="D90" s="45" t="inlineStr">
+        <is>
+          <t>L-03</t>
+        </is>
+      </c>
+      <c r="E90" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
         </is>
       </c>
       <c r="F90" s="40" t="inlineStr"/>
@@ -7197,44 +6696,44 @@
       <c r="K90" s="40" t="inlineStr"/>
       <c r="L90" s="40" t="inlineStr"/>
       <c r="M90" s="40" t="inlineStr"/>
-      <c r="N90" s="40" t="inlineStr"/>
+      <c r="N90" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="O90" s="40" t="inlineStr"/>
       <c r="P90" s="40" t="inlineStr"/>
       <c r="Q90" s="40" t="inlineStr"/>
-      <c r="R90" s="65" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="R90" s="40" t="inlineStr"/>
       <c r="S90" s="40" t="inlineStr"/>
       <c r="T90" s="38" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U90" s="41" t="inlineStr"/>
+      <c r="U90" s="41" t="inlineStr">
+        <is>
+          <t>Rohrer &amp; Taylor 2007</t>
+        </is>
+      </c>
       <c r="V90" s="1" t="n"/>
     </row>
     <row r="91" ht="24" customHeight="1">
       <c r="A91" s="1" t="n"/>
-      <c r="B91" s="15" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C91" s="37" t="inlineStr">
         <is>
-          <t>PATCH /admin/cronograma/{aluno_id} — ajustar data_prova</t>
-        </is>
-      </c>
-      <c r="D91" s="43" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
-      <c r="E91" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
+          <t>Testes unitários pytest — algoritmo de priorização</t>
+        </is>
+      </c>
+      <c r="D91" s="38" t="inlineStr"/>
+      <c r="E91" s="42" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
         </is>
       </c>
       <c r="F91" s="40" t="inlineStr"/>
@@ -7245,15 +6744,15 @@
       <c r="K91" s="40" t="inlineStr"/>
       <c r="L91" s="40" t="inlineStr"/>
       <c r="M91" s="40" t="inlineStr"/>
-      <c r="N91" s="40" t="inlineStr"/>
+      <c r="N91" s="59" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="O91" s="40" t="inlineStr"/>
       <c r="P91" s="40" t="inlineStr"/>
       <c r="Q91" s="40" t="inlineStr"/>
-      <c r="R91" s="65" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="R91" s="40" t="inlineStr"/>
       <c r="S91" s="40" t="inlineStr"/>
       <c r="T91" s="38" t="inlineStr">
         <is>
@@ -7265,76 +6764,48 @@
     </row>
     <row r="92" ht="24" customHeight="1">
       <c r="A92" s="1" t="n"/>
-      <c r="B92" s="15" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
-      <c r="C92" s="37" t="inlineStr">
-        <is>
-          <t>PATCH /admin/config/ia-provider + /pesos-algoritmo (W1-W4)</t>
-        </is>
-      </c>
-      <c r="D92" s="43" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
-      <c r="E92" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
-        </is>
-      </c>
-      <c r="F92" s="40" t="inlineStr"/>
-      <c r="G92" s="40" t="inlineStr"/>
-      <c r="H92" s="40" t="inlineStr"/>
-      <c r="I92" s="40" t="inlineStr"/>
-      <c r="J92" s="40" t="inlineStr"/>
-      <c r="K92" s="40" t="inlineStr"/>
-      <c r="L92" s="40" t="inlineStr"/>
-      <c r="M92" s="40" t="inlineStr"/>
-      <c r="N92" s="40" t="inlineStr"/>
-      <c r="O92" s="40" t="inlineStr"/>
-      <c r="P92" s="40" t="inlineStr"/>
-      <c r="Q92" s="40" t="inlineStr"/>
-      <c r="R92" s="65" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="S92" s="40" t="inlineStr"/>
-      <c r="T92" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
-        </is>
-      </c>
-      <c r="U92" s="41" t="inlineStr">
-        <is>
-          <t>Validar soma W1+W2+W3+W4 = 1.0</t>
-        </is>
-      </c>
+      <c r="B92" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ◆  FASE 4 — Quiz IA + Calibração Adaptativa + Padrão Cognitivo   ·   Semanas 10–12</t>
+        </is>
+      </c>
+      <c r="C92" s="78" t="n"/>
+      <c r="D92" s="78" t="n"/>
+      <c r="E92" s="78" t="n"/>
+      <c r="F92" s="78" t="n"/>
+      <c r="G92" s="78" t="n"/>
+      <c r="H92" s="78" t="n"/>
+      <c r="I92" s="78" t="n"/>
+      <c r="J92" s="78" t="n"/>
+      <c r="K92" s="78" t="n"/>
+      <c r="L92" s="78" t="n"/>
+      <c r="M92" s="78" t="n"/>
+      <c r="N92" s="78" t="n"/>
+      <c r="O92" s="78" t="n"/>
+      <c r="P92" s="78" t="n"/>
+      <c r="Q92" s="78" t="n"/>
+      <c r="R92" s="78" t="n"/>
+      <c r="S92" s="78" t="n"/>
+      <c r="T92" s="78" t="n"/>
+      <c r="U92" s="79" t="n"/>
       <c r="V92" s="1" t="n"/>
     </row>
     <row r="93" ht="24" customHeight="1">
       <c r="A93" s="1" t="n"/>
-      <c r="B93" s="15" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
+      <c r="B93" s="14" t="inlineStr">
+        <is>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C93" s="37" t="inlineStr">
         <is>
-          <t>GET /admin/meta/{aluno_id}/historico — déficit privado por janela</t>
-        </is>
-      </c>
-      <c r="D93" s="47" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="E93" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
+          <t>Camada AIProvider: interface + GeminiProvider + AnthropicProvider</t>
+        </is>
+      </c>
+      <c r="D93" s="38" t="inlineStr"/>
+      <c r="E93" s="60" t="inlineStr">
+        <is>
+          <t>🧠 IA</t>
         </is>
       </c>
       <c r="F93" s="40" t="inlineStr"/>
@@ -7346,43 +6817,47 @@
       <c r="L93" s="40" t="inlineStr"/>
       <c r="M93" s="40" t="inlineStr"/>
       <c r="N93" s="40" t="inlineStr"/>
-      <c r="O93" s="40" t="inlineStr"/>
+      <c r="O93" s="63" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="P93" s="40" t="inlineStr"/>
       <c r="Q93" s="40" t="inlineStr"/>
       <c r="R93" s="40" t="inlineStr"/>
-      <c r="S93" s="65" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="S93" s="40" t="inlineStr"/>
       <c r="T93" s="38" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U93" s="41" t="inlineStr"/>
+      <c r="U93" s="41" t="inlineStr">
+        <is>
+          <t>Admin troca via ConfigSistema sem redeploy</t>
+        </is>
+      </c>
       <c r="V93" s="1" t="n"/>
     </row>
     <row r="94" ht="24" customHeight="1">
       <c r="A94" s="1" t="n"/>
-      <c r="B94" s="15" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C94" s="37" t="inlineStr">
         <is>
-          <t>GET /admin/padrao-cognitivo/{aluno_id}</t>
-        </is>
-      </c>
-      <c r="D94" s="48" t="inlineStr">
-        <is>
-          <t>D-09</t>
-        </is>
-      </c>
-      <c r="E94" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
+          <t>quiz_generator.py — parâmetro momento (primeiro_contato / revisao)</t>
+        </is>
+      </c>
+      <c r="D94" s="45" t="inlineStr">
+        <is>
+          <t>L-02</t>
+        </is>
+      </c>
+      <c r="E94" s="60" t="inlineStr">
+        <is>
+          <t>🧠 IA</t>
         </is>
       </c>
       <c r="F94" s="40" t="inlineStr"/>
@@ -7394,43 +6869,43 @@
       <c r="L94" s="40" t="inlineStr"/>
       <c r="M94" s="40" t="inlineStr"/>
       <c r="N94" s="40" t="inlineStr"/>
-      <c r="O94" s="40" t="inlineStr"/>
+      <c r="O94" s="63" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="P94" s="40" t="inlineStr"/>
       <c r="Q94" s="40" t="inlineStr"/>
       <c r="R94" s="40" t="inlineStr"/>
-      <c r="S94" s="65" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="S94" s="40" t="inlineStr"/>
       <c r="T94" s="38" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U94" s="41" t="inlineStr"/>
+      <c r="U94" s="41" t="inlineStr">
+        <is>
+          <t>primeiro_contato: 70% conceito puro. revisao: 70% contraste+aplicação+exceção.</t>
+        </is>
+      </c>
       <c r="V94" s="1" t="n"/>
     </row>
     <row r="95" ht="24" customHeight="1">
       <c r="A95" s="1" t="n"/>
-      <c r="B95" s="15" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
+      <c r="B95" s="14" t="inlineStr">
+        <is>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C95" s="37" t="inlineStr">
         <is>
-          <t>GET /admin/confianca-estimativas — tópicos com estimativas não calibradas</t>
-        </is>
-      </c>
-      <c r="D95" s="55" t="inlineStr">
-        <is>
-          <t>BETA</t>
-        </is>
-      </c>
-      <c r="E95" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
+          <t>Anti-alucinação: grounding no material real do aluno</t>
+        </is>
+      </c>
+      <c r="D95" s="38" t="inlineStr"/>
+      <c r="E95" s="60" t="inlineStr">
+        <is>
+          <t>🧠 IA</t>
         </is>
       </c>
       <c r="F95" s="40" t="inlineStr"/>
@@ -7442,43 +6917,43 @@
       <c r="L95" s="40" t="inlineStr"/>
       <c r="M95" s="40" t="inlineStr"/>
       <c r="N95" s="40" t="inlineStr"/>
-      <c r="O95" s="40" t="inlineStr"/>
+      <c r="O95" s="63" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="P95" s="40" t="inlineStr"/>
       <c r="Q95" s="40" t="inlineStr"/>
       <c r="R95" s="40" t="inlineStr"/>
-      <c r="S95" s="65" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="S95" s="40" t="inlineStr"/>
       <c r="T95" s="38" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U95" s="41" t="inlineStr">
-        <is>
-          <t>Admin monitora qualidade das estimativas durante o beta</t>
-        </is>
-      </c>
+      <c r="U95" s="41" t="inlineStr"/>
       <c r="V95" s="1" t="n"/>
     </row>
     <row r="96" ht="24" customHeight="1">
       <c r="A96" s="1" t="n"/>
-      <c r="B96" s="15" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
+      <c r="B96" s="14" t="inlineStr">
+        <is>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C96" s="37" t="inlineStr">
         <is>
-          <t>Testar painel admin completo</t>
-        </is>
-      </c>
-      <c r="D96" s="38" t="inlineStr"/>
-      <c r="E96" s="42" t="inlineStr">
-        <is>
-          <t>✅ Teste</t>
+          <t>Quiz focado nos erros críticos pendentes do tópico</t>
+        </is>
+      </c>
+      <c r="D96" s="45" t="inlineStr">
+        <is>
+          <t>L-08</t>
+        </is>
+      </c>
+      <c r="E96" s="60" t="inlineStr">
+        <is>
+          <t>🧠 IA</t>
         </is>
       </c>
       <c r="F96" s="40" t="inlineStr"/>
@@ -7490,15 +6965,15 @@
       <c r="L96" s="40" t="inlineStr"/>
       <c r="M96" s="40" t="inlineStr"/>
       <c r="N96" s="40" t="inlineStr"/>
-      <c r="O96" s="40" t="inlineStr"/>
+      <c r="O96" s="63" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="P96" s="40" t="inlineStr"/>
       <c r="Q96" s="40" t="inlineStr"/>
       <c r="R96" s="40" t="inlineStr"/>
-      <c r="S96" s="65" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="S96" s="40" t="inlineStr"/>
       <c r="T96" s="38" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
@@ -7509,9 +6984,9 @@
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="1" t="n"/>
-      <c r="B97" s="66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ◆  FASE 5 — Dashboard + IP + Mapa + PEDAG-01 + Simulado + Radar   ·   Semanas 14–17</t>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C97" s="78" t="n"/>
@@ -7537,20 +7012,24 @@
     </row>
     <row r="98" ht="24" customHeight="1">
       <c r="A98" s="1" t="n"/>
-      <c r="B98" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C98" s="37" t="inlineStr">
         <is>
-          <t>GET /dashboard/kpis + por-materia + evolucao-mensal + ranking-erros</t>
-        </is>
-      </c>
-      <c r="D98" s="38" t="inlineStr"/>
-      <c r="E98" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
+          <t>Calibração UX-02: lógica adaptativa — ajusta dificuldade pela resposta anterior</t>
+        </is>
+      </c>
+      <c r="D98" s="48" t="inlineStr">
+        <is>
+          <t>UX-02</t>
+        </is>
+      </c>
+      <c r="E98" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
         </is>
       </c>
       <c r="F98" s="40" t="inlineStr"/>
@@ -7563,38 +7042,46 @@
       <c r="M98" s="40" t="inlineStr"/>
       <c r="N98" s="40" t="inlineStr"/>
       <c r="O98" s="40" t="inlineStr"/>
-      <c r="P98" s="40" t="inlineStr"/>
+      <c r="P98" s="63" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="Q98" s="40" t="inlineStr"/>
       <c r="R98" s="40" t="inlineStr"/>
-      <c r="S98" s="67" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="S98" s="40" t="inlineStr"/>
       <c r="T98" s="38" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U98" s="41" t="inlineStr"/>
+      <c r="U98" s="41" t="inlineStr">
+        <is>
+          <t>4-5 acertos=sobe / 2-3=mantém / 0-1=desce</t>
+        </is>
+      </c>
       <c r="V98" s="1" t="n"/>
     </row>
     <row r="99" ht="24" customHeight="1">
       <c r="A99" s="1" t="n"/>
-      <c r="B99" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C99" s="37" t="inlineStr">
         <is>
-          <t>GET /export/xlsx — reutiliza lógica SISFIG ~80%</t>
-        </is>
-      </c>
-      <c r="D99" s="38" t="inlineStr"/>
-      <c r="E99" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
+          <t>Calibração UX-02: fonte=calibracao peso 1.2x — diluído após 3 baterias reais</t>
+        </is>
+      </c>
+      <c r="D99" s="48" t="inlineStr">
+        <is>
+          <t>UX-02</t>
+        </is>
+      </c>
+      <c r="E99" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
         </is>
       </c>
       <c r="F99" s="40" t="inlineStr"/>
@@ -7607,42 +7094,46 @@
       <c r="M99" s="40" t="inlineStr"/>
       <c r="N99" s="40" t="inlineStr"/>
       <c r="O99" s="40" t="inlineStr"/>
-      <c r="P99" s="40" t="inlineStr"/>
+      <c r="P99" s="63" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="Q99" s="40" t="inlineStr"/>
       <c r="R99" s="40" t="inlineStr"/>
-      <c r="S99" s="67" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="S99" s="40" t="inlineStr"/>
       <c r="T99" s="38" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U99" s="41" t="inlineStr"/>
+      <c r="U99" s="41" t="inlineStr">
+        <is>
+          <t>Dados reais substituem progressivamente. CAT: van der Linden &amp; Hambleton 1997.</t>
+        </is>
+      </c>
       <c r="V99" s="1" t="n"/>
     </row>
     <row r="100" ht="24" customHeight="1">
       <c r="A100" s="1" t="n"/>
-      <c r="B100" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C100" s="37" t="inlineStr">
         <is>
-          <t>Relatório PDF semanal automático + link mentor 7 dias</t>
-        </is>
-      </c>
-      <c r="D100" s="45" t="inlineStr">
-        <is>
-          <t>L-07</t>
-        </is>
-      </c>
-      <c r="E100" s="68" t="inlineStr">
-        <is>
-          <t>📄 Relatório</t>
+          <t>Calibração UX-02: UI sem timer + framing de diagnóstico + feedback pós-cal</t>
+        </is>
+      </c>
+      <c r="D100" s="48" t="inlineStr">
+        <is>
+          <t>UX-02</t>
+        </is>
+      </c>
+      <c r="E100" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
         </is>
       </c>
       <c r="F100" s="40" t="inlineStr"/>
@@ -7655,42 +7146,46 @@
       <c r="M100" s="40" t="inlineStr"/>
       <c r="N100" s="40" t="inlineStr"/>
       <c r="O100" s="40" t="inlineStr"/>
-      <c r="P100" s="40" t="inlineStr"/>
+      <c r="P100" s="63" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="Q100" s="40" t="inlineStr"/>
       <c r="R100" s="40" t="inlineStr"/>
-      <c r="S100" s="67" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="S100" s="40" t="inlineStr"/>
       <c r="T100" s="38" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U100" s="41" t="inlineStr"/>
+      <c r="U100" s="41" t="inlineStr">
+        <is>
+          <t>'Quanto mais honesto, melhor o plano.' Aluno vê nível detectado + pontos fortes + lacunas</t>
+        </is>
+      </c>
       <c r="V100" s="1" t="n"/>
     </row>
     <row r="101" ht="24" customHeight="1">
       <c r="A101" s="1" t="n"/>
-      <c r="B101" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B101" s="14" t="inlineStr">
+        <is>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C101" s="37" t="inlineStr">
         <is>
-          <t>services/indice_prontidao.py — IP = Σ(acerto × peso × decay × cobertura)</t>
-        </is>
-      </c>
-      <c r="D101" s="69" t="inlineStr">
-        <is>
-          <t>D-10</t>
-        </is>
-      </c>
-      <c r="E101" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
+          <t>flashcard_generator.py — resposta digitada avaliada por IA</t>
+        </is>
+      </c>
+      <c r="D101" s="46" t="inlineStr">
+        <is>
+          <t>D-14</t>
+        </is>
+      </c>
+      <c r="E101" s="60" t="inlineStr">
+        <is>
+          <t>🧠 IA</t>
         </is>
       </c>
       <c r="F101" s="40" t="inlineStr"/>
@@ -7703,7 +7198,11 @@
       <c r="M101" s="40" t="inlineStr"/>
       <c r="N101" s="40" t="inlineStr"/>
       <c r="O101" s="40" t="inlineStr"/>
-      <c r="P101" s="40" t="inlineStr"/>
+      <c r="P101" s="63" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="Q101" s="40" t="inlineStr"/>
       <c r="R101" s="40" t="inlineStr"/>
       <c r="S101" s="40" t="inlineStr"/>
@@ -7714,26 +7213,26 @@
       </c>
       <c r="U101" s="41" t="inlineStr">
         <is>
-          <t>0 a 100 ponderado pelo edital. Framing: diagnóstico, não pontuação.</t>
+          <t>Sem STT. Chi 1994: self-explanation effect preservado pela geração ativa. IA verifica conceitos cobertos.</t>
         </is>
       </c>
       <c r="V101" s="1" t="n"/>
     </row>
     <row r="102" ht="24" customHeight="1">
       <c r="A102" s="1" t="n"/>
-      <c r="B102" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C102" s="37" t="inlineStr">
         <is>
-          <t>Mapa de progresso: tópicos coloridos por situacao — GAME-01</t>
-        </is>
-      </c>
-      <c r="D102" s="69" t="inlineStr">
-        <is>
-          <t>GAME-01</t>
+          <t>POST /flashcard/avaliar — IA compara resposta com conceitos esperados</t>
+        </is>
+      </c>
+      <c r="D102" s="46" t="inlineStr">
+        <is>
+          <t>D-14</t>
         </is>
       </c>
       <c r="E102" s="51" t="inlineStr">
@@ -7751,7 +7250,11 @@
       <c r="M102" s="40" t="inlineStr"/>
       <c r="N102" s="40" t="inlineStr"/>
       <c r="O102" s="40" t="inlineStr"/>
-      <c r="P102" s="40" t="inlineStr"/>
+      <c r="P102" s="63" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="Q102" s="40" t="inlineStr"/>
       <c r="R102" s="40" t="inlineStr"/>
       <c r="S102" s="40" t="inlineStr"/>
@@ -7762,31 +7265,31 @@
       </c>
       <c r="U102" s="41" t="inlineStr">
         <is>
-          <t>Dominado=verde/Em estudo=amarelo/Não iniciado=cinza. Bandura 1997: autoeficácia por visualização.</t>
+          <t>Retorna: cobertura, conceitos_ok, conceitos_faltando, feedback</t>
         </is>
       </c>
       <c r="V102" s="1" t="n"/>
     </row>
     <row r="103" ht="24" customHeight="1">
       <c r="A103" s="1" t="n"/>
-      <c r="B103" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B103" s="14" t="inlineStr">
+        <is>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C103" s="37" t="inlineStr">
         <is>
-          <t>Curva de mastery: histórico semanal do IP em gráfico</t>
-        </is>
-      </c>
-      <c r="D103" s="69" t="inlineStr">
-        <is>
-          <t>D-10</t>
-        </is>
-      </c>
-      <c r="E103" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
+          <t>services/nlp_mapper.py — input livre → tópico (Modo Mentor L-01)</t>
+        </is>
+      </c>
+      <c r="D103" s="45" t="inlineStr">
+        <is>
+          <t>L-01</t>
+        </is>
+      </c>
+      <c r="E103" s="60" t="inlineStr">
+        <is>
+          <t>🧠 IA</t>
         </is>
       </c>
       <c r="F103" s="40" t="inlineStr"/>
@@ -7799,7 +7302,11 @@
       <c r="M103" s="40" t="inlineStr"/>
       <c r="N103" s="40" t="inlineStr"/>
       <c r="O103" s="40" t="inlineStr"/>
-      <c r="P103" s="40" t="inlineStr"/>
+      <c r="P103" s="63" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="Q103" s="40" t="inlineStr"/>
       <c r="R103" s="40" t="inlineStr"/>
       <c r="S103" s="40" t="inlineStr"/>
@@ -7808,30 +7315,22 @@
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U103" s="41" t="inlineStr">
-        <is>
-          <t>Dweck 2006: growth mindset — aluno vê que esforço produz progresso mensurável</t>
-        </is>
-      </c>
+      <c r="U103" s="41" t="inlineStr"/>
       <c r="V103" s="1" t="n"/>
     </row>
     <row r="104" ht="24" customHeight="1">
       <c r="A104" s="1" t="n"/>
-      <c r="B104" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C104" s="37" t="inlineStr">
         <is>
-          <t>Meta de IP: aluno define IP alvo e prazo</t>
-        </is>
-      </c>
-      <c r="D104" s="69" t="inlineStr">
-        <is>
-          <t>D-10</t>
-        </is>
-      </c>
+          <t>POST /quiz/gerar + /quiz/responder + POST /sessao/input</t>
+        </is>
+      </c>
+      <c r="D104" s="38" t="inlineStr"/>
       <c r="E104" s="51" t="inlineStr">
         <is>
           <t>🔌 API</t>
@@ -7847,7 +7346,11 @@
       <c r="M104" s="40" t="inlineStr"/>
       <c r="N104" s="40" t="inlineStr"/>
       <c r="O104" s="40" t="inlineStr"/>
-      <c r="P104" s="40" t="inlineStr"/>
+      <c r="P104" s="63" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="Q104" s="40" t="inlineStr"/>
       <c r="R104" s="40" t="inlineStr"/>
       <c r="S104" s="40" t="inlineStr"/>
@@ -7861,24 +7364,24 @@
     </row>
     <row r="105" ht="24" customHeight="1">
       <c r="A105" s="1" t="n"/>
-      <c r="B105" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B105" s="14" t="inlineStr">
+        <is>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C105" s="37" t="inlineStr">
         <is>
-          <t>Impacto da meta semanal no IP: '+X pontos se concluir esta semana'</t>
-        </is>
-      </c>
-      <c r="D105" s="69" t="inlineStr">
-        <is>
-          <t>D-10</t>
-        </is>
-      </c>
-      <c r="E105" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
+          <t>padrao_cognitivo.py — classifica tipo de erro por raciocínio exigido</t>
+        </is>
+      </c>
+      <c r="D105" s="48" t="inlineStr">
+        <is>
+          <t>D-09</t>
+        </is>
+      </c>
+      <c r="E105" s="60" t="inlineStr">
+        <is>
+          <t>🧠 IA</t>
         </is>
       </c>
       <c r="F105" s="40" t="inlineStr"/>
@@ -7891,8 +7394,16 @@
       <c r="M105" s="40" t="inlineStr"/>
       <c r="N105" s="40" t="inlineStr"/>
       <c r="O105" s="40" t="inlineStr"/>
-      <c r="P105" s="40" t="inlineStr"/>
-      <c r="Q105" s="40" t="inlineStr"/>
+      <c r="P105" s="63" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="Q105" s="63" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="R105" s="40" t="inlineStr"/>
       <c r="S105" s="40" t="inlineStr"/>
       <c r="T105" s="38" t="inlineStr">
@@ -7900,29 +7411,33 @@
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U105" s="41" t="inlineStr"/>
+      <c r="U105" s="41" t="inlineStr">
+        <is>
+          <t>Ativa com &gt;= 50 questões erradas. Kahneman 2011: System 1 vs System 2.</t>
+        </is>
+      </c>
       <c r="V105" s="1" t="n"/>
     </row>
     <row r="106" ht="24" customHeight="1">
       <c r="A106" s="1" t="n"/>
-      <c r="B106" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C106" s="37" t="inlineStr">
         <is>
-          <t>services/diagnostico_topico.py — classifica situacao por tópico</t>
-        </is>
-      </c>
-      <c r="D106" s="49" t="inlineStr">
-        <is>
-          <t>PEDAG-01</t>
-        </is>
-      </c>
-      <c r="E106" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
+          <t>Quiz prioriza tipo problemático detectado para o aluno</t>
+        </is>
+      </c>
+      <c r="D106" s="48" t="inlineStr">
+        <is>
+          <t>D-09</t>
+        </is>
+      </c>
+      <c r="E106" s="60" t="inlineStr">
+        <is>
+          <t>🧠 IA</t>
         </is>
       </c>
       <c r="F106" s="40" t="inlineStr"/>
@@ -7936,7 +7451,11 @@
       <c r="N106" s="40" t="inlineStr"/>
       <c r="O106" s="40" t="inlineStr"/>
       <c r="P106" s="40" t="inlineStr"/>
-      <c r="Q106" s="40" t="inlineStr"/>
+      <c r="Q106" s="63" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="R106" s="40" t="inlineStr"/>
       <c r="S106" s="40" t="inlineStr"/>
       <c r="T106" s="38" t="inlineStr">
@@ -7944,33 +7463,25 @@
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U106" s="41" t="inlineStr">
-        <is>
-          <t>esquecimento/dificuldade_genuina/misconception_ativa/instavel/aprendendo/consolidando</t>
-        </is>
-      </c>
+      <c r="U106" s="41" t="inlineStr"/>
       <c r="V106" s="1" t="n"/>
     </row>
     <row r="107" ht="24" customHeight="1">
       <c r="A107" s="1" t="n"/>
-      <c r="B107" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B107" s="14" t="inlineStr">
+        <is>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C107" s="37" t="inlineStr">
         <is>
-          <t>Detecção esquecimento: acertava &gt;70%, caiu para &lt;50%</t>
-        </is>
-      </c>
-      <c r="D107" s="49" t="inlineStr">
-        <is>
-          <t>PEDAG-01</t>
-        </is>
-      </c>
-      <c r="E107" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
+          <t>Testar fluxo completo: calibração → quiz elaborativo → flashcard</t>
+        </is>
+      </c>
+      <c r="D107" s="38" t="inlineStr"/>
+      <c r="E107" s="42" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
         </is>
       </c>
       <c r="F107" s="40" t="inlineStr"/>
@@ -7984,7 +7495,11 @@
       <c r="N107" s="40" t="inlineStr"/>
       <c r="O107" s="40" t="inlineStr"/>
       <c r="P107" s="40" t="inlineStr"/>
-      <c r="Q107" s="40" t="inlineStr"/>
+      <c r="Q107" s="63" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="R107" s="40" t="inlineStr"/>
       <c r="S107" s="40" t="inlineStr"/>
       <c r="T107" s="38" t="inlineStr">
@@ -7994,79 +7509,59 @@
       </c>
       <c r="U107" s="41" t="inlineStr">
         <is>
-          <t>Resposta: revisão antecipada, intervalo reduzido à metade. VanLehn 2011.</t>
+          <t>Marco: quiz IA funcionando</t>
         </is>
       </c>
       <c r="V107" s="1" t="n"/>
     </row>
     <row r="108" ht="24" customHeight="1">
       <c r="A108" s="1" t="n"/>
-      <c r="B108" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
-        </is>
-      </c>
-      <c r="C108" s="37" t="inlineStr">
-        <is>
-          <t>Detecção dificuldade genuína: nunca atingiu &gt;60% após 2+ ciclos</t>
-        </is>
-      </c>
-      <c r="D108" s="49" t="inlineStr">
-        <is>
-          <t>PEDAG-01</t>
-        </is>
-      </c>
-      <c r="E108" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
-        </is>
-      </c>
-      <c r="F108" s="40" t="inlineStr"/>
-      <c r="G108" s="40" t="inlineStr"/>
-      <c r="H108" s="40" t="inlineStr"/>
-      <c r="I108" s="40" t="inlineStr"/>
-      <c r="J108" s="40" t="inlineStr"/>
-      <c r="K108" s="40" t="inlineStr"/>
-      <c r="L108" s="40" t="inlineStr"/>
-      <c r="M108" s="40" t="inlineStr"/>
-      <c r="N108" s="40" t="inlineStr"/>
-      <c r="O108" s="40" t="inlineStr"/>
-      <c r="P108" s="40" t="inlineStr"/>
-      <c r="Q108" s="40" t="inlineStr"/>
-      <c r="R108" s="40" t="inlineStr"/>
-      <c r="S108" s="40" t="inlineStr"/>
-      <c r="T108" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
-        </is>
-      </c>
-      <c r="U108" s="41" t="inlineStr">
-        <is>
-          <t>Resposta: diagnóstico de pré-requisito + nova explicação</t>
-        </is>
-      </c>
+      <c r="B108" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ◆  PAINEL ADMIN   ·   Semanas 12–14</t>
+        </is>
+      </c>
+      <c r="C108" s="78" t="n"/>
+      <c r="D108" s="78" t="n"/>
+      <c r="E108" s="78" t="n"/>
+      <c r="F108" s="78" t="n"/>
+      <c r="G108" s="78" t="n"/>
+      <c r="H108" s="78" t="n"/>
+      <c r="I108" s="78" t="n"/>
+      <c r="J108" s="78" t="n"/>
+      <c r="K108" s="78" t="n"/>
+      <c r="L108" s="78" t="n"/>
+      <c r="M108" s="78" t="n"/>
+      <c r="N108" s="78" t="n"/>
+      <c r="O108" s="78" t="n"/>
+      <c r="P108" s="78" t="n"/>
+      <c r="Q108" s="78" t="n"/>
+      <c r="R108" s="78" t="n"/>
+      <c r="S108" s="78" t="n"/>
+      <c r="T108" s="78" t="n"/>
+      <c r="U108" s="79" t="n"/>
       <c r="V108" s="1" t="n"/>
     </row>
     <row r="109" ht="24" customHeight="1">
       <c r="A109" s="1" t="n"/>
-      <c r="B109" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B109" s="15" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="C109" s="37" t="inlineStr">
         <is>
-          <t>Diagnóstico de pré-requisito: verifica dependencias[] do tópico</t>
-        </is>
-      </c>
-      <c r="D109" s="49" t="inlineStr">
-        <is>
-          <t>PEDAG-01</t>
-        </is>
-      </c>
-      <c r="E109" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
+          <t>Middleware: bloquear /admin para role != admin</t>
+        </is>
+      </c>
+      <c r="D109" s="43" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="E109" s="50" t="inlineStr">
+        <is>
+          <t>🔒 Auth</t>
         </is>
       </c>
       <c r="F109" s="40" t="inlineStr"/>
@@ -8080,7 +7575,11 @@
       <c r="N109" s="40" t="inlineStr"/>
       <c r="O109" s="40" t="inlineStr"/>
       <c r="P109" s="40" t="inlineStr"/>
-      <c r="Q109" s="40" t="inlineStr"/>
+      <c r="Q109" s="65" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="R109" s="40" t="inlineStr"/>
       <c r="S109" s="40" t="inlineStr"/>
       <c r="T109" s="38" t="inlineStr">
@@ -8088,33 +7587,29 @@
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U109" s="41" t="inlineStr">
-        <is>
-          <t>Se pré-req &lt; 60%: insere na fila com prioridade alta antes de continuar</t>
-        </is>
-      </c>
+      <c r="U109" s="41" t="inlineStr"/>
       <c r="V109" s="1" t="n"/>
     </row>
     <row r="110" ht="24" customHeight="1">
       <c r="A110" s="1" t="n"/>
-      <c r="B110" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="C110" s="37" t="inlineStr">
         <is>
-          <t>Geração de explicação alternativa: prompt modo=reexplicacao</t>
-        </is>
-      </c>
-      <c r="D110" s="49" t="inlineStr">
-        <is>
-          <t>PEDAG-01</t>
-        </is>
-      </c>
-      <c r="E110" s="60" t="inlineStr">
-        <is>
-          <t>🧠 IA</t>
+          <t>GET/POST/PATCH /admin/usuarios — criar, bloquear, resetar senha</t>
+        </is>
+      </c>
+      <c r="D110" s="43" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="E110" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
         </is>
       </c>
       <c r="F110" s="40" t="inlineStr"/>
@@ -8128,7 +7623,11 @@
       <c r="N110" s="40" t="inlineStr"/>
       <c r="O110" s="40" t="inlineStr"/>
       <c r="P110" s="40" t="inlineStr"/>
-      <c r="Q110" s="40" t="inlineStr"/>
+      <c r="Q110" s="65" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="R110" s="40" t="inlineStr"/>
       <c r="S110" s="40" t="inlineStr"/>
       <c r="T110" s="38" t="inlineStr">
@@ -8136,33 +7635,29 @@
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U110" s="41" t="inlineStr">
-        <is>
-          <t>Outra analogia, outro ponto de entrada. Chi et al. 1989: mudança de representação.</t>
-        </is>
-      </c>
+      <c r="U110" s="41" t="inlineStr"/>
       <c r="V110" s="1" t="n"/>
     </row>
     <row r="111" ht="24" customHeight="1">
       <c r="A111" s="1" t="n"/>
-      <c r="B111" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B111" s="15" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="C111" s="37" t="inlineStr">
         <is>
-          <t>Detecção misconception ativa: erra sempre na mesma direção específica</t>
-        </is>
-      </c>
-      <c r="D111" s="49" t="inlineStr">
-        <is>
-          <t>PEDAG-01</t>
-        </is>
-      </c>
-      <c r="E111" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
+          <t>GET /admin/dashboard-geral — IP, % conclusão, situacao tópicos</t>
+        </is>
+      </c>
+      <c r="D111" s="43" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="E111" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
         </is>
       </c>
       <c r="F111" s="40" t="inlineStr"/>
@@ -8177,40 +7672,40 @@
       <c r="O111" s="40" t="inlineStr"/>
       <c r="P111" s="40" t="inlineStr"/>
       <c r="Q111" s="40" t="inlineStr"/>
-      <c r="R111" s="40" t="inlineStr"/>
+      <c r="R111" s="65" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="S111" s="40" t="inlineStr"/>
       <c r="T111" s="38" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U111" s="41" t="inlineStr">
-        <is>
-          <t>Ex: sempre confunde X com Y. Questão de confronto direto. Chi 2008.</t>
-        </is>
-      </c>
+      <c r="U111" s="41" t="inlineStr"/>
       <c r="V111" s="1" t="n"/>
     </row>
     <row r="112" ht="24" customHeight="1">
       <c r="A112" s="1" t="n"/>
-      <c r="B112" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B112" s="15" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="C112" s="37" t="inlineStr">
         <is>
-          <t>Interleaving forçado para tópicos em dificuldade_genuina</t>
-        </is>
-      </c>
-      <c r="D112" s="49" t="inlineStr">
-        <is>
-          <t>PEDAG-01</t>
-        </is>
-      </c>
-      <c r="E112" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
+          <t>POST /admin/editais + PUT /admin/topicos</t>
+        </is>
+      </c>
+      <c r="D112" s="43" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="E112" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
         </is>
       </c>
       <c r="F112" s="40" t="inlineStr"/>
@@ -8225,40 +7720,40 @@
       <c r="O112" s="40" t="inlineStr"/>
       <c r="P112" s="40" t="inlineStr"/>
       <c r="Q112" s="40" t="inlineStr"/>
-      <c r="R112" s="40" t="inlineStr"/>
+      <c r="R112" s="65" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="S112" s="40" t="inlineStr"/>
       <c r="T112" s="38" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U112" s="41" t="inlineStr">
-        <is>
-          <t>Nunca 2 sessões seguidas do tópico difícil. Kornell &amp; Bjork 2008.</t>
-        </is>
-      </c>
+      <c r="U112" s="41" t="inlineStr"/>
       <c r="V112" s="1" t="n"/>
     </row>
     <row r="113" ht="24" customHeight="1">
       <c r="A113" s="1" t="n"/>
-      <c r="B113" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B113" s="15" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="C113" s="37" t="inlineStr">
         <is>
-          <t>Campo situacao em Topico — alimenta dashboard e relatório do mentor</t>
-        </is>
-      </c>
-      <c r="D113" s="49" t="inlineStr">
-        <is>
-          <t>PEDAG-01</t>
-        </is>
-      </c>
-      <c r="E113" s="44" t="inlineStr">
-        <is>
-          <t>🗄️ Banco</t>
+          <t>PATCH /admin/cronograma/{aluno_id} — ajustar data_prova</t>
+        </is>
+      </c>
+      <c r="D113" s="43" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="E113" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
         </is>
       </c>
       <c r="F113" s="40" t="inlineStr"/>
@@ -8273,7 +7768,11 @@
       <c r="O113" s="40" t="inlineStr"/>
       <c r="P113" s="40" t="inlineStr"/>
       <c r="Q113" s="40" t="inlineStr"/>
-      <c r="R113" s="40" t="inlineStr"/>
+      <c r="R113" s="65" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="S113" s="40" t="inlineStr"/>
       <c r="T113" s="38" t="inlineStr">
         <is>
@@ -8285,24 +7784,24 @@
     </row>
     <row r="114" ht="24" customHeight="1">
       <c r="A114" s="1" t="n"/>
-      <c r="B114" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B114" s="15" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="C114" s="37" t="inlineStr">
         <is>
-          <t>Horário de estudo no relatório do mentor (timestamp das sessões)</t>
-        </is>
-      </c>
-      <c r="D114" s="49" t="inlineStr">
-        <is>
-          <t>PEDAG-01</t>
-        </is>
-      </c>
-      <c r="E114" s="68" t="inlineStr">
-        <is>
-          <t>📄 Relatório</t>
+          <t>PATCH /admin/config/ia-provider + /pesos-algoritmo (W1-W4)</t>
+        </is>
+      </c>
+      <c r="D114" s="43" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="E114" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
         </is>
       </c>
       <c r="F114" s="40" t="inlineStr"/>
@@ -8317,7 +7816,11 @@
       <c r="O114" s="40" t="inlineStr"/>
       <c r="P114" s="40" t="inlineStr"/>
       <c r="Q114" s="40" t="inlineStr"/>
-      <c r="R114" s="40" t="inlineStr"/>
+      <c r="R114" s="65" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="S114" s="40" t="inlineStr"/>
       <c r="T114" s="38" t="inlineStr">
         <is>
@@ -8326,31 +7829,31 @@
       </c>
       <c r="U114" s="41" t="inlineStr">
         <is>
-          <t>Walker 2017: sono consolida memória. Padrão visível após 4 semanas de dados.</t>
+          <t>Validar soma W1+W2+W3+W4 = 1.0</t>
         </is>
       </c>
       <c r="V114" s="1" t="n"/>
     </row>
     <row r="115" ht="24" customHeight="1">
       <c r="A115" s="1" t="n"/>
-      <c r="B115" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B115" s="15" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="C115" s="37" t="inlineStr">
         <is>
-          <t>services/simulado_generator.py — distribuição por pesos do edital</t>
-        </is>
-      </c>
-      <c r="D115" s="49" t="inlineStr">
-        <is>
-          <t>D-11</t>
-        </is>
-      </c>
-      <c r="E115" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
+          <t>GET /admin/meta/{aluno_id}/historico — déficit privado por janela</t>
+        </is>
+      </c>
+      <c r="D115" s="47" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="E115" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
         </is>
       </c>
       <c r="F115" s="40" t="inlineStr"/>
@@ -8366,7 +7869,11 @@
       <c r="P115" s="40" t="inlineStr"/>
       <c r="Q115" s="40" t="inlineStr"/>
       <c r="R115" s="40" t="inlineStr"/>
-      <c r="S115" s="40" t="inlineStr"/>
+      <c r="S115" s="65" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="T115" s="38" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
@@ -8377,19 +7884,19 @@
     </row>
     <row r="116" ht="24" customHeight="1">
       <c r="A116" s="1" t="n"/>
-      <c r="B116" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B116" s="15" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="C116" s="37" t="inlineStr">
         <is>
-          <t>POST /simulado/gerar + /responder + timer + relatório pós-simulado</t>
-        </is>
-      </c>
-      <c r="D116" s="49" t="inlineStr">
-        <is>
-          <t>D-11</t>
+          <t>GET /admin/padrao-cognitivo/{aluno_id}</t>
+        </is>
+      </c>
+      <c r="D116" s="48" t="inlineStr">
+        <is>
+          <t>D-09</t>
         </is>
       </c>
       <c r="E116" s="51" t="inlineStr">
@@ -8410,39 +7917,39 @@
       <c r="P116" s="40" t="inlineStr"/>
       <c r="Q116" s="40" t="inlineStr"/>
       <c r="R116" s="40" t="inlineStr"/>
-      <c r="S116" s="40" t="inlineStr"/>
+      <c r="S116" s="65" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="T116" s="38" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U116" s="41" t="inlineStr">
-        <is>
-          <t>Framing: chefe de fase. Csikszentmihalyi: challenge-skill balance.</t>
-        </is>
-      </c>
+      <c r="U116" s="41" t="inlineStr"/>
       <c r="V116" s="1" t="n"/>
     </row>
     <row r="117" ht="24" customHeight="1">
       <c r="A117" s="1" t="n"/>
-      <c r="B117" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B117" s="15" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="C117" s="37" t="inlineStr">
         <is>
-          <t>Simulado obrigatório automático no Modo Revisão Final</t>
-        </is>
-      </c>
-      <c r="D117" s="49" t="inlineStr">
-        <is>
-          <t>D-11</t>
-        </is>
-      </c>
-      <c r="E117" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
+          <t>GET /admin/confianca-estimativas — tópicos com estimativas não calibradas</t>
+        </is>
+      </c>
+      <c r="D117" s="55" t="inlineStr">
+        <is>
+          <t>BETA</t>
+        </is>
+      </c>
+      <c r="E117" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
         </is>
       </c>
       <c r="F117" s="40" t="inlineStr"/>
@@ -8458,7 +7965,11 @@
       <c r="P117" s="40" t="inlineStr"/>
       <c r="Q117" s="40" t="inlineStr"/>
       <c r="R117" s="40" t="inlineStr"/>
-      <c r="S117" s="40" t="inlineStr"/>
+      <c r="S117" s="65" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="T117" s="38" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
@@ -8466,31 +7977,27 @@
       </c>
       <c r="U117" s="41" t="inlineStr">
         <is>
-          <t>Penúltima semana antes da prova</t>
+          <t>Admin monitora qualidade das estimativas durante o beta</t>
         </is>
       </c>
       <c r="V117" s="1" t="n"/>
     </row>
     <row r="118" ht="24" customHeight="1">
       <c r="A118" s="1" t="n"/>
-      <c r="B118" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
+      <c r="B118" s="15" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="C118" s="37" t="inlineStr">
         <is>
-          <t>Job scraping editais por área + notificação email (D-12)</t>
-        </is>
-      </c>
-      <c r="D118" s="70" t="inlineStr">
-        <is>
-          <t>D-12</t>
-        </is>
-      </c>
-      <c r="E118" s="38" t="inlineStr">
-        <is>
-          <t>⚙️ Config</t>
+          <t>Testar painel admin completo</t>
+        </is>
+      </c>
+      <c r="D118" s="38" t="inlineStr"/>
+      <c r="E118" s="42" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
         </is>
       </c>
       <c r="F118" s="40" t="inlineStr"/>
@@ -8506,7 +8013,11 @@
       <c r="P118" s="40" t="inlineStr"/>
       <c r="Q118" s="40" t="inlineStr"/>
       <c r="R118" s="40" t="inlineStr"/>
-      <c r="S118" s="40" t="inlineStr"/>
+      <c r="S118" s="65" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="T118" s="38" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
@@ -8517,46 +8028,30 @@
     </row>
     <row r="119" ht="24" customHeight="1">
       <c r="A119" s="1" t="n"/>
-      <c r="B119" s="16" t="inlineStr">
-        <is>
-          <t>F-05</t>
-        </is>
-      </c>
-      <c r="C119" s="37" t="inlineStr">
-        <is>
-          <t>Botão criar cronograma pré-edital na notificação (D-12)</t>
-        </is>
-      </c>
-      <c r="D119" s="70" t="inlineStr">
-        <is>
-          <t>D-12</t>
-        </is>
-      </c>
-      <c r="E119" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
-        </is>
-      </c>
-      <c r="F119" s="40" t="inlineStr"/>
-      <c r="G119" s="40" t="inlineStr"/>
-      <c r="H119" s="40" t="inlineStr"/>
-      <c r="I119" s="40" t="inlineStr"/>
-      <c r="J119" s="40" t="inlineStr"/>
-      <c r="K119" s="40" t="inlineStr"/>
-      <c r="L119" s="40" t="inlineStr"/>
-      <c r="M119" s="40" t="inlineStr"/>
-      <c r="N119" s="40" t="inlineStr"/>
-      <c r="O119" s="40" t="inlineStr"/>
-      <c r="P119" s="40" t="inlineStr"/>
-      <c r="Q119" s="40" t="inlineStr"/>
-      <c r="R119" s="40" t="inlineStr"/>
-      <c r="S119" s="40" t="inlineStr"/>
-      <c r="T119" s="38" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
-        </is>
-      </c>
-      <c r="U119" s="41" t="inlineStr"/>
+      <c r="B119" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ◆  FASE 5 — Dashboard + IP + Mapa + PEDAG-01 + Simulado + Radar   ·   Semanas 14–17</t>
+        </is>
+      </c>
+      <c r="C119" s="78" t="n"/>
+      <c r="D119" s="78" t="n"/>
+      <c r="E119" s="78" t="n"/>
+      <c r="F119" s="78" t="n"/>
+      <c r="G119" s="78" t="n"/>
+      <c r="H119" s="78" t="n"/>
+      <c r="I119" s="78" t="n"/>
+      <c r="J119" s="78" t="n"/>
+      <c r="K119" s="78" t="n"/>
+      <c r="L119" s="78" t="n"/>
+      <c r="M119" s="78" t="n"/>
+      <c r="N119" s="78" t="n"/>
+      <c r="O119" s="78" t="n"/>
+      <c r="P119" s="78" t="n"/>
+      <c r="Q119" s="78" t="n"/>
+      <c r="R119" s="78" t="n"/>
+      <c r="S119" s="78" t="n"/>
+      <c r="T119" s="78" t="n"/>
+      <c r="U119" s="79" t="n"/>
       <c r="V119" s="1" t="n"/>
     </row>
     <row r="120" ht="24" customHeight="1">
@@ -8568,13 +8063,13 @@
       </c>
       <c r="C120" s="37" t="inlineStr">
         <is>
-          <t>Teste ponta a ponta: onboarding → calibração → quiz → simulado → relatório</t>
+          <t>GET /dashboard/kpis + por-materia + evolucao-mensal + ranking-erros</t>
         </is>
       </c>
       <c r="D120" s="38" t="inlineStr"/>
-      <c r="E120" s="42" t="inlineStr">
-        <is>
-          <t>✅ Teste</t>
+      <c r="E120" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
         </is>
       </c>
       <c r="F120" s="40" t="inlineStr"/>
@@ -8590,24 +8085,24 @@
       <c r="P120" s="40" t="inlineStr"/>
       <c r="Q120" s="40" t="inlineStr"/>
       <c r="R120" s="40" t="inlineStr"/>
-      <c r="S120" s="40" t="inlineStr"/>
+      <c r="S120" s="67" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="T120" s="38" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U120" s="41" t="inlineStr">
-        <is>
-          <t>Marco: produto completo validado</t>
-        </is>
-      </c>
+      <c r="U120" s="41" t="inlineStr"/>
       <c r="V120" s="1" t="n"/>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="1" t="n"/>
-      <c r="B121" s="71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ◆  FASE 6 — Inteligência Coletiva + FSRS + Gamificação Avançada   ·   Semanas 18–22 (pós-beta)</t>
+      <c r="B121" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
         </is>
       </c>
       <c r="C121" s="78" t="n"/>
@@ -8633,24 +8128,24 @@
     </row>
     <row r="122" ht="24" customHeight="1">
       <c r="A122" s="1" t="n"/>
-      <c r="B122" s="17" t="inlineStr">
-        <is>
-          <t>F-06</t>
+      <c r="B122" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
         </is>
       </c>
       <c r="C122" s="37" t="inlineStr">
         <is>
-          <t>Model: TopicoColetivo + PerfilColetivo</t>
+          <t>Relatório PDF semanal automático + link mentor 7 dias</t>
         </is>
       </c>
       <c r="D122" s="45" t="inlineStr">
         <is>
-          <t>D-IC</t>
-        </is>
-      </c>
-      <c r="E122" s="44" t="inlineStr">
-        <is>
-          <t>🗄️ Banco</t>
+          <t>L-07</t>
+        </is>
+      </c>
+      <c r="E122" s="68" t="inlineStr">
+        <is>
+          <t>📄 Relatório</t>
         </is>
       </c>
       <c r="F122" s="40" t="inlineStr"/>
@@ -8666,34 +8161,34 @@
       <c r="P122" s="40" t="inlineStr"/>
       <c r="Q122" s="40" t="inlineStr"/>
       <c r="R122" s="40" t="inlineStr"/>
-      <c r="S122" s="40" t="inlineStr"/>
-      <c r="T122" s="42" t="inlineStr">
-        <is>
-          <t>✅ Concluído</t>
-        </is>
-      </c>
-      <c r="U122" s="41" t="inlineStr">
-        <is>
-          <t>Dados agregados anônimos. Mín. 5 alunos por perfil.</t>
-        </is>
-      </c>
+      <c r="S122" s="67" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="T122" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U122" s="41" t="inlineStr"/>
       <c r="V122" s="1" t="n"/>
     </row>
     <row r="123" ht="24" customHeight="1">
       <c r="A123" s="1" t="n"/>
-      <c r="B123" s="17" t="inlineStr">
-        <is>
-          <t>F-06</t>
+      <c r="B123" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
         </is>
       </c>
       <c r="C123" s="37" t="inlineStr">
         <is>
-          <t>services/inteligencia_coletiva.py — agregação anônima</t>
-        </is>
-      </c>
-      <c r="D123" s="45" t="inlineStr">
-        <is>
-          <t>D-IC</t>
+          <t>services/indice_prontidao.py — IP = Σ(acerto × peso × decay × cobertura)</t>
+        </is>
+      </c>
+      <c r="D123" s="69" t="inlineStr">
+        <is>
+          <t>D-10</t>
         </is>
       </c>
       <c r="E123" s="52" t="inlineStr">
@@ -8722,31 +8217,31 @@
       </c>
       <c r="U123" s="41" t="inlineStr">
         <is>
-          <t>Job Celery Beat toda segunda às 3h. Nunca real-time.</t>
+          <t>0 a 100 ponderado pelo edital. Framing: diagnóstico, não pontuação.</t>
         </is>
       </c>
       <c r="V123" s="1" t="n"/>
     </row>
     <row r="124" ht="24" customHeight="1">
       <c r="A124" s="1" t="n"/>
-      <c r="B124" s="17" t="inlineStr">
-        <is>
-          <t>F-06</t>
+      <c r="B124" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
         </is>
       </c>
       <c r="C124" s="37" t="inlineStr">
         <is>
-          <t>Enriquecer cronograma novo com perfil coletivo</t>
-        </is>
-      </c>
-      <c r="D124" s="45" t="inlineStr">
-        <is>
-          <t>D-IC</t>
-        </is>
-      </c>
-      <c r="E124" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
+          <t>Mapa de progresso: tópicos coloridos por situacao — GAME-01</t>
+        </is>
+      </c>
+      <c r="D124" s="69" t="inlineStr">
+        <is>
+          <t>GAME-01</t>
+        </is>
+      </c>
+      <c r="E124" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
         </is>
       </c>
       <c r="F124" s="40" t="inlineStr"/>
@@ -8770,31 +8265,31 @@
       </c>
       <c r="U124" s="41" t="inlineStr">
         <is>
-          <t>Ajusta pesos, durações, adiciona tópicos cobrados fora do edital</t>
+          <t>Dominado=verde/Em estudo=amarelo/Não iniciado=cinza. Bandura 1997: autoeficácia por visualização.</t>
         </is>
       </c>
       <c r="V124" s="1" t="n"/>
     </row>
     <row r="125" ht="24" customHeight="1">
       <c r="A125" s="1" t="n"/>
-      <c r="B125" s="17" t="inlineStr">
-        <is>
-          <t>F-06</t>
+      <c r="B125" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
         </is>
       </c>
       <c r="C125" s="37" t="inlineStr">
         <is>
-          <t>Calibrar pesos por fonte com dados reais de acerto pós-prova</t>
-        </is>
-      </c>
-      <c r="D125" s="45" t="inlineStr">
-        <is>
-          <t>D-IC</t>
-        </is>
-      </c>
-      <c r="E125" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
+          <t>Curva de mastery: histórico semanal do IP em gráfico</t>
+        </is>
+      </c>
+      <c r="D125" s="69" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="E125" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
         </is>
       </c>
       <c r="F125" s="40" t="inlineStr"/>
@@ -8818,31 +8313,31 @@
       </c>
       <c r="U125" s="41" t="inlineStr">
         <is>
-          <t>D-IC aprende qual fonte é mais preditiva por área/banca</t>
+          <t>Dweck 2006: growth mindset — aluno vê que esforço produz progresso mensurável</t>
         </is>
       </c>
       <c r="V125" s="1" t="n"/>
     </row>
     <row r="126" ht="24" customHeight="1">
       <c r="A126" s="1" t="n"/>
-      <c r="B126" s="17" t="inlineStr">
-        <is>
-          <t>F-06</t>
+      <c r="B126" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
         </is>
       </c>
       <c r="C126" s="37" t="inlineStr">
         <is>
-          <t>Atualizar flag confianca: baixa→media→alta conforme dados chegam</t>
-        </is>
-      </c>
-      <c r="D126" s="45" t="inlineStr">
-        <is>
-          <t>D-IC</t>
-        </is>
-      </c>
-      <c r="E126" s="52" t="inlineStr">
-        <is>
-          <t>🧠 Algo</t>
+          <t>Meta de IP: aluno define IP alvo e prazo</t>
+        </is>
+      </c>
+      <c r="D126" s="69" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="E126" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
         </is>
       </c>
       <c r="F126" s="40" t="inlineStr"/>
@@ -8864,28 +8359,24 @@
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U126" s="41" t="inlineStr">
-        <is>
-          <t>Intervalo de estimativa se estreita. Pontual quando confianca=alta.</t>
-        </is>
-      </c>
+      <c r="U126" s="41" t="inlineStr"/>
       <c r="V126" s="1" t="n"/>
     </row>
     <row r="127" ht="24" customHeight="1">
       <c r="A127" s="1" t="n"/>
-      <c r="B127" s="17" t="inlineStr">
-        <is>
-          <t>F-06</t>
+      <c r="B127" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
         </is>
       </c>
       <c r="C127" s="37" t="inlineStr">
         <is>
-          <t>GET /admin/perfil-coletivo/{area}/{banca}/{cargo}</t>
-        </is>
-      </c>
-      <c r="D127" s="43" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
+          <t>Impacto da meta semanal no IP: '+X pontos se concluir esta semana'</t>
+        </is>
+      </c>
+      <c r="D127" s="69" t="inlineStr">
+        <is>
+          <t>D-10</t>
         </is>
       </c>
       <c r="E127" s="51" t="inlineStr">
@@ -8917,24 +8408,24 @@
     </row>
     <row r="128" ht="24" customHeight="1">
       <c r="A128" s="1" t="n"/>
-      <c r="B128" s="17" t="inlineStr">
-        <is>
-          <t>F-06</t>
+      <c r="B128" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
         </is>
       </c>
       <c r="C128" s="37" t="inlineStr">
         <is>
-          <t>Teste de anonimização — nenhum dado individual exposto</t>
-        </is>
-      </c>
-      <c r="D128" s="45" t="inlineStr">
-        <is>
-          <t>D-IC</t>
-        </is>
-      </c>
-      <c r="E128" s="42" t="inlineStr">
-        <is>
-          <t>✅ Teste</t>
+          <t>services/diagnostico_topico.py — classifica situacao por tópico</t>
+        </is>
+      </c>
+      <c r="D128" s="49" t="inlineStr">
+        <is>
+          <t>PEDAG-01</t>
+        </is>
+      </c>
+      <c r="E128" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
         </is>
       </c>
       <c r="F128" s="40" t="inlineStr"/>
@@ -8956,24 +8447,28 @@
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="U128" s="41" t="inlineStr"/>
+      <c r="U128" s="41" t="inlineStr">
+        <is>
+          <t>esquecimento/dificuldade_genuina/misconception_ativa/instavel/aprendendo/consolidando</t>
+        </is>
+      </c>
       <c r="V128" s="1" t="n"/>
     </row>
     <row r="129" ht="24" customHeight="1">
       <c r="A129" s="1" t="n"/>
-      <c r="B129" s="17" t="inlineStr">
-        <is>
-          <t>F-06</t>
+      <c r="B129" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
         </is>
       </c>
       <c r="C129" s="37" t="inlineStr">
         <is>
-          <t>Implementar algoritmo FSRS usando stability + difficulty acumulados</t>
-        </is>
-      </c>
-      <c r="D129" s="72" t="inlineStr">
-        <is>
-          <t>FSRS</t>
+          <t>Detecção esquecimento: acertava &gt;70%, caiu para &lt;50%</t>
+        </is>
+      </c>
+      <c r="D129" s="49" t="inlineStr">
+        <is>
+          <t>PEDAG-01</t>
         </is>
       </c>
       <c r="E129" s="52" t="inlineStr">
@@ -9002,31 +8497,31 @@
       </c>
       <c r="U129" s="41" t="inlineStr">
         <is>
-          <t>Substitui decay fixo por λ aprendido por aluno/tópico. Wozniak / Jarrett Ye 2022. Requer 3-4 meses de dados.</t>
+          <t>Resposta: revisão antecipada, intervalo reduzido à metade. VanLehn 2011.</t>
         </is>
       </c>
       <c r="V129" s="1" t="n"/>
     </row>
     <row r="130" ht="24" customHeight="1">
       <c r="A130" s="1" t="n"/>
-      <c r="B130" s="17" t="inlineStr">
-        <is>
-          <t>F-06</t>
+      <c r="B130" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
         </is>
       </c>
       <c r="C130" s="37" t="inlineStr">
         <is>
-          <t>Validar FSRS: comparar intervalo sugerido vs intervalo histórico real</t>
-        </is>
-      </c>
-      <c r="D130" s="72" t="inlineStr">
-        <is>
-          <t>FSRS</t>
-        </is>
-      </c>
-      <c r="E130" s="42" t="inlineStr">
-        <is>
-          <t>✅ Teste</t>
+          <t>Detecção dificuldade genuína: nunca atingiu &gt;60% após 2+ ciclos</t>
+        </is>
+      </c>
+      <c r="D130" s="49" t="inlineStr">
+        <is>
+          <t>PEDAG-01</t>
+        </is>
+      </c>
+      <c r="E130" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
         </is>
       </c>
       <c r="F130" s="40" t="inlineStr"/>
@@ -9050,26 +8545,26 @@
       </c>
       <c r="U130" s="41" t="inlineStr">
         <is>
-          <t>Requer mín. 10 alunos ativos com histórico completo</t>
+          <t>Resposta: diagnóstico de pré-requisito + nova explicação</t>
         </is>
       </c>
       <c r="V130" s="1" t="n"/>
     </row>
     <row r="131" ht="24" customHeight="1">
       <c r="A131" s="1" t="n"/>
-      <c r="B131" s="17" t="inlineStr">
-        <is>
-          <t>F-06</t>
+      <c r="B131" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
         </is>
       </c>
       <c r="C131" s="37" t="inlineStr">
         <is>
-          <t>Interleaving por similaridade temática — refinamento do atual</t>
-        </is>
-      </c>
-      <c r="D131" s="45" t="inlineStr">
-        <is>
-          <t>L-03</t>
+          <t>Diagnóstico de pré-requisito: verifica dependencias[] do tópico</t>
+        </is>
+      </c>
+      <c r="D131" s="49" t="inlineStr">
+        <is>
+          <t>PEDAG-01</t>
         </is>
       </c>
       <c r="E131" s="52" t="inlineStr">
@@ -9098,31 +8593,31 @@
       </c>
       <c r="U131" s="41" t="inlineStr">
         <is>
-          <t>Priorizar intercalar matérias da mesma área jurídica. Rohrer 2007 refinamento.</t>
+          <t>Se pré-req &lt; 60%: insere na fila com prioridade alta antes de continuar</t>
         </is>
       </c>
       <c r="V131" s="1" t="n"/>
     </row>
     <row r="132" ht="24" customHeight="1">
       <c r="A132" s="1" t="n"/>
-      <c r="B132" s="17" t="inlineStr">
-        <is>
-          <t>F-06</t>
+      <c r="B132" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
         </is>
       </c>
       <c r="C132" s="37" t="inlineStr">
         <is>
-          <t>Adversário calibrado: mediana dos aprovados na última edição</t>
-        </is>
-      </c>
-      <c r="D132" s="69" t="inlineStr">
-        <is>
-          <t>GAME-01</t>
-        </is>
-      </c>
-      <c r="E132" s="51" t="inlineStr">
-        <is>
-          <t>🔌 API</t>
+          <t>Geração de explicação alternativa: prompt modo=reexplicacao</t>
+        </is>
+      </c>
+      <c r="D132" s="49" t="inlineStr">
+        <is>
+          <t>PEDAG-01</t>
+        </is>
+      </c>
+      <c r="E132" s="60" t="inlineStr">
+        <is>
+          <t>🧠 IA</t>
         </is>
       </c>
       <c r="F132" s="40" t="inlineStr"/>
@@ -9146,553 +8641,1017 @@
       </c>
       <c r="U132" s="41" t="inlineStr">
         <is>
-          <t>Near-peer competition. Garcia &amp; Tor 2009. Requer dados reais de aprovados.</t>
+          <t>Outra analogia, outro ponto de entrada. Chi et al. 1989: mudança de representação.</t>
         </is>
       </c>
       <c r="V132" s="1" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n"/>
-      <c r="B133" s="1" t="n"/>
-      <c r="C133" s="1" t="n"/>
-      <c r="D133" s="1" t="n"/>
-      <c r="E133" s="1" t="n"/>
-      <c r="F133" s="1" t="n"/>
-      <c r="G133" s="1" t="n"/>
-      <c r="H133" s="1" t="n"/>
-      <c r="I133" s="1" t="n"/>
-      <c r="J133" s="1" t="n"/>
-      <c r="K133" s="1" t="n"/>
-      <c r="L133" s="1" t="n"/>
-      <c r="M133" s="1" t="n"/>
-      <c r="N133" s="1" t="n"/>
-      <c r="O133" s="1" t="n"/>
-      <c r="P133" s="1" t="n"/>
-      <c r="Q133" s="1" t="n"/>
-      <c r="R133" s="1" t="n"/>
-      <c r="S133" s="1" t="n"/>
-      <c r="T133" s="1" t="n"/>
-      <c r="U133" s="1" t="n"/>
+      <c r="B133" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
+        </is>
+      </c>
+      <c r="C133" s="37" t="inlineStr">
+        <is>
+          <t>Detecção misconception ativa: erra sempre na mesma direção específica</t>
+        </is>
+      </c>
+      <c r="D133" s="49" t="inlineStr">
+        <is>
+          <t>PEDAG-01</t>
+        </is>
+      </c>
+      <c r="E133" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
+        </is>
+      </c>
+      <c r="F133" s="40" t="inlineStr"/>
+      <c r="G133" s="40" t="inlineStr"/>
+      <c r="H133" s="40" t="inlineStr"/>
+      <c r="I133" s="40" t="inlineStr"/>
+      <c r="J133" s="40" t="inlineStr"/>
+      <c r="K133" s="40" t="inlineStr"/>
+      <c r="L133" s="40" t="inlineStr"/>
+      <c r="M133" s="40" t="inlineStr"/>
+      <c r="N133" s="40" t="inlineStr"/>
+      <c r="O133" s="40" t="inlineStr"/>
+      <c r="P133" s="40" t="inlineStr"/>
+      <c r="Q133" s="40" t="inlineStr"/>
+      <c r="R133" s="40" t="inlineStr"/>
+      <c r="S133" s="40" t="inlineStr"/>
+      <c r="T133" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U133" s="41" t="inlineStr">
+        <is>
+          <t>Ex: sempre confunde X com Y. Questão de confronto direto. Chi 2008.</t>
+        </is>
+      </c>
       <c r="V133" s="1" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n"/>
-      <c r="B134" s="73" t="inlineStr">
+      <c r="B134" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
+        </is>
+      </c>
+      <c r="C134" s="37" t="inlineStr">
+        <is>
+          <t>Interleaving forçado para tópicos em dificuldade_genuina</t>
+        </is>
+      </c>
+      <c r="D134" s="49" t="inlineStr">
+        <is>
+          <t>PEDAG-01</t>
+        </is>
+      </c>
+      <c r="E134" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
+        </is>
+      </c>
+      <c r="F134" s="40" t="inlineStr"/>
+      <c r="G134" s="40" t="inlineStr"/>
+      <c r="H134" s="40" t="inlineStr"/>
+      <c r="I134" s="40" t="inlineStr"/>
+      <c r="J134" s="40" t="inlineStr"/>
+      <c r="K134" s="40" t="inlineStr"/>
+      <c r="L134" s="40" t="inlineStr"/>
+      <c r="M134" s="40" t="inlineStr"/>
+      <c r="N134" s="40" t="inlineStr"/>
+      <c r="O134" s="40" t="inlineStr"/>
+      <c r="P134" s="40" t="inlineStr"/>
+      <c r="Q134" s="40" t="inlineStr"/>
+      <c r="R134" s="40" t="inlineStr"/>
+      <c r="S134" s="40" t="inlineStr"/>
+      <c r="T134" s="38" t="inlineStr">
         <is>
           <t>⬜ Pendente</t>
         </is>
       </c>
-      <c r="C134" s="1" t="n"/>
-      <c r="D134" s="1" t="n"/>
-      <c r="E134" s="1" t="n"/>
-      <c r="F134" s="1" t="n"/>
-      <c r="G134" s="1" t="n"/>
-      <c r="H134" s="1" t="n"/>
-      <c r="I134" s="1" t="n"/>
-      <c r="J134" s="1" t="n"/>
-      <c r="K134" s="1" t="n"/>
-      <c r="L134" s="1" t="n"/>
-      <c r="M134" s="1" t="n"/>
-      <c r="N134" s="1" t="n"/>
-      <c r="O134" s="1" t="n"/>
-      <c r="P134" s="1" t="n"/>
-      <c r="Q134" s="1" t="n"/>
-      <c r="R134" s="1" t="n"/>
-      <c r="S134" s="1" t="n"/>
-      <c r="T134" s="1" t="n"/>
-      <c r="U134" s="1" t="n"/>
+      <c r="U134" s="41" t="inlineStr">
+        <is>
+          <t>Nunca 2 sessões seguidas do tópico difícil. Kornell &amp; Bjork 2008.</t>
+        </is>
+      </c>
       <c r="V134" s="1" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n"/>
-      <c r="B135" s="20" t="inlineStr">
-        <is>
-          <t>🟡 Em andamento</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="n"/>
-      <c r="D135" s="1" t="n"/>
-      <c r="E135" s="1" t="n"/>
-      <c r="F135" s="1" t="n"/>
-      <c r="G135" s="1" t="n"/>
-      <c r="H135" s="1" t="n"/>
-      <c r="I135" s="1" t="n"/>
-      <c r="J135" s="1" t="n"/>
-      <c r="K135" s="1" t="n"/>
-      <c r="L135" s="1" t="n"/>
-      <c r="M135" s="1" t="n"/>
-      <c r="N135" s="1" t="n"/>
-      <c r="O135" s="1" t="n"/>
-      <c r="P135" s="1" t="n"/>
-      <c r="Q135" s="1" t="n"/>
-      <c r="R135" s="1" t="n"/>
-      <c r="S135" s="1" t="n"/>
-      <c r="T135" s="1" t="n"/>
-      <c r="U135" s="1" t="n"/>
+      <c r="B135" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
+        </is>
+      </c>
+      <c r="C135" s="37" t="inlineStr">
+        <is>
+          <t>Campo situacao em Topico — alimenta dashboard e relatório do mentor</t>
+        </is>
+      </c>
+      <c r="D135" s="49" t="inlineStr">
+        <is>
+          <t>PEDAG-01</t>
+        </is>
+      </c>
+      <c r="E135" s="44" t="inlineStr">
+        <is>
+          <t>🗄️ Banco</t>
+        </is>
+      </c>
+      <c r="F135" s="40" t="inlineStr"/>
+      <c r="G135" s="40" t="inlineStr"/>
+      <c r="H135" s="40" t="inlineStr"/>
+      <c r="I135" s="40" t="inlineStr"/>
+      <c r="J135" s="40" t="inlineStr"/>
+      <c r="K135" s="40" t="inlineStr"/>
+      <c r="L135" s="40" t="inlineStr"/>
+      <c r="M135" s="40" t="inlineStr"/>
+      <c r="N135" s="40" t="inlineStr"/>
+      <c r="O135" s="40" t="inlineStr"/>
+      <c r="P135" s="40" t="inlineStr"/>
+      <c r="Q135" s="40" t="inlineStr"/>
+      <c r="R135" s="40" t="inlineStr"/>
+      <c r="S135" s="40" t="inlineStr"/>
+      <c r="T135" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U135" s="41" t="inlineStr"/>
       <c r="V135" s="1" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n"/>
-      <c r="B136" s="74" t="inlineStr">
-        <is>
-          <t>✅ Concluído</t>
-        </is>
-      </c>
-      <c r="C136" s="1" t="n"/>
-      <c r="D136" s="1" t="n"/>
-      <c r="E136" s="1" t="n"/>
-      <c r="F136" s="1" t="n"/>
-      <c r="G136" s="1" t="n"/>
-      <c r="H136" s="1" t="n"/>
-      <c r="I136" s="1" t="n"/>
-      <c r="J136" s="1" t="n"/>
-      <c r="K136" s="1" t="n"/>
-      <c r="L136" s="1" t="n"/>
-      <c r="M136" s="1" t="n"/>
-      <c r="N136" s="1" t="n"/>
-      <c r="O136" s="1" t="n"/>
-      <c r="P136" s="1" t="n"/>
-      <c r="Q136" s="1" t="n"/>
-      <c r="R136" s="1" t="n"/>
-      <c r="S136" s="1" t="n"/>
-      <c r="T136" s="1" t="n"/>
-      <c r="U136" s="1" t="n"/>
+      <c r="B136" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
+        </is>
+      </c>
+      <c r="C136" s="37" t="inlineStr">
+        <is>
+          <t>Horário de estudo no relatório do mentor (timestamp das sessões)</t>
+        </is>
+      </c>
+      <c r="D136" s="49" t="inlineStr">
+        <is>
+          <t>PEDAG-01</t>
+        </is>
+      </c>
+      <c r="E136" s="68" t="inlineStr">
+        <is>
+          <t>📄 Relatório</t>
+        </is>
+      </c>
+      <c r="F136" s="40" t="inlineStr"/>
+      <c r="G136" s="40" t="inlineStr"/>
+      <c r="H136" s="40" t="inlineStr"/>
+      <c r="I136" s="40" t="inlineStr"/>
+      <c r="J136" s="40" t="inlineStr"/>
+      <c r="K136" s="40" t="inlineStr"/>
+      <c r="L136" s="40" t="inlineStr"/>
+      <c r="M136" s="40" t="inlineStr"/>
+      <c r="N136" s="40" t="inlineStr"/>
+      <c r="O136" s="40" t="inlineStr"/>
+      <c r="P136" s="40" t="inlineStr"/>
+      <c r="Q136" s="40" t="inlineStr"/>
+      <c r="R136" s="40" t="inlineStr"/>
+      <c r="S136" s="40" t="inlineStr"/>
+      <c r="T136" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U136" s="41" t="inlineStr">
+        <is>
+          <t>Walker 2017: sono consolida memória. Padrão visível após 4 semanas de dados.</t>
+        </is>
+      </c>
       <c r="V136" s="1" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n"/>
-      <c r="B137" s="19" t="inlineStr">
-        <is>
-          <t>🔴 Bloqueado</t>
-        </is>
-      </c>
-      <c r="C137" s="1" t="n"/>
-      <c r="D137" s="1" t="n"/>
-      <c r="E137" s="1" t="n"/>
-      <c r="F137" s="1" t="n"/>
-      <c r="G137" s="1" t="n"/>
-      <c r="H137" s="1" t="n"/>
-      <c r="I137" s="1" t="n"/>
-      <c r="J137" s="1" t="n"/>
-      <c r="K137" s="1" t="n"/>
-      <c r="L137" s="1" t="n"/>
-      <c r="M137" s="1" t="n"/>
-      <c r="N137" s="1" t="n"/>
-      <c r="O137" s="1" t="n"/>
-      <c r="P137" s="1" t="n"/>
-      <c r="Q137" s="1" t="n"/>
-      <c r="R137" s="1" t="n"/>
-      <c r="S137" s="1" t="n"/>
-      <c r="T137" s="1" t="n"/>
-      <c r="U137" s="1" t="n"/>
+      <c r="B137" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
+        </is>
+      </c>
+      <c r="C137" s="37" t="inlineStr">
+        <is>
+          <t>services/simulado_generator.py — distribuição por pesos do edital</t>
+        </is>
+      </c>
+      <c r="D137" s="49" t="inlineStr">
+        <is>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="E137" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
+        </is>
+      </c>
+      <c r="F137" s="40" t="inlineStr"/>
+      <c r="G137" s="40" t="inlineStr"/>
+      <c r="H137" s="40" t="inlineStr"/>
+      <c r="I137" s="40" t="inlineStr"/>
+      <c r="J137" s="40" t="inlineStr"/>
+      <c r="K137" s="40" t="inlineStr"/>
+      <c r="L137" s="40" t="inlineStr"/>
+      <c r="M137" s="40" t="inlineStr"/>
+      <c r="N137" s="40" t="inlineStr"/>
+      <c r="O137" s="40" t="inlineStr"/>
+      <c r="P137" s="40" t="inlineStr"/>
+      <c r="Q137" s="40" t="inlineStr"/>
+      <c r="R137" s="40" t="inlineStr"/>
+      <c r="S137" s="40" t="inlineStr"/>
+      <c r="T137" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U137" s="41" t="inlineStr"/>
       <c r="V137" s="1" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n"/>
-      <c r="B138" s="1" t="n"/>
-      <c r="C138" s="1" t="n"/>
-      <c r="D138" s="1" t="n"/>
-      <c r="E138" s="1" t="n"/>
-      <c r="F138" s="1" t="n"/>
-      <c r="G138" s="1" t="n"/>
-      <c r="H138" s="1" t="n"/>
-      <c r="I138" s="1" t="n"/>
-      <c r="J138" s="1" t="n"/>
-      <c r="K138" s="1" t="n"/>
-      <c r="L138" s="1" t="n"/>
-      <c r="M138" s="1" t="n"/>
-      <c r="N138" s="1" t="n"/>
-      <c r="O138" s="1" t="n"/>
-      <c r="P138" s="1" t="n"/>
-      <c r="Q138" s="1" t="n"/>
-      <c r="R138" s="1" t="n"/>
-      <c r="S138" s="1" t="n"/>
-      <c r="T138" s="1" t="n"/>
-      <c r="U138" s="1" t="n"/>
+      <c r="B138" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
+        </is>
+      </c>
+      <c r="C138" s="37" t="inlineStr">
+        <is>
+          <t>POST /simulado/gerar + /responder + timer + relatório pós-simulado</t>
+        </is>
+      </c>
+      <c r="D138" s="49" t="inlineStr">
+        <is>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="E138" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
+        </is>
+      </c>
+      <c r="F138" s="40" t="inlineStr"/>
+      <c r="G138" s="40" t="inlineStr"/>
+      <c r="H138" s="40" t="inlineStr"/>
+      <c r="I138" s="40" t="inlineStr"/>
+      <c r="J138" s="40" t="inlineStr"/>
+      <c r="K138" s="40" t="inlineStr"/>
+      <c r="L138" s="40" t="inlineStr"/>
+      <c r="M138" s="40" t="inlineStr"/>
+      <c r="N138" s="40" t="inlineStr"/>
+      <c r="O138" s="40" t="inlineStr"/>
+      <c r="P138" s="40" t="inlineStr"/>
+      <c r="Q138" s="40" t="inlineStr"/>
+      <c r="R138" s="40" t="inlineStr"/>
+      <c r="S138" s="40" t="inlineStr"/>
+      <c r="T138" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U138" s="41" t="inlineStr">
+        <is>
+          <t>Framing: chefe de fase. Csikszentmihalyi: challenge-skill balance.</t>
+        </is>
+      </c>
       <c r="V138" s="1" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n"/>
-      <c r="B139" s="1" t="n"/>
-      <c r="C139" s="1" t="n"/>
-      <c r="D139" s="1" t="n"/>
-      <c r="E139" s="1" t="n"/>
-      <c r="F139" s="1" t="n"/>
-      <c r="G139" s="1" t="n"/>
-      <c r="H139" s="1" t="n"/>
-      <c r="I139" s="1" t="n"/>
-      <c r="J139" s="1" t="n"/>
-      <c r="K139" s="1" t="n"/>
-      <c r="L139" s="1" t="n"/>
-      <c r="M139" s="1" t="n"/>
-      <c r="N139" s="1" t="n"/>
-      <c r="O139" s="1" t="n"/>
-      <c r="P139" s="1" t="n"/>
-      <c r="Q139" s="1" t="n"/>
-      <c r="R139" s="1" t="n"/>
-      <c r="S139" s="1" t="n"/>
-      <c r="T139" s="1" t="n"/>
-      <c r="U139" s="1" t="n"/>
+      <c r="B139" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
+        </is>
+      </c>
+      <c r="C139" s="37" t="inlineStr">
+        <is>
+          <t>Simulado obrigatório automático no Modo Revisão Final</t>
+        </is>
+      </c>
+      <c r="D139" s="49" t="inlineStr">
+        <is>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="E139" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
+        </is>
+      </c>
+      <c r="F139" s="40" t="inlineStr"/>
+      <c r="G139" s="40" t="inlineStr"/>
+      <c r="H139" s="40" t="inlineStr"/>
+      <c r="I139" s="40" t="inlineStr"/>
+      <c r="J139" s="40" t="inlineStr"/>
+      <c r="K139" s="40" t="inlineStr"/>
+      <c r="L139" s="40" t="inlineStr"/>
+      <c r="M139" s="40" t="inlineStr"/>
+      <c r="N139" s="40" t="inlineStr"/>
+      <c r="O139" s="40" t="inlineStr"/>
+      <c r="P139" s="40" t="inlineStr"/>
+      <c r="Q139" s="40" t="inlineStr"/>
+      <c r="R139" s="40" t="inlineStr"/>
+      <c r="S139" s="40" t="inlineStr"/>
+      <c r="T139" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U139" s="41" t="inlineStr">
+        <is>
+          <t>Penúltima semana antes da prova</t>
+        </is>
+      </c>
       <c r="V139" s="1" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n"/>
-      <c r="B140" s="1" t="n"/>
-      <c r="C140" s="1" t="n"/>
-      <c r="D140" s="1" t="n"/>
-      <c r="E140" s="1" t="n"/>
-      <c r="F140" s="1" t="n"/>
-      <c r="G140" s="1" t="n"/>
-      <c r="H140" s="1" t="n"/>
-      <c r="I140" s="1" t="n"/>
-      <c r="J140" s="1" t="n"/>
-      <c r="K140" s="1" t="n"/>
-      <c r="L140" s="1" t="n"/>
-      <c r="M140" s="1" t="n"/>
-      <c r="N140" s="1" t="n"/>
-      <c r="O140" s="1" t="n"/>
-      <c r="P140" s="1" t="n"/>
-      <c r="Q140" s="1" t="n"/>
-      <c r="R140" s="1" t="n"/>
-      <c r="S140" s="1" t="n"/>
-      <c r="T140" s="1" t="n"/>
-      <c r="U140" s="1" t="n"/>
+      <c r="B140" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
+        </is>
+      </c>
+      <c r="C140" s="37" t="inlineStr">
+        <is>
+          <t>Job scraping editais por área + notificação email (D-12)</t>
+        </is>
+      </c>
+      <c r="D140" s="70" t="inlineStr">
+        <is>
+          <t>D-12</t>
+        </is>
+      </c>
+      <c r="E140" s="38" t="inlineStr">
+        <is>
+          <t>⚙️ Config</t>
+        </is>
+      </c>
+      <c r="F140" s="40" t="inlineStr"/>
+      <c r="G140" s="40" t="inlineStr"/>
+      <c r="H140" s="40" t="inlineStr"/>
+      <c r="I140" s="40" t="inlineStr"/>
+      <c r="J140" s="40" t="inlineStr"/>
+      <c r="K140" s="40" t="inlineStr"/>
+      <c r="L140" s="40" t="inlineStr"/>
+      <c r="M140" s="40" t="inlineStr"/>
+      <c r="N140" s="40" t="inlineStr"/>
+      <c r="O140" s="40" t="inlineStr"/>
+      <c r="P140" s="40" t="inlineStr"/>
+      <c r="Q140" s="40" t="inlineStr"/>
+      <c r="R140" s="40" t="inlineStr"/>
+      <c r="S140" s="40" t="inlineStr"/>
+      <c r="T140" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U140" s="41" t="inlineStr"/>
       <c r="V140" s="1" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n"/>
-      <c r="B141" s="1" t="n"/>
-      <c r="C141" s="1" t="n"/>
-      <c r="D141" s="1" t="n"/>
-      <c r="E141" s="1" t="n"/>
-      <c r="F141" s="1" t="n"/>
-      <c r="G141" s="1" t="n"/>
-      <c r="H141" s="1" t="n"/>
-      <c r="I141" s="1" t="n"/>
-      <c r="J141" s="1" t="n"/>
-      <c r="K141" s="1" t="n"/>
-      <c r="L141" s="1" t="n"/>
-      <c r="M141" s="1" t="n"/>
-      <c r="N141" s="1" t="n"/>
-      <c r="O141" s="1" t="n"/>
-      <c r="P141" s="1" t="n"/>
-      <c r="Q141" s="1" t="n"/>
-      <c r="R141" s="1" t="n"/>
-      <c r="S141" s="1" t="n"/>
-      <c r="T141" s="1" t="n"/>
-      <c r="U141" s="1" t="n"/>
+      <c r="B141" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
+        </is>
+      </c>
+      <c r="C141" s="37" t="inlineStr">
+        <is>
+          <t>Botão criar cronograma pré-edital na notificação (D-12)</t>
+        </is>
+      </c>
+      <c r="D141" s="70" t="inlineStr">
+        <is>
+          <t>D-12</t>
+        </is>
+      </c>
+      <c r="E141" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
+        </is>
+      </c>
+      <c r="F141" s="40" t="inlineStr"/>
+      <c r="G141" s="40" t="inlineStr"/>
+      <c r="H141" s="40" t="inlineStr"/>
+      <c r="I141" s="40" t="inlineStr"/>
+      <c r="J141" s="40" t="inlineStr"/>
+      <c r="K141" s="40" t="inlineStr"/>
+      <c r="L141" s="40" t="inlineStr"/>
+      <c r="M141" s="40" t="inlineStr"/>
+      <c r="N141" s="40" t="inlineStr"/>
+      <c r="O141" s="40" t="inlineStr"/>
+      <c r="P141" s="40" t="inlineStr"/>
+      <c r="Q141" s="40" t="inlineStr"/>
+      <c r="R141" s="40" t="inlineStr"/>
+      <c r="S141" s="40" t="inlineStr"/>
+      <c r="T141" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U141" s="41" t="inlineStr"/>
       <c r="V141" s="1" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n"/>
-      <c r="B142" s="1" t="n"/>
-      <c r="C142" s="1" t="n"/>
-      <c r="D142" s="1" t="n"/>
-      <c r="E142" s="1" t="n"/>
-      <c r="F142" s="1" t="n"/>
-      <c r="G142" s="1" t="n"/>
-      <c r="H142" s="1" t="n"/>
-      <c r="I142" s="1" t="n"/>
-      <c r="J142" s="1" t="n"/>
-      <c r="K142" s="1" t="n"/>
-      <c r="L142" s="1" t="n"/>
-      <c r="M142" s="1" t="n"/>
-      <c r="N142" s="1" t="n"/>
-      <c r="O142" s="1" t="n"/>
-      <c r="P142" s="1" t="n"/>
-      <c r="Q142" s="1" t="n"/>
-      <c r="R142" s="1" t="n"/>
-      <c r="S142" s="1" t="n"/>
-      <c r="T142" s="1" t="n"/>
-      <c r="U142" s="1" t="n"/>
+      <c r="B142" s="16" t="inlineStr">
+        <is>
+          <t>F-05</t>
+        </is>
+      </c>
+      <c r="C142" s="37" t="inlineStr">
+        <is>
+          <t>Teste ponta a ponta: onboarding → calibração → quiz → simulado → relatório</t>
+        </is>
+      </c>
+      <c r="D142" s="38" t="inlineStr"/>
+      <c r="E142" s="42" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
+        </is>
+      </c>
+      <c r="F142" s="40" t="inlineStr"/>
+      <c r="G142" s="40" t="inlineStr"/>
+      <c r="H142" s="40" t="inlineStr"/>
+      <c r="I142" s="40" t="inlineStr"/>
+      <c r="J142" s="40" t="inlineStr"/>
+      <c r="K142" s="40" t="inlineStr"/>
+      <c r="L142" s="40" t="inlineStr"/>
+      <c r="M142" s="40" t="inlineStr"/>
+      <c r="N142" s="40" t="inlineStr"/>
+      <c r="O142" s="40" t="inlineStr"/>
+      <c r="P142" s="40" t="inlineStr"/>
+      <c r="Q142" s="40" t="inlineStr"/>
+      <c r="R142" s="40" t="inlineStr"/>
+      <c r="S142" s="40" t="inlineStr"/>
+      <c r="T142" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U142" s="41" t="inlineStr">
+        <is>
+          <t>Marco: produto completo validado</t>
+        </is>
+      </c>
       <c r="V142" s="1" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n"/>
-      <c r="B143" s="1" t="n"/>
-      <c r="C143" s="1" t="n"/>
-      <c r="D143" s="1" t="n"/>
-      <c r="E143" s="1" t="n"/>
-      <c r="F143" s="1" t="n"/>
-      <c r="G143" s="1" t="n"/>
-      <c r="H143" s="1" t="n"/>
-      <c r="I143" s="1" t="n"/>
-      <c r="J143" s="1" t="n"/>
-      <c r="K143" s="1" t="n"/>
-      <c r="L143" s="1" t="n"/>
-      <c r="M143" s="1" t="n"/>
-      <c r="N143" s="1" t="n"/>
-      <c r="O143" s="1" t="n"/>
-      <c r="P143" s="1" t="n"/>
-      <c r="Q143" s="1" t="n"/>
-      <c r="R143" s="1" t="n"/>
-      <c r="S143" s="1" t="n"/>
-      <c r="T143" s="1" t="n"/>
-      <c r="U143" s="1" t="n"/>
+      <c r="B143" s="71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ◆  FASE 6 — Inteligência Coletiva + FSRS + Gamificação Avançada   ·   Semanas 18–22 (pós-beta)</t>
+        </is>
+      </c>
+      <c r="C143" s="78" t="n"/>
+      <c r="D143" s="78" t="n"/>
+      <c r="E143" s="78" t="n"/>
+      <c r="F143" s="78" t="n"/>
+      <c r="G143" s="78" t="n"/>
+      <c r="H143" s="78" t="n"/>
+      <c r="I143" s="78" t="n"/>
+      <c r="J143" s="78" t="n"/>
+      <c r="K143" s="78" t="n"/>
+      <c r="L143" s="78" t="n"/>
+      <c r="M143" s="78" t="n"/>
+      <c r="N143" s="78" t="n"/>
+      <c r="O143" s="78" t="n"/>
+      <c r="P143" s="78" t="n"/>
+      <c r="Q143" s="78" t="n"/>
+      <c r="R143" s="78" t="n"/>
+      <c r="S143" s="78" t="n"/>
+      <c r="T143" s="78" t="n"/>
+      <c r="U143" s="79" t="n"/>
       <c r="V143" s="1" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n"/>
-      <c r="B144" s="1" t="n"/>
-      <c r="C144" s="1" t="n"/>
-      <c r="D144" s="1" t="n"/>
-      <c r="E144" s="1" t="n"/>
-      <c r="F144" s="1" t="n"/>
-      <c r="G144" s="1" t="n"/>
-      <c r="H144" s="1" t="n"/>
-      <c r="I144" s="1" t="n"/>
-      <c r="J144" s="1" t="n"/>
-      <c r="K144" s="1" t="n"/>
-      <c r="L144" s="1" t="n"/>
-      <c r="M144" s="1" t="n"/>
-      <c r="N144" s="1" t="n"/>
-      <c r="O144" s="1" t="n"/>
-      <c r="P144" s="1" t="n"/>
-      <c r="Q144" s="1" t="n"/>
-      <c r="R144" s="1" t="n"/>
-      <c r="S144" s="1" t="n"/>
-      <c r="T144" s="1" t="n"/>
-      <c r="U144" s="1" t="n"/>
+      <c r="B144" s="17" t="inlineStr">
+        <is>
+          <t>F-06</t>
+        </is>
+      </c>
+      <c r="C144" s="37" t="inlineStr">
+        <is>
+          <t>Model: TopicoColetivo + PerfilColetivo</t>
+        </is>
+      </c>
+      <c r="D144" s="45" t="inlineStr">
+        <is>
+          <t>D-IC</t>
+        </is>
+      </c>
+      <c r="E144" s="44" t="inlineStr">
+        <is>
+          <t>🗄️ Banco</t>
+        </is>
+      </c>
+      <c r="F144" s="40" t="inlineStr"/>
+      <c r="G144" s="40" t="inlineStr"/>
+      <c r="H144" s="40" t="inlineStr"/>
+      <c r="I144" s="40" t="inlineStr"/>
+      <c r="J144" s="40" t="inlineStr"/>
+      <c r="K144" s="40" t="inlineStr"/>
+      <c r="L144" s="40" t="inlineStr"/>
+      <c r="M144" s="40" t="inlineStr"/>
+      <c r="N144" s="40" t="inlineStr"/>
+      <c r="O144" s="40" t="inlineStr"/>
+      <c r="P144" s="40" t="inlineStr"/>
+      <c r="Q144" s="40" t="inlineStr"/>
+      <c r="R144" s="40" t="inlineStr"/>
+      <c r="S144" s="40" t="inlineStr"/>
+      <c r="T144" s="42" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
+        </is>
+      </c>
+      <c r="U144" s="41" t="inlineStr">
+        <is>
+          <t>Dados agregados anônimos. Mín. 5 alunos por perfil.</t>
+        </is>
+      </c>
       <c r="V144" s="1" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n"/>
-      <c r="B145" s="1" t="n"/>
-      <c r="C145" s="1" t="n"/>
-      <c r="D145" s="1" t="n"/>
-      <c r="E145" s="1" t="n"/>
-      <c r="F145" s="1" t="n"/>
-      <c r="G145" s="1" t="n"/>
-      <c r="H145" s="1" t="n"/>
-      <c r="I145" s="1" t="n"/>
-      <c r="J145" s="1" t="n"/>
-      <c r="K145" s="1" t="n"/>
-      <c r="L145" s="1" t="n"/>
-      <c r="M145" s="1" t="n"/>
-      <c r="N145" s="1" t="n"/>
-      <c r="O145" s="1" t="n"/>
-      <c r="P145" s="1" t="n"/>
-      <c r="Q145" s="1" t="n"/>
-      <c r="R145" s="1" t="n"/>
-      <c r="S145" s="1" t="n"/>
-      <c r="T145" s="1" t="n"/>
-      <c r="U145" s="1" t="n"/>
+      <c r="B145" s="17" t="inlineStr">
+        <is>
+          <t>F-06</t>
+        </is>
+      </c>
+      <c r="C145" s="37" t="inlineStr">
+        <is>
+          <t>services/inteligencia_coletiva.py — agregação anônima</t>
+        </is>
+      </c>
+      <c r="D145" s="45" t="inlineStr">
+        <is>
+          <t>D-IC</t>
+        </is>
+      </c>
+      <c r="E145" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
+        </is>
+      </c>
+      <c r="F145" s="40" t="inlineStr"/>
+      <c r="G145" s="40" t="inlineStr"/>
+      <c r="H145" s="40" t="inlineStr"/>
+      <c r="I145" s="40" t="inlineStr"/>
+      <c r="J145" s="40" t="inlineStr"/>
+      <c r="K145" s="40" t="inlineStr"/>
+      <c r="L145" s="40" t="inlineStr"/>
+      <c r="M145" s="40" t="inlineStr"/>
+      <c r="N145" s="40" t="inlineStr"/>
+      <c r="O145" s="40" t="inlineStr"/>
+      <c r="P145" s="40" t="inlineStr"/>
+      <c r="Q145" s="40" t="inlineStr"/>
+      <c r="R145" s="40" t="inlineStr"/>
+      <c r="S145" s="40" t="inlineStr"/>
+      <c r="T145" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U145" s="41" t="inlineStr">
+        <is>
+          <t>Job Celery Beat toda segunda às 3h. Nunca real-time.</t>
+        </is>
+      </c>
       <c r="V145" s="1" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n"/>
-      <c r="B146" s="1" t="n"/>
-      <c r="C146" s="1" t="n"/>
-      <c r="D146" s="1" t="n"/>
-      <c r="E146" s="1" t="n"/>
-      <c r="F146" s="1" t="n"/>
-      <c r="G146" s="1" t="n"/>
-      <c r="H146" s="1" t="n"/>
-      <c r="I146" s="1" t="n"/>
-      <c r="J146" s="1" t="n"/>
-      <c r="K146" s="1" t="n"/>
-      <c r="L146" s="1" t="n"/>
-      <c r="M146" s="1" t="n"/>
-      <c r="N146" s="1" t="n"/>
-      <c r="O146" s="1" t="n"/>
-      <c r="P146" s="1" t="n"/>
-      <c r="Q146" s="1" t="n"/>
-      <c r="R146" s="1" t="n"/>
-      <c r="S146" s="1" t="n"/>
-      <c r="T146" s="1" t="n"/>
-      <c r="U146" s="1" t="n"/>
+      <c r="B146" s="17" t="inlineStr">
+        <is>
+          <t>F-06</t>
+        </is>
+      </c>
+      <c r="C146" s="37" t="inlineStr">
+        <is>
+          <t>Enriquecer cronograma novo com perfil coletivo</t>
+        </is>
+      </c>
+      <c r="D146" s="45" t="inlineStr">
+        <is>
+          <t>D-IC</t>
+        </is>
+      </c>
+      <c r="E146" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
+        </is>
+      </c>
+      <c r="F146" s="40" t="inlineStr"/>
+      <c r="G146" s="40" t="inlineStr"/>
+      <c r="H146" s="40" t="inlineStr"/>
+      <c r="I146" s="40" t="inlineStr"/>
+      <c r="J146" s="40" t="inlineStr"/>
+      <c r="K146" s="40" t="inlineStr"/>
+      <c r="L146" s="40" t="inlineStr"/>
+      <c r="M146" s="40" t="inlineStr"/>
+      <c r="N146" s="40" t="inlineStr"/>
+      <c r="O146" s="40" t="inlineStr"/>
+      <c r="P146" s="40" t="inlineStr"/>
+      <c r="Q146" s="40" t="inlineStr"/>
+      <c r="R146" s="40" t="inlineStr"/>
+      <c r="S146" s="40" t="inlineStr"/>
+      <c r="T146" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U146" s="41" t="inlineStr">
+        <is>
+          <t>Ajusta pesos, durações, adiciona tópicos cobrados fora do edital</t>
+        </is>
+      </c>
       <c r="V146" s="1" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n"/>
-      <c r="B147" s="1" t="n"/>
-      <c r="C147" s="1" t="n"/>
-      <c r="D147" s="1" t="n"/>
-      <c r="E147" s="1" t="n"/>
-      <c r="F147" s="1" t="n"/>
-      <c r="G147" s="1" t="n"/>
-      <c r="H147" s="1" t="n"/>
-      <c r="I147" s="1" t="n"/>
-      <c r="J147" s="1" t="n"/>
-      <c r="K147" s="1" t="n"/>
-      <c r="L147" s="1" t="n"/>
-      <c r="M147" s="1" t="n"/>
-      <c r="N147" s="1" t="n"/>
-      <c r="O147" s="1" t="n"/>
-      <c r="P147" s="1" t="n"/>
-      <c r="Q147" s="1" t="n"/>
-      <c r="R147" s="1" t="n"/>
-      <c r="S147" s="1" t="n"/>
-      <c r="T147" s="1" t="n"/>
-      <c r="U147" s="1" t="n"/>
+      <c r="B147" s="17" t="inlineStr">
+        <is>
+          <t>F-06</t>
+        </is>
+      </c>
+      <c r="C147" s="37" t="inlineStr">
+        <is>
+          <t>Calibrar pesos por fonte com dados reais de acerto pós-prova</t>
+        </is>
+      </c>
+      <c r="D147" s="45" t="inlineStr">
+        <is>
+          <t>D-IC</t>
+        </is>
+      </c>
+      <c r="E147" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
+        </is>
+      </c>
+      <c r="F147" s="40" t="inlineStr"/>
+      <c r="G147" s="40" t="inlineStr"/>
+      <c r="H147" s="40" t="inlineStr"/>
+      <c r="I147" s="40" t="inlineStr"/>
+      <c r="J147" s="40" t="inlineStr"/>
+      <c r="K147" s="40" t="inlineStr"/>
+      <c r="L147" s="40" t="inlineStr"/>
+      <c r="M147" s="40" t="inlineStr"/>
+      <c r="N147" s="40" t="inlineStr"/>
+      <c r="O147" s="40" t="inlineStr"/>
+      <c r="P147" s="40" t="inlineStr"/>
+      <c r="Q147" s="40" t="inlineStr"/>
+      <c r="R147" s="40" t="inlineStr"/>
+      <c r="S147" s="40" t="inlineStr"/>
+      <c r="T147" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U147" s="41" t="inlineStr">
+        <is>
+          <t>D-IC aprende qual fonte é mais preditiva por área/banca</t>
+        </is>
+      </c>
       <c r="V147" s="1" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n"/>
-      <c r="B148" s="1" t="n"/>
-      <c r="C148" s="1" t="n"/>
-      <c r="D148" s="1" t="n"/>
-      <c r="E148" s="1" t="n"/>
-      <c r="F148" s="1" t="n"/>
-      <c r="G148" s="1" t="n"/>
-      <c r="H148" s="1" t="n"/>
-      <c r="I148" s="1" t="n"/>
-      <c r="J148" s="1" t="n"/>
-      <c r="K148" s="1" t="n"/>
-      <c r="L148" s="1" t="n"/>
-      <c r="M148" s="1" t="n"/>
-      <c r="N148" s="1" t="n"/>
-      <c r="O148" s="1" t="n"/>
-      <c r="P148" s="1" t="n"/>
-      <c r="Q148" s="1" t="n"/>
-      <c r="R148" s="1" t="n"/>
-      <c r="S148" s="1" t="n"/>
-      <c r="T148" s="1" t="n"/>
-      <c r="U148" s="1" t="n"/>
+      <c r="B148" s="17" t="inlineStr">
+        <is>
+          <t>F-06</t>
+        </is>
+      </c>
+      <c r="C148" s="37" t="inlineStr">
+        <is>
+          <t>Atualizar flag confianca: baixa→media→alta conforme dados chegam</t>
+        </is>
+      </c>
+      <c r="D148" s="45" t="inlineStr">
+        <is>
+          <t>D-IC</t>
+        </is>
+      </c>
+      <c r="E148" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
+        </is>
+      </c>
+      <c r="F148" s="40" t="inlineStr"/>
+      <c r="G148" s="40" t="inlineStr"/>
+      <c r="H148" s="40" t="inlineStr"/>
+      <c r="I148" s="40" t="inlineStr"/>
+      <c r="J148" s="40" t="inlineStr"/>
+      <c r="K148" s="40" t="inlineStr"/>
+      <c r="L148" s="40" t="inlineStr"/>
+      <c r="M148" s="40" t="inlineStr"/>
+      <c r="N148" s="40" t="inlineStr"/>
+      <c r="O148" s="40" t="inlineStr"/>
+      <c r="P148" s="40" t="inlineStr"/>
+      <c r="Q148" s="40" t="inlineStr"/>
+      <c r="R148" s="40" t="inlineStr"/>
+      <c r="S148" s="40" t="inlineStr"/>
+      <c r="T148" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U148" s="41" t="inlineStr">
+        <is>
+          <t>Intervalo de estimativa se estreita. Pontual quando confianca=alta.</t>
+        </is>
+      </c>
       <c r="V148" s="1" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n"/>
-      <c r="B149" s="1" t="n"/>
-      <c r="C149" s="1" t="n"/>
-      <c r="D149" s="1" t="n"/>
-      <c r="E149" s="1" t="n"/>
-      <c r="F149" s="1" t="n"/>
-      <c r="G149" s="1" t="n"/>
-      <c r="H149" s="1" t="n"/>
-      <c r="I149" s="1" t="n"/>
-      <c r="J149" s="1" t="n"/>
-      <c r="K149" s="1" t="n"/>
-      <c r="L149" s="1" t="n"/>
-      <c r="M149" s="1" t="n"/>
-      <c r="N149" s="1" t="n"/>
-      <c r="O149" s="1" t="n"/>
-      <c r="P149" s="1" t="n"/>
-      <c r="Q149" s="1" t="n"/>
-      <c r="R149" s="1" t="n"/>
-      <c r="S149" s="1" t="n"/>
-      <c r="T149" s="1" t="n"/>
-      <c r="U149" s="1" t="n"/>
+      <c r="B149" s="17" t="inlineStr">
+        <is>
+          <t>F-06</t>
+        </is>
+      </c>
+      <c r="C149" s="37" t="inlineStr">
+        <is>
+          <t>GET /admin/perfil-coletivo/{area}/{banca}/{cargo}</t>
+        </is>
+      </c>
+      <c r="D149" s="43" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="E149" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
+        </is>
+      </c>
+      <c r="F149" s="40" t="inlineStr"/>
+      <c r="G149" s="40" t="inlineStr"/>
+      <c r="H149" s="40" t="inlineStr"/>
+      <c r="I149" s="40" t="inlineStr"/>
+      <c r="J149" s="40" t="inlineStr"/>
+      <c r="K149" s="40" t="inlineStr"/>
+      <c r="L149" s="40" t="inlineStr"/>
+      <c r="M149" s="40" t="inlineStr"/>
+      <c r="N149" s="40" t="inlineStr"/>
+      <c r="O149" s="40" t="inlineStr"/>
+      <c r="P149" s="40" t="inlineStr"/>
+      <c r="Q149" s="40" t="inlineStr"/>
+      <c r="R149" s="40" t="inlineStr"/>
+      <c r="S149" s="40" t="inlineStr"/>
+      <c r="T149" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U149" s="41" t="inlineStr"/>
       <c r="V149" s="1" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n"/>
-      <c r="B150" s="1" t="n"/>
-      <c r="C150" s="1" t="n"/>
-      <c r="D150" s="1" t="n"/>
-      <c r="E150" s="1" t="n"/>
-      <c r="F150" s="1" t="n"/>
-      <c r="G150" s="1" t="n"/>
-      <c r="H150" s="1" t="n"/>
-      <c r="I150" s="1" t="n"/>
-      <c r="J150" s="1" t="n"/>
-      <c r="K150" s="1" t="n"/>
-      <c r="L150" s="1" t="n"/>
-      <c r="M150" s="1" t="n"/>
-      <c r="N150" s="1" t="n"/>
-      <c r="O150" s="1" t="n"/>
-      <c r="P150" s="1" t="n"/>
-      <c r="Q150" s="1" t="n"/>
-      <c r="R150" s="1" t="n"/>
-      <c r="S150" s="1" t="n"/>
-      <c r="T150" s="1" t="n"/>
-      <c r="U150" s="1" t="n"/>
+      <c r="B150" s="17" t="inlineStr">
+        <is>
+          <t>F-06</t>
+        </is>
+      </c>
+      <c r="C150" s="37" t="inlineStr">
+        <is>
+          <t>Teste de anonimização — nenhum dado individual exposto</t>
+        </is>
+      </c>
+      <c r="D150" s="45" t="inlineStr">
+        <is>
+          <t>D-IC</t>
+        </is>
+      </c>
+      <c r="E150" s="42" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
+        </is>
+      </c>
+      <c r="F150" s="40" t="inlineStr"/>
+      <c r="G150" s="40" t="inlineStr"/>
+      <c r="H150" s="40" t="inlineStr"/>
+      <c r="I150" s="40" t="inlineStr"/>
+      <c r="J150" s="40" t="inlineStr"/>
+      <c r="K150" s="40" t="inlineStr"/>
+      <c r="L150" s="40" t="inlineStr"/>
+      <c r="M150" s="40" t="inlineStr"/>
+      <c r="N150" s="40" t="inlineStr"/>
+      <c r="O150" s="40" t="inlineStr"/>
+      <c r="P150" s="40" t="inlineStr"/>
+      <c r="Q150" s="40" t="inlineStr"/>
+      <c r="R150" s="40" t="inlineStr"/>
+      <c r="S150" s="40" t="inlineStr"/>
+      <c r="T150" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U150" s="41" t="inlineStr"/>
       <c r="V150" s="1" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n"/>
-      <c r="B151" s="1" t="n"/>
-      <c r="C151" s="1" t="n"/>
-      <c r="D151" s="1" t="n"/>
-      <c r="E151" s="1" t="n"/>
-      <c r="F151" s="1" t="n"/>
-      <c r="G151" s="1" t="n"/>
-      <c r="H151" s="1" t="n"/>
-      <c r="I151" s="1" t="n"/>
-      <c r="J151" s="1" t="n"/>
-      <c r="K151" s="1" t="n"/>
-      <c r="L151" s="1" t="n"/>
-      <c r="M151" s="1" t="n"/>
-      <c r="N151" s="1" t="n"/>
-      <c r="O151" s="1" t="n"/>
-      <c r="P151" s="1" t="n"/>
-      <c r="Q151" s="1" t="n"/>
-      <c r="R151" s="1" t="n"/>
-      <c r="S151" s="1" t="n"/>
-      <c r="T151" s="1" t="n"/>
-      <c r="U151" s="1" t="n"/>
+      <c r="B151" s="17" t="inlineStr">
+        <is>
+          <t>F-06</t>
+        </is>
+      </c>
+      <c r="C151" s="37" t="inlineStr">
+        <is>
+          <t>Implementar algoritmo FSRS usando stability + difficulty acumulados</t>
+        </is>
+      </c>
+      <c r="D151" s="72" t="inlineStr">
+        <is>
+          <t>FSRS</t>
+        </is>
+      </c>
+      <c r="E151" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
+        </is>
+      </c>
+      <c r="F151" s="40" t="inlineStr"/>
+      <c r="G151" s="40" t="inlineStr"/>
+      <c r="H151" s="40" t="inlineStr"/>
+      <c r="I151" s="40" t="inlineStr"/>
+      <c r="J151" s="40" t="inlineStr"/>
+      <c r="K151" s="40" t="inlineStr"/>
+      <c r="L151" s="40" t="inlineStr"/>
+      <c r="M151" s="40" t="inlineStr"/>
+      <c r="N151" s="40" t="inlineStr"/>
+      <c r="O151" s="40" t="inlineStr"/>
+      <c r="P151" s="40" t="inlineStr"/>
+      <c r="Q151" s="40" t="inlineStr"/>
+      <c r="R151" s="40" t="inlineStr"/>
+      <c r="S151" s="40" t="inlineStr"/>
+      <c r="T151" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U151" s="41" t="inlineStr">
+        <is>
+          <t>Substitui decay fixo por λ aprendido por aluno/tópico. Wozniak / Jarrett Ye 2022. Requer 3-4 meses de dados.</t>
+        </is>
+      </c>
       <c r="V151" s="1" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n"/>
-      <c r="B152" s="1" t="n"/>
-      <c r="C152" s="1" t="n"/>
-      <c r="D152" s="1" t="n"/>
-      <c r="E152" s="1" t="n"/>
-      <c r="F152" s="1" t="n"/>
-      <c r="G152" s="1" t="n"/>
-      <c r="H152" s="1" t="n"/>
-      <c r="I152" s="1" t="n"/>
-      <c r="J152" s="1" t="n"/>
-      <c r="K152" s="1" t="n"/>
-      <c r="L152" s="1" t="n"/>
-      <c r="M152" s="1" t="n"/>
-      <c r="N152" s="1" t="n"/>
-      <c r="O152" s="1" t="n"/>
-      <c r="P152" s="1" t="n"/>
-      <c r="Q152" s="1" t="n"/>
-      <c r="R152" s="1" t="n"/>
-      <c r="S152" s="1" t="n"/>
-      <c r="T152" s="1" t="n"/>
-      <c r="U152" s="1" t="n"/>
+      <c r="B152" s="17" t="inlineStr">
+        <is>
+          <t>F-06</t>
+        </is>
+      </c>
+      <c r="C152" s="37" t="inlineStr">
+        <is>
+          <t>Validar FSRS: comparar intervalo sugerido vs intervalo histórico real</t>
+        </is>
+      </c>
+      <c r="D152" s="72" t="inlineStr">
+        <is>
+          <t>FSRS</t>
+        </is>
+      </c>
+      <c r="E152" s="42" t="inlineStr">
+        <is>
+          <t>✅ Teste</t>
+        </is>
+      </c>
+      <c r="F152" s="40" t="inlineStr"/>
+      <c r="G152" s="40" t="inlineStr"/>
+      <c r="H152" s="40" t="inlineStr"/>
+      <c r="I152" s="40" t="inlineStr"/>
+      <c r="J152" s="40" t="inlineStr"/>
+      <c r="K152" s="40" t="inlineStr"/>
+      <c r="L152" s="40" t="inlineStr"/>
+      <c r="M152" s="40" t="inlineStr"/>
+      <c r="N152" s="40" t="inlineStr"/>
+      <c r="O152" s="40" t="inlineStr"/>
+      <c r="P152" s="40" t="inlineStr"/>
+      <c r="Q152" s="40" t="inlineStr"/>
+      <c r="R152" s="40" t="inlineStr"/>
+      <c r="S152" s="40" t="inlineStr"/>
+      <c r="T152" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U152" s="41" t="inlineStr">
+        <is>
+          <t>Requer mín. 10 alunos ativos com histórico completo</t>
+        </is>
+      </c>
       <c r="V152" s="1" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n"/>
-      <c r="B153" s="1" t="n"/>
-      <c r="C153" s="1" t="n"/>
-      <c r="D153" s="1" t="n"/>
-      <c r="E153" s="1" t="n"/>
-      <c r="F153" s="1" t="n"/>
-      <c r="G153" s="1" t="n"/>
-      <c r="H153" s="1" t="n"/>
-      <c r="I153" s="1" t="n"/>
-      <c r="J153" s="1" t="n"/>
-      <c r="K153" s="1" t="n"/>
-      <c r="L153" s="1" t="n"/>
-      <c r="M153" s="1" t="n"/>
-      <c r="N153" s="1" t="n"/>
-      <c r="O153" s="1" t="n"/>
-      <c r="P153" s="1" t="n"/>
-      <c r="Q153" s="1" t="n"/>
-      <c r="R153" s="1" t="n"/>
-      <c r="S153" s="1" t="n"/>
-      <c r="T153" s="1" t="n"/>
-      <c r="U153" s="1" t="n"/>
+      <c r="B153" s="17" t="inlineStr">
+        <is>
+          <t>F-06</t>
+        </is>
+      </c>
+      <c r="C153" s="37" t="inlineStr">
+        <is>
+          <t>Interleaving por similaridade temática — refinamento do atual</t>
+        </is>
+      </c>
+      <c r="D153" s="45" t="inlineStr">
+        <is>
+          <t>L-03</t>
+        </is>
+      </c>
+      <c r="E153" s="52" t="inlineStr">
+        <is>
+          <t>🧠 Algo</t>
+        </is>
+      </c>
+      <c r="F153" s="40" t="inlineStr"/>
+      <c r="G153" s="40" t="inlineStr"/>
+      <c r="H153" s="40" t="inlineStr"/>
+      <c r="I153" s="40" t="inlineStr"/>
+      <c r="J153" s="40" t="inlineStr"/>
+      <c r="K153" s="40" t="inlineStr"/>
+      <c r="L153" s="40" t="inlineStr"/>
+      <c r="M153" s="40" t="inlineStr"/>
+      <c r="N153" s="40" t="inlineStr"/>
+      <c r="O153" s="40" t="inlineStr"/>
+      <c r="P153" s="40" t="inlineStr"/>
+      <c r="Q153" s="40" t="inlineStr"/>
+      <c r="R153" s="40" t="inlineStr"/>
+      <c r="S153" s="40" t="inlineStr"/>
+      <c r="T153" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U153" s="41" t="inlineStr">
+        <is>
+          <t>Priorizar intercalar matérias da mesma área jurídica. Rohrer 2007 refinamento.</t>
+        </is>
+      </c>
       <c r="V153" s="1" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n"/>
-      <c r="B154" s="1" t="n"/>
-      <c r="C154" s="1" t="n"/>
-      <c r="D154" s="1" t="n"/>
-      <c r="E154" s="1" t="n"/>
-      <c r="F154" s="1" t="n"/>
-      <c r="G154" s="1" t="n"/>
-      <c r="H154" s="1" t="n"/>
-      <c r="I154" s="1" t="n"/>
-      <c r="J154" s="1" t="n"/>
-      <c r="K154" s="1" t="n"/>
-      <c r="L154" s="1" t="n"/>
-      <c r="M154" s="1" t="n"/>
-      <c r="N154" s="1" t="n"/>
-      <c r="O154" s="1" t="n"/>
-      <c r="P154" s="1" t="n"/>
-      <c r="Q154" s="1" t="n"/>
-      <c r="R154" s="1" t="n"/>
-      <c r="S154" s="1" t="n"/>
-      <c r="T154" s="1" t="n"/>
-      <c r="U154" s="1" t="n"/>
+      <c r="B154" s="17" t="inlineStr">
+        <is>
+          <t>F-06</t>
+        </is>
+      </c>
+      <c r="C154" s="37" t="inlineStr">
+        <is>
+          <t>Adversário calibrado: mediana dos aprovados na última edição</t>
+        </is>
+      </c>
+      <c r="D154" s="69" t="inlineStr">
+        <is>
+          <t>GAME-01</t>
+        </is>
+      </c>
+      <c r="E154" s="51" t="inlineStr">
+        <is>
+          <t>🔌 API</t>
+        </is>
+      </c>
+      <c r="F154" s="40" t="inlineStr"/>
+      <c r="G154" s="40" t="inlineStr"/>
+      <c r="H154" s="40" t="inlineStr"/>
+      <c r="I154" s="40" t="inlineStr"/>
+      <c r="J154" s="40" t="inlineStr"/>
+      <c r="K154" s="40" t="inlineStr"/>
+      <c r="L154" s="40" t="inlineStr"/>
+      <c r="M154" s="40" t="inlineStr"/>
+      <c r="N154" s="40" t="inlineStr"/>
+      <c r="O154" s="40" t="inlineStr"/>
+      <c r="P154" s="40" t="inlineStr"/>
+      <c r="Q154" s="40" t="inlineStr"/>
+      <c r="R154" s="40" t="inlineStr"/>
+      <c r="S154" s="40" t="inlineStr"/>
+      <c r="T154" s="38" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
+      <c r="U154" s="41" t="inlineStr">
+        <is>
+          <t>Near-peer competition. Garcia &amp; Tor 2009. Requer dados reais de aprovados.</t>
+        </is>
+      </c>
       <c r="V154" s="1" t="n"/>
     </row>
     <row r="155">
@@ -9721,7 +9680,11 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n"/>
-      <c r="B156" s="1" t="n"/>
+      <c r="B156" s="73" t="inlineStr">
+        <is>
+          <t>⬜ Pendente</t>
+        </is>
+      </c>
       <c r="C156" s="1" t="n"/>
       <c r="D156" s="1" t="n"/>
       <c r="E156" s="1" t="n"/>
@@ -9745,7 +9708,11 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n"/>
-      <c r="B157" s="1" t="n"/>
+      <c r="B157" s="20" t="inlineStr">
+        <is>
+          <t>🟡 Em andamento</t>
+        </is>
+      </c>
       <c r="C157" s="1" t="n"/>
       <c r="D157" s="1" t="n"/>
       <c r="E157" s="1" t="n"/>
@@ -9769,7 +9736,11 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n"/>
-      <c r="B158" s="1" t="n"/>
+      <c r="B158" s="74" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
+        </is>
+      </c>
       <c r="C158" s="1" t="n"/>
       <c r="D158" s="1" t="n"/>
       <c r="E158" s="1" t="n"/>
@@ -9793,7 +9764,11 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n"/>
-      <c r="B159" s="1" t="n"/>
+      <c r="B159" s="19" t="inlineStr">
+        <is>
+          <t>🔴 Bloqueado</t>
+        </is>
+      </c>
       <c r="C159" s="1" t="n"/>
       <c r="D159" s="1" t="n"/>
       <c r="E159" s="1" t="n"/>
@@ -12214,6 +12189,534 @@
       <c r="T259" s="1" t="n"/>
       <c r="U259" s="1" t="n"/>
       <c r="V259" s="1" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n"/>
+      <c r="B260" s="1" t="n"/>
+      <c r="C260" s="1" t="n"/>
+      <c r="D260" s="1" t="n"/>
+      <c r="E260" s="1" t="n"/>
+      <c r="F260" s="1" t="n"/>
+      <c r="G260" s="1" t="n"/>
+      <c r="H260" s="1" t="n"/>
+      <c r="I260" s="1" t="n"/>
+      <c r="J260" s="1" t="n"/>
+      <c r="K260" s="1" t="n"/>
+      <c r="L260" s="1" t="n"/>
+      <c r="M260" s="1" t="n"/>
+      <c r="N260" s="1" t="n"/>
+      <c r="O260" s="1" t="n"/>
+      <c r="P260" s="1" t="n"/>
+      <c r="Q260" s="1" t="n"/>
+      <c r="R260" s="1" t="n"/>
+      <c r="S260" s="1" t="n"/>
+      <c r="T260" s="1" t="n"/>
+      <c r="U260" s="1" t="n"/>
+      <c r="V260" s="1" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n"/>
+      <c r="B261" s="1" t="n"/>
+      <c r="C261" s="1" t="n"/>
+      <c r="D261" s="1" t="n"/>
+      <c r="E261" s="1" t="n"/>
+      <c r="F261" s="1" t="n"/>
+      <c r="G261" s="1" t="n"/>
+      <c r="H261" s="1" t="n"/>
+      <c r="I261" s="1" t="n"/>
+      <c r="J261" s="1" t="n"/>
+      <c r="K261" s="1" t="n"/>
+      <c r="L261" s="1" t="n"/>
+      <c r="M261" s="1" t="n"/>
+      <c r="N261" s="1" t="n"/>
+      <c r="O261" s="1" t="n"/>
+      <c r="P261" s="1" t="n"/>
+      <c r="Q261" s="1" t="n"/>
+      <c r="R261" s="1" t="n"/>
+      <c r="S261" s="1" t="n"/>
+      <c r="T261" s="1" t="n"/>
+      <c r="U261" s="1" t="n"/>
+      <c r="V261" s="1" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n"/>
+      <c r="B262" s="1" t="n"/>
+      <c r="C262" s="1" t="n"/>
+      <c r="D262" s="1" t="n"/>
+      <c r="E262" s="1" t="n"/>
+      <c r="F262" s="1" t="n"/>
+      <c r="G262" s="1" t="n"/>
+      <c r="H262" s="1" t="n"/>
+      <c r="I262" s="1" t="n"/>
+      <c r="J262" s="1" t="n"/>
+      <c r="K262" s="1" t="n"/>
+      <c r="L262" s="1" t="n"/>
+      <c r="M262" s="1" t="n"/>
+      <c r="N262" s="1" t="n"/>
+      <c r="O262" s="1" t="n"/>
+      <c r="P262" s="1" t="n"/>
+      <c r="Q262" s="1" t="n"/>
+      <c r="R262" s="1" t="n"/>
+      <c r="S262" s="1" t="n"/>
+      <c r="T262" s="1" t="n"/>
+      <c r="U262" s="1" t="n"/>
+      <c r="V262" s="1" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n"/>
+      <c r="B263" s="1" t="n"/>
+      <c r="C263" s="1" t="n"/>
+      <c r="D263" s="1" t="n"/>
+      <c r="E263" s="1" t="n"/>
+      <c r="F263" s="1" t="n"/>
+      <c r="G263" s="1" t="n"/>
+      <c r="H263" s="1" t="n"/>
+      <c r="I263" s="1" t="n"/>
+      <c r="J263" s="1" t="n"/>
+      <c r="K263" s="1" t="n"/>
+      <c r="L263" s="1" t="n"/>
+      <c r="M263" s="1" t="n"/>
+      <c r="N263" s="1" t="n"/>
+      <c r="O263" s="1" t="n"/>
+      <c r="P263" s="1" t="n"/>
+      <c r="Q263" s="1" t="n"/>
+      <c r="R263" s="1" t="n"/>
+      <c r="S263" s="1" t="n"/>
+      <c r="T263" s="1" t="n"/>
+      <c r="U263" s="1" t="n"/>
+      <c r="V263" s="1" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="n"/>
+      <c r="B264" s="1" t="n"/>
+      <c r="C264" s="1" t="n"/>
+      <c r="D264" s="1" t="n"/>
+      <c r="E264" s="1" t="n"/>
+      <c r="F264" s="1" t="n"/>
+      <c r="G264" s="1" t="n"/>
+      <c r="H264" s="1" t="n"/>
+      <c r="I264" s="1" t="n"/>
+      <c r="J264" s="1" t="n"/>
+      <c r="K264" s="1" t="n"/>
+      <c r="L264" s="1" t="n"/>
+      <c r="M264" s="1" t="n"/>
+      <c r="N264" s="1" t="n"/>
+      <c r="O264" s="1" t="n"/>
+      <c r="P264" s="1" t="n"/>
+      <c r="Q264" s="1" t="n"/>
+      <c r="R264" s="1" t="n"/>
+      <c r="S264" s="1" t="n"/>
+      <c r="T264" s="1" t="n"/>
+      <c r="U264" s="1" t="n"/>
+      <c r="V264" s="1" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="n"/>
+      <c r="B265" s="1" t="n"/>
+      <c r="C265" s="1" t="n"/>
+      <c r="D265" s="1" t="n"/>
+      <c r="E265" s="1" t="n"/>
+      <c r="F265" s="1" t="n"/>
+      <c r="G265" s="1" t="n"/>
+      <c r="H265" s="1" t="n"/>
+      <c r="I265" s="1" t="n"/>
+      <c r="J265" s="1" t="n"/>
+      <c r="K265" s="1" t="n"/>
+      <c r="L265" s="1" t="n"/>
+      <c r="M265" s="1" t="n"/>
+      <c r="N265" s="1" t="n"/>
+      <c r="O265" s="1" t="n"/>
+      <c r="P265" s="1" t="n"/>
+      <c r="Q265" s="1" t="n"/>
+      <c r="R265" s="1" t="n"/>
+      <c r="S265" s="1" t="n"/>
+      <c r="T265" s="1" t="n"/>
+      <c r="U265" s="1" t="n"/>
+      <c r="V265" s="1" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n"/>
+      <c r="B266" s="1" t="n"/>
+      <c r="C266" s="1" t="n"/>
+      <c r="D266" s="1" t="n"/>
+      <c r="E266" s="1" t="n"/>
+      <c r="F266" s="1" t="n"/>
+      <c r="G266" s="1" t="n"/>
+      <c r="H266" s="1" t="n"/>
+      <c r="I266" s="1" t="n"/>
+      <c r="J266" s="1" t="n"/>
+      <c r="K266" s="1" t="n"/>
+      <c r="L266" s="1" t="n"/>
+      <c r="M266" s="1" t="n"/>
+      <c r="N266" s="1" t="n"/>
+      <c r="O266" s="1" t="n"/>
+      <c r="P266" s="1" t="n"/>
+      <c r="Q266" s="1" t="n"/>
+      <c r="R266" s="1" t="n"/>
+      <c r="S266" s="1" t="n"/>
+      <c r="T266" s="1" t="n"/>
+      <c r="U266" s="1" t="n"/>
+      <c r="V266" s="1" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n"/>
+      <c r="B267" s="1" t="n"/>
+      <c r="C267" s="1" t="n"/>
+      <c r="D267" s="1" t="n"/>
+      <c r="E267" s="1" t="n"/>
+      <c r="F267" s="1" t="n"/>
+      <c r="G267" s="1" t="n"/>
+      <c r="H267" s="1" t="n"/>
+      <c r="I267" s="1" t="n"/>
+      <c r="J267" s="1" t="n"/>
+      <c r="K267" s="1" t="n"/>
+      <c r="L267" s="1" t="n"/>
+      <c r="M267" s="1" t="n"/>
+      <c r="N267" s="1" t="n"/>
+      <c r="O267" s="1" t="n"/>
+      <c r="P267" s="1" t="n"/>
+      <c r="Q267" s="1" t="n"/>
+      <c r="R267" s="1" t="n"/>
+      <c r="S267" s="1" t="n"/>
+      <c r="T267" s="1" t="n"/>
+      <c r="U267" s="1" t="n"/>
+      <c r="V267" s="1" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n"/>
+      <c r="B268" s="1" t="n"/>
+      <c r="C268" s="1" t="n"/>
+      <c r="D268" s="1" t="n"/>
+      <c r="E268" s="1" t="n"/>
+      <c r="F268" s="1" t="n"/>
+      <c r="G268" s="1" t="n"/>
+      <c r="H268" s="1" t="n"/>
+      <c r="I268" s="1" t="n"/>
+      <c r="J268" s="1" t="n"/>
+      <c r="K268" s="1" t="n"/>
+      <c r="L268" s="1" t="n"/>
+      <c r="M268" s="1" t="n"/>
+      <c r="N268" s="1" t="n"/>
+      <c r="O268" s="1" t="n"/>
+      <c r="P268" s="1" t="n"/>
+      <c r="Q268" s="1" t="n"/>
+      <c r="R268" s="1" t="n"/>
+      <c r="S268" s="1" t="n"/>
+      <c r="T268" s="1" t="n"/>
+      <c r="U268" s="1" t="n"/>
+      <c r="V268" s="1" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n"/>
+      <c r="B269" s="1" t="n"/>
+      <c r="C269" s="1" t="n"/>
+      <c r="D269" s="1" t="n"/>
+      <c r="E269" s="1" t="n"/>
+      <c r="F269" s="1" t="n"/>
+      <c r="G269" s="1" t="n"/>
+      <c r="H269" s="1" t="n"/>
+      <c r="I269" s="1" t="n"/>
+      <c r="J269" s="1" t="n"/>
+      <c r="K269" s="1" t="n"/>
+      <c r="L269" s="1" t="n"/>
+      <c r="M269" s="1" t="n"/>
+      <c r="N269" s="1" t="n"/>
+      <c r="O269" s="1" t="n"/>
+      <c r="P269" s="1" t="n"/>
+      <c r="Q269" s="1" t="n"/>
+      <c r="R269" s="1" t="n"/>
+      <c r="S269" s="1" t="n"/>
+      <c r="T269" s="1" t="n"/>
+      <c r="U269" s="1" t="n"/>
+      <c r="V269" s="1" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n"/>
+      <c r="B270" s="1" t="n"/>
+      <c r="C270" s="1" t="n"/>
+      <c r="D270" s="1" t="n"/>
+      <c r="E270" s="1" t="n"/>
+      <c r="F270" s="1" t="n"/>
+      <c r="G270" s="1" t="n"/>
+      <c r="H270" s="1" t="n"/>
+      <c r="I270" s="1" t="n"/>
+      <c r="J270" s="1" t="n"/>
+      <c r="K270" s="1" t="n"/>
+      <c r="L270" s="1" t="n"/>
+      <c r="M270" s="1" t="n"/>
+      <c r="N270" s="1" t="n"/>
+      <c r="O270" s="1" t="n"/>
+      <c r="P270" s="1" t="n"/>
+      <c r="Q270" s="1" t="n"/>
+      <c r="R270" s="1" t="n"/>
+      <c r="S270" s="1" t="n"/>
+      <c r="T270" s="1" t="n"/>
+      <c r="U270" s="1" t="n"/>
+      <c r="V270" s="1" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="n"/>
+      <c r="B271" s="1" t="n"/>
+      <c r="C271" s="1" t="n"/>
+      <c r="D271" s="1" t="n"/>
+      <c r="E271" s="1" t="n"/>
+      <c r="F271" s="1" t="n"/>
+      <c r="G271" s="1" t="n"/>
+      <c r="H271" s="1" t="n"/>
+      <c r="I271" s="1" t="n"/>
+      <c r="J271" s="1" t="n"/>
+      <c r="K271" s="1" t="n"/>
+      <c r="L271" s="1" t="n"/>
+      <c r="M271" s="1" t="n"/>
+      <c r="N271" s="1" t="n"/>
+      <c r="O271" s="1" t="n"/>
+      <c r="P271" s="1" t="n"/>
+      <c r="Q271" s="1" t="n"/>
+      <c r="R271" s="1" t="n"/>
+      <c r="S271" s="1" t="n"/>
+      <c r="T271" s="1" t="n"/>
+      <c r="U271" s="1" t="n"/>
+      <c r="V271" s="1" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="n"/>
+      <c r="B272" s="1" t="n"/>
+      <c r="C272" s="1" t="n"/>
+      <c r="D272" s="1" t="n"/>
+      <c r="E272" s="1" t="n"/>
+      <c r="F272" s="1" t="n"/>
+      <c r="G272" s="1" t="n"/>
+      <c r="H272" s="1" t="n"/>
+      <c r="I272" s="1" t="n"/>
+      <c r="J272" s="1" t="n"/>
+      <c r="K272" s="1" t="n"/>
+      <c r="L272" s="1" t="n"/>
+      <c r="M272" s="1" t="n"/>
+      <c r="N272" s="1" t="n"/>
+      <c r="O272" s="1" t="n"/>
+      <c r="P272" s="1" t="n"/>
+      <c r="Q272" s="1" t="n"/>
+      <c r="R272" s="1" t="n"/>
+      <c r="S272" s="1" t="n"/>
+      <c r="T272" s="1" t="n"/>
+      <c r="U272" s="1" t="n"/>
+      <c r="V272" s="1" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="n"/>
+      <c r="B273" s="1" t="n"/>
+      <c r="C273" s="1" t="n"/>
+      <c r="D273" s="1" t="n"/>
+      <c r="E273" s="1" t="n"/>
+      <c r="F273" s="1" t="n"/>
+      <c r="G273" s="1" t="n"/>
+      <c r="H273" s="1" t="n"/>
+      <c r="I273" s="1" t="n"/>
+      <c r="J273" s="1" t="n"/>
+      <c r="K273" s="1" t="n"/>
+      <c r="L273" s="1" t="n"/>
+      <c r="M273" s="1" t="n"/>
+      <c r="N273" s="1" t="n"/>
+      <c r="O273" s="1" t="n"/>
+      <c r="P273" s="1" t="n"/>
+      <c r="Q273" s="1" t="n"/>
+      <c r="R273" s="1" t="n"/>
+      <c r="S273" s="1" t="n"/>
+      <c r="T273" s="1" t="n"/>
+      <c r="U273" s="1" t="n"/>
+      <c r="V273" s="1" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="n"/>
+      <c r="B274" s="1" t="n"/>
+      <c r="C274" s="1" t="n"/>
+      <c r="D274" s="1" t="n"/>
+      <c r="E274" s="1" t="n"/>
+      <c r="F274" s="1" t="n"/>
+      <c r="G274" s="1" t="n"/>
+      <c r="H274" s="1" t="n"/>
+      <c r="I274" s="1" t="n"/>
+      <c r="J274" s="1" t="n"/>
+      <c r="K274" s="1" t="n"/>
+      <c r="L274" s="1" t="n"/>
+      <c r="M274" s="1" t="n"/>
+      <c r="N274" s="1" t="n"/>
+      <c r="O274" s="1" t="n"/>
+      <c r="P274" s="1" t="n"/>
+      <c r="Q274" s="1" t="n"/>
+      <c r="R274" s="1" t="n"/>
+      <c r="S274" s="1" t="n"/>
+      <c r="T274" s="1" t="n"/>
+      <c r="U274" s="1" t="n"/>
+      <c r="V274" s="1" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="n"/>
+      <c r="B275" s="1" t="n"/>
+      <c r="C275" s="1" t="n"/>
+      <c r="D275" s="1" t="n"/>
+      <c r="E275" s="1" t="n"/>
+      <c r="F275" s="1" t="n"/>
+      <c r="G275" s="1" t="n"/>
+      <c r="H275" s="1" t="n"/>
+      <c r="I275" s="1" t="n"/>
+      <c r="J275" s="1" t="n"/>
+      <c r="K275" s="1" t="n"/>
+      <c r="L275" s="1" t="n"/>
+      <c r="M275" s="1" t="n"/>
+      <c r="N275" s="1" t="n"/>
+      <c r="O275" s="1" t="n"/>
+      <c r="P275" s="1" t="n"/>
+      <c r="Q275" s="1" t="n"/>
+      <c r="R275" s="1" t="n"/>
+      <c r="S275" s="1" t="n"/>
+      <c r="T275" s="1" t="n"/>
+      <c r="U275" s="1" t="n"/>
+      <c r="V275" s="1" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="n"/>
+      <c r="B276" s="1" t="n"/>
+      <c r="C276" s="1" t="n"/>
+      <c r="D276" s="1" t="n"/>
+      <c r="E276" s="1" t="n"/>
+      <c r="F276" s="1" t="n"/>
+      <c r="G276" s="1" t="n"/>
+      <c r="H276" s="1" t="n"/>
+      <c r="I276" s="1" t="n"/>
+      <c r="J276" s="1" t="n"/>
+      <c r="K276" s="1" t="n"/>
+      <c r="L276" s="1" t="n"/>
+      <c r="M276" s="1" t="n"/>
+      <c r="N276" s="1" t="n"/>
+      <c r="O276" s="1" t="n"/>
+      <c r="P276" s="1" t="n"/>
+      <c r="Q276" s="1" t="n"/>
+      <c r="R276" s="1" t="n"/>
+      <c r="S276" s="1" t="n"/>
+      <c r="T276" s="1" t="n"/>
+      <c r="U276" s="1" t="n"/>
+      <c r="V276" s="1" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="n"/>
+      <c r="B277" s="1" t="n"/>
+      <c r="C277" s="1" t="n"/>
+      <c r="D277" s="1" t="n"/>
+      <c r="E277" s="1" t="n"/>
+      <c r="F277" s="1" t="n"/>
+      <c r="G277" s="1" t="n"/>
+      <c r="H277" s="1" t="n"/>
+      <c r="I277" s="1" t="n"/>
+      <c r="J277" s="1" t="n"/>
+      <c r="K277" s="1" t="n"/>
+      <c r="L277" s="1" t="n"/>
+      <c r="M277" s="1" t="n"/>
+      <c r="N277" s="1" t="n"/>
+      <c r="O277" s="1" t="n"/>
+      <c r="P277" s="1" t="n"/>
+      <c r="Q277" s="1" t="n"/>
+      <c r="R277" s="1" t="n"/>
+      <c r="S277" s="1" t="n"/>
+      <c r="T277" s="1" t="n"/>
+      <c r="U277" s="1" t="n"/>
+      <c r="V277" s="1" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="n"/>
+      <c r="B278" s="1" t="n"/>
+      <c r="C278" s="1" t="n"/>
+      <c r="D278" s="1" t="n"/>
+      <c r="E278" s="1" t="n"/>
+      <c r="F278" s="1" t="n"/>
+      <c r="G278" s="1" t="n"/>
+      <c r="H278" s="1" t="n"/>
+      <c r="I278" s="1" t="n"/>
+      <c r="J278" s="1" t="n"/>
+      <c r="K278" s="1" t="n"/>
+      <c r="L278" s="1" t="n"/>
+      <c r="M278" s="1" t="n"/>
+      <c r="N278" s="1" t="n"/>
+      <c r="O278" s="1" t="n"/>
+      <c r="P278" s="1" t="n"/>
+      <c r="Q278" s="1" t="n"/>
+      <c r="R278" s="1" t="n"/>
+      <c r="S278" s="1" t="n"/>
+      <c r="T278" s="1" t="n"/>
+      <c r="U278" s="1" t="n"/>
+      <c r="V278" s="1" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="n"/>
+      <c r="B279" s="1" t="n"/>
+      <c r="C279" s="1" t="n"/>
+      <c r="D279" s="1" t="n"/>
+      <c r="E279" s="1" t="n"/>
+      <c r="F279" s="1" t="n"/>
+      <c r="G279" s="1" t="n"/>
+      <c r="H279" s="1" t="n"/>
+      <c r="I279" s="1" t="n"/>
+      <c r="J279" s="1" t="n"/>
+      <c r="K279" s="1" t="n"/>
+      <c r="L279" s="1" t="n"/>
+      <c r="M279" s="1" t="n"/>
+      <c r="N279" s="1" t="n"/>
+      <c r="O279" s="1" t="n"/>
+      <c r="P279" s="1" t="n"/>
+      <c r="Q279" s="1" t="n"/>
+      <c r="R279" s="1" t="n"/>
+      <c r="S279" s="1" t="n"/>
+      <c r="T279" s="1" t="n"/>
+      <c r="U279" s="1" t="n"/>
+      <c r="V279" s="1" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="n"/>
+      <c r="B280" s="1" t="n"/>
+      <c r="C280" s="1" t="n"/>
+      <c r="D280" s="1" t="n"/>
+      <c r="E280" s="1" t="n"/>
+      <c r="F280" s="1" t="n"/>
+      <c r="G280" s="1" t="n"/>
+      <c r="H280" s="1" t="n"/>
+      <c r="I280" s="1" t="n"/>
+      <c r="J280" s="1" t="n"/>
+      <c r="K280" s="1" t="n"/>
+      <c r="L280" s="1" t="n"/>
+      <c r="M280" s="1" t="n"/>
+      <c r="N280" s="1" t="n"/>
+      <c r="O280" s="1" t="n"/>
+      <c r="P280" s="1" t="n"/>
+      <c r="Q280" s="1" t="n"/>
+      <c r="R280" s="1" t="n"/>
+      <c r="S280" s="1" t="n"/>
+      <c r="T280" s="1" t="n"/>
+      <c r="U280" s="1" t="n"/>
+      <c r="V280" s="1" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="n"/>
+      <c r="B281" s="1" t="n"/>
+      <c r="C281" s="1" t="n"/>
+      <c r="D281" s="1" t="n"/>
+      <c r="E281" s="1" t="n"/>
+      <c r="F281" s="1" t="n"/>
+      <c r="G281" s="1" t="n"/>
+      <c r="H281" s="1" t="n"/>
+      <c r="I281" s="1" t="n"/>
+      <c r="J281" s="1" t="n"/>
+      <c r="K281" s="1" t="n"/>
+      <c r="L281" s="1" t="n"/>
+      <c r="M281" s="1" t="n"/>
+      <c r="N281" s="1" t="n"/>
+      <c r="O281" s="1" t="n"/>
+      <c r="P281" s="1" t="n"/>
+      <c r="Q281" s="1" t="n"/>
+      <c r="R281" s="1" t="n"/>
+      <c r="S281" s="1" t="n"/>
+      <c r="T281" s="1" t="n"/>
+      <c r="U281" s="1" t="n"/>
+      <c r="V281" s="1" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/concursoai_roadmap_v3_FINAL.xlsx
+++ b/concursoai_roadmap_v3_FINAL.xlsx
@@ -5235,9 +5235,9 @@
           <t>✅ Teste</t>
         </is>
       </c>
-      <c r="T55" s="84" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T55" s="88" t="inlineStr">
+        <is>
+          <t>🟡 Em andamento</t>
         </is>
       </c>
     </row>

--- a/concursoai_roadmap_v3_FINAL.xlsx
+++ b/concursoai_roadmap_v3_FINAL.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="58">
+  <fonts count="59">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -351,6 +351,11 @@
       <color rgb="008ab0c8"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FFA500"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="28">
     <fill>
@@ -560,7 +565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -805,6 +810,7 @@
     <xf numFmtId="0" fontId="55" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5042,9 +5048,9 @@
           <t>💻 Backend</t>
         </is>
       </c>
-      <c r="T48" s="84" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T48" s="90" t="inlineStr">
+        <is>
+          <t>🟡 Em andamento</t>
         </is>
       </c>
     </row>

--- a/concursoai_roadmap_v3_FINAL.xlsx
+++ b/concursoai_roadmap_v3_FINAL.xlsx
@@ -5048,9 +5048,9 @@
           <t>💻 Backend</t>
         </is>
       </c>
-      <c r="T48" s="90" t="inlineStr">
-        <is>
-          <t>🟡 Em andamento</t>
+      <c r="T48" s="89" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
         </is>
       </c>
     </row>
@@ -5106,9 +5106,9 @@
           <t>✅ Teste</t>
         </is>
       </c>
-      <c r="T50" s="84" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T50" s="89" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
         </is>
       </c>
     </row>
@@ -5133,9 +5133,9 @@
           <t>✅ Teste</t>
         </is>
       </c>
-      <c r="T51" s="84" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T51" s="89" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
         </is>
       </c>
     </row>

--- a/concursoai_roadmap_v3_FINAL.xlsx
+++ b/concursoai_roadmap_v3_FINAL.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="59">
+  <fonts count="60">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -356,6 +356,11 @@
       <color rgb="00FFA500"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00F0A500"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="28">
     <fill>
@@ -565,7 +570,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -811,6 +816,7 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5160,9 +5166,9 @@
           <t>✅ Teste</t>
         </is>
       </c>
-      <c r="T52" s="84" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T52" s="89" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
         </is>
       </c>
     </row>
@@ -5214,9 +5220,9 @@
           <t>✅ Teste</t>
         </is>
       </c>
-      <c r="T54" s="84" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T54" s="89" t="inlineStr">
+        <is>
+          <t>✅ Concluído</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5247,7 @@
           <t>✅ Teste</t>
         </is>
       </c>
-      <c r="T55" s="88" t="inlineStr">
+      <c r="T55" s="91" t="inlineStr">
         <is>
           <t>🟡 Em andamento</t>
         </is>
@@ -5268,9 +5274,9 @@
           <t>✅ Teste</t>
         </is>
       </c>
-      <c r="T56" s="84" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T56" s="91" t="inlineStr">
+        <is>
+          <t>🟡 Em andamento</t>
         </is>
       </c>
     </row>
@@ -5295,9 +5301,9 @@
           <t>✅ Teste</t>
         </is>
       </c>
-      <c r="T57" s="84" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T57" s="91" t="inlineStr">
+        <is>
+          <t>🟡 Em andamento</t>
         </is>
       </c>
     </row>
@@ -5322,9 +5328,9 @@
           <t>✅ Teste</t>
         </is>
       </c>
-      <c r="T58" s="84" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T58" s="91" t="inlineStr">
+        <is>
+          <t>🟡 Em andamento</t>
         </is>
       </c>
     </row>
@@ -5349,9 +5355,9 @@
           <t>✅ Teste</t>
         </is>
       </c>
-      <c r="T59" s="84" t="inlineStr">
-        <is>
-          <t>⬜ Pendente</t>
+      <c r="T59" s="91" t="inlineStr">
+        <is>
+          <t>🟡 Em andamento</t>
         </is>
       </c>
     </row>
